--- a/PRACTICAS DOCENCIA/LABORATORIO MB1/LISTADO COMPLETO MACROS/PUNTEOS FINALES.xlsx
+++ b/PRACTICAS DOCENCIA/LABORATORIO MB1/LISTADO COMPLETO MACROS/PUNTEOS FINALES.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ubicacion C a D\Documentos\gitPrimer-Semetre-25\Lab MB1 B\LISTADO COMPLETO MACROS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Documents\gitPrimer-Semestre-25\PRACTICAS DOCENCIA\LABORATORIO MB1\LISTADO COMPLETO MACROS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7D8185-6717-443E-A15A-787AB624CF54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CA809A-287D-47A0-B4AC-BBF854AA7444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{F4BDE4DC-E94C-4D9E-A851-8F281B73FE4C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F4BDE4DC-E94C-4D9E-A851-8F281B73FE4C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="111">
   <si>
     <t>No.</t>
   </si>
@@ -356,6 +357,12 @@
   </si>
   <si>
     <t>HT(9/10/2025)</t>
+  </si>
+  <si>
+    <t>HT(16/10/2025)</t>
+  </si>
+  <si>
+    <t>Proyecto Final</t>
   </si>
 </sst>
 </file>
@@ -899,13 +906,766 @@
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="htfexp"/>
+      <sheetName val="punteo"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="6">
+          <cell r="L6">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="L7">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="L8">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="L9">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="L10">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="L11">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="L12">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="L13">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="L14">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="L15">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="L16">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="L17">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="L18">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="L19">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="L20">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="L21">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="L22">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="L23">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="L24">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="L25">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="L26">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="L27">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="L28">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="L29">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="L30">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="L31">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="L32">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="L33">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="L34">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="L35">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="L36">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="L37">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="L38">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="L39">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="L40">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="L41">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="L42">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="L43">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="L44">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="L45">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="L46">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="L47">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="L48">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="L49">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="L50">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="L51">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="L52">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="L53">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="L54">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="L55">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="L56">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="L57">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="L58">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="L59">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="L60">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="L61">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="L62">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="L63">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="L64">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="L65">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="L66">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="L67">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="L68">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="L69">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="L70">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="L71">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="L72">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="L73">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="L74">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="L75">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="L76">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="L77">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="L78">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="htfxasint"/>
       <sheetName val="punteo"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="6">
+          <cell r="L6">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="L7">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="L8">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="L9">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="L10">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="L11">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="L12">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="L13">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="L14">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="L15">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="L16">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="L17">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="L18">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="L19">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="L20">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="L21">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="L22">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="L23">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="L24">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="L25">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="L26">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="L27">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="L28">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="L29">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="L30">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="L31">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="L32">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="L33">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="L34">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="L35">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="L36">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="L37">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="L38">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="L39">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="L40">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="L41">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="L42">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="L43">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="L44">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="L45">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="L46">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="L47">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="L48">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="L49">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="L50">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="L51">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="L52">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="L53">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="L54">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="L55">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="L56">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="L57">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="L58">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="L59">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="L60">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="L61">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="L62">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="L63">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="L64">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="L65">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="L66">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="L67">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="L68">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="L69">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="L70">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="L71">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="L72">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="L73">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="L74">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="L75">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="L76">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="L77">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="L78">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1209,39 +1969,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9337005-F0FF-4A3F-B098-783C2B519B7D}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A4:W80"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A4:X80"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.26953125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.28515625" style="1" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="20.1796875" customWidth="1"/>
-    <col min="5" max="5" width="36.1796875" customWidth="1"/>
-    <col min="6" max="6" width="22.54296875" customWidth="1"/>
-    <col min="7" max="7" width="19.54296875" customWidth="1"/>
-    <col min="8" max="9" width="19.90625" customWidth="1"/>
-    <col min="10" max="10" width="24.1796875" customWidth="1"/>
-    <col min="11" max="11" width="30.7265625" customWidth="1"/>
-    <col min="12" max="13" width="27.6328125" customWidth="1"/>
-    <col min="14" max="14" width="21.1796875" customWidth="1"/>
-    <col min="15" max="19" width="27.26953125" customWidth="1"/>
-    <col min="20" max="21" width="31.81640625" customWidth="1"/>
-    <col min="22" max="22" width="22.81640625" customWidth="1"/>
-    <col min="23" max="23" width="18.54296875" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
+    <col min="5" max="5" width="36.140625" customWidth="1"/>
+    <col min="6" max="6" width="29.5703125" customWidth="1"/>
+    <col min="7" max="7" width="25.85546875" customWidth="1"/>
+    <col min="8" max="8" width="29.42578125" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="10" max="10" width="29.28515625" customWidth="1"/>
+    <col min="11" max="11" width="30.7109375" customWidth="1"/>
+    <col min="12" max="12" width="27.5703125" customWidth="1"/>
+    <col min="13" max="13" width="32" customWidth="1"/>
+    <col min="14" max="14" width="21.140625" customWidth="1"/>
+    <col min="15" max="16" width="27.28515625" customWidth="1"/>
+    <col min="17" max="17" width="33.5703125" customWidth="1"/>
+    <col min="18" max="20" width="27.28515625" customWidth="1"/>
+    <col min="21" max="22" width="31.85546875" customWidth="1"/>
+    <col min="23" max="23" width="22.85546875" customWidth="1"/>
+    <col min="24" max="24" width="18.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:23" x14ac:dyDescent="0.35">
-      <c r="T4" s="5" t="s">
-        <v>75</v>
-      </c>
+    <row r="4" spans="3:24" x14ac:dyDescent="0.25">
       <c r="U4" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="V4" s="15" t="s">
+      <c r="V4" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="W4" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="W4" s="15"/>
-    </row>
-    <row r="5" spans="3:23" x14ac:dyDescent="0.35">
+      <c r="X4" s="15"/>
+    </row>
+    <row r="5" spans="3:24" x14ac:dyDescent="0.25">
       <c r="J5" t="s">
         <v>96</v>
       </c>
@@ -1257,20 +2021,20 @@
       <c r="Q5" t="s">
         <v>107</v>
       </c>
-      <c r="T5" s="5" t="s">
+      <c r="U5" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="U5" s="5" t="s">
+      <c r="V5" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="V5" s="4" t="s">
+      <c r="W5" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="W5" s="4" t="s">
+      <c r="X5" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="3:23" x14ac:dyDescent="0.35">
+    <row r="6" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C6" s="1" t="s">
         <v>0</v>
       </c>
@@ -1316,22 +2080,27 @@
       <c r="Q6" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="7">
+      <c r="R6" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="S6" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="T6" s="4"/>
+      <c r="U6" s="7">
         <v>45911</v>
       </c>
-      <c r="U6" s="4" t="s">
+      <c r="V6" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="V6" s="2">
+      <c r="W6" s="2">
         <v>45930</v>
       </c>
-      <c r="W6" s="2">
+      <c r="X6" s="2">
         <v>45902</v>
       </c>
     </row>
-    <row r="7" spans="3:23" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C7">
         <v>1</v>
       </c>
@@ -1376,22 +2145,26 @@
         <v>0</v>
       </c>
       <c r="R7" s="14">
-        <f>IF([1]punteo!M6="",0,[2]punteo!M6)</f>
-        <v>0</v>
-      </c>
-      <c r="T7">
+        <f>IF([2]punteo!L6="",0,[2]punteo!L6)</f>
+        <v>0</v>
+      </c>
+      <c r="S7" s="14">
+        <f>IF([3]punteo!L6="",0,[3]punteo!L6)</f>
+        <v>0</v>
+      </c>
+      <c r="U7">
         <f>IF(O7&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="U7">
+      <c r="V7">
         <f>IF(P7&gt;0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="V7" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="3:23" x14ac:dyDescent="0.35">
+      <c r="W7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C8">
         <v>2</v>
       </c>
@@ -1439,22 +2212,26 @@
         <v>100</v>
       </c>
       <c r="R8" s="14">
-        <f>IF([1]punteo!M7="",0,[2]punteo!M7)</f>
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <f t="shared" ref="T8:T71" si="0">IF(O8&gt;0,1,0)</f>
-        <v>1</v>
+        <f>IF([2]punteo!L7="",0,[2]punteo!L7)</f>
+        <v>100</v>
+      </c>
+      <c r="S8" s="14">
+        <f>IF([3]punteo!L7="",0,[3]punteo!L7)</f>
+        <v>100</v>
       </c>
       <c r="U8">
-        <f t="shared" ref="U8:U71" si="1">IF(P8&gt;0,1,0)</f>
+        <f t="shared" ref="U8:U71" si="0">IF(O8&gt;0,1,0)</f>
         <v>1</v>
       </c>
       <c r="V8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="3:23" x14ac:dyDescent="0.35">
+        <f t="shared" ref="V8:V71" si="1">IF(P8&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C9">
         <v>3</v>
       </c>
@@ -1499,22 +2276,26 @@
         <v>80</v>
       </c>
       <c r="R9" s="14">
-        <f>IF([1]punteo!M8="",0,[2]punteo!M8)</f>
-        <v>0</v>
-      </c>
-      <c r="T9">
+        <f>IF([2]punteo!L8="",0,[2]punteo!L8)</f>
+        <v>0</v>
+      </c>
+      <c r="S9" s="14">
+        <f>IF([3]punteo!L8="",0,[3]punteo!L8)</f>
+        <v>100</v>
+      </c>
+      <c r="U9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U9">
+      <c r="V9">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="3:23" x14ac:dyDescent="0.35">
+      <c r="W9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C10">
         <v>4</v>
       </c>
@@ -1556,22 +2337,26 @@
         <v>0</v>
       </c>
       <c r="R10" s="14">
-        <f>IF([1]punteo!M9="",0,[2]punteo!M9)</f>
-        <v>0</v>
-      </c>
-      <c r="T10">
+        <f>IF([2]punteo!L9="",0,[2]punteo!L9)</f>
+        <v>0</v>
+      </c>
+      <c r="S10" s="14">
+        <f>IF([3]punteo!L9="",0,[3]punteo!L9)</f>
+        <v>0</v>
+      </c>
+      <c r="U10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U10">
+      <c r="V10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="3:23" x14ac:dyDescent="0.35">
+      <c r="W10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C11">
         <v>5</v>
       </c>
@@ -1616,22 +2401,26 @@
         <v>100</v>
       </c>
       <c r="R11" s="14">
-        <f>IF([1]punteo!M10="",0,[2]punteo!M10)</f>
-        <v>0</v>
-      </c>
-      <c r="T11">
+        <f>IF([2]punteo!L10="",0,[2]punteo!L10)</f>
+        <v>100</v>
+      </c>
+      <c r="S11" s="14">
+        <f>IF([3]punteo!L10="",0,[3]punteo!L10)</f>
+        <v>100</v>
+      </c>
+      <c r="U11">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U11">
+      <c r="V11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="3:23" x14ac:dyDescent="0.35">
+      <c r="W11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C12">
         <v>6</v>
       </c>
@@ -1673,22 +2462,26 @@
         <v>0</v>
       </c>
       <c r="R12" s="14">
-        <f>IF([1]punteo!M11="",0,[2]punteo!M11)</f>
-        <v>0</v>
-      </c>
-      <c r="T12">
+        <f>IF([2]punteo!L11="",0,[2]punteo!L11)</f>
+        <v>0</v>
+      </c>
+      <c r="S12" s="14">
+        <f>IF([3]punteo!L11="",0,[3]punteo!L11)</f>
+        <v>0</v>
+      </c>
+      <c r="U12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U12">
+      <c r="V12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="3:23" x14ac:dyDescent="0.35">
+      <c r="W12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C13">
         <v>7</v>
       </c>
@@ -1733,22 +2526,26 @@
         <v>80</v>
       </c>
       <c r="R13" s="14">
-        <f>IF([1]punteo!M12="",0,[2]punteo!M12)</f>
-        <v>0</v>
-      </c>
-      <c r="T13">
+        <f>IF([2]punteo!L12="",0,[2]punteo!L12)</f>
+        <v>100</v>
+      </c>
+      <c r="S13" s="14">
+        <f>IF([3]punteo!L12="",0,[3]punteo!L12)</f>
+        <v>0</v>
+      </c>
+      <c r="U13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U13">
+      <c r="V13">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="3:23" x14ac:dyDescent="0.35">
+      <c r="W13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C14">
         <v>8</v>
       </c>
@@ -1793,22 +2590,26 @@
         <v>80</v>
       </c>
       <c r="R14" s="14">
-        <f>IF([1]punteo!M13="",0,[2]punteo!M13)</f>
-        <v>0</v>
-      </c>
-      <c r="T14">
+        <f>IF([2]punteo!L13="",0,[2]punteo!L13)</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="14">
+        <f>IF([3]punteo!L13="",0,[3]punteo!L13)</f>
+        <v>100</v>
+      </c>
+      <c r="U14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U14">
+      <c r="V14">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="3:23" x14ac:dyDescent="0.35">
+      <c r="W14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C15">
         <v>9</v>
       </c>
@@ -1856,22 +2657,26 @@
         <v>100</v>
       </c>
       <c r="R15" s="14">
-        <f>IF([1]punteo!M14="",0,[2]punteo!M14)</f>
-        <v>0</v>
-      </c>
-      <c r="T15">
+        <f>IF([2]punteo!L14="",0,[2]punteo!L14)</f>
+        <v>100</v>
+      </c>
+      <c r="S15" s="14">
+        <f>IF([3]punteo!L14="",0,[3]punteo!L14)</f>
+        <v>100</v>
+      </c>
+      <c r="U15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U15">
+      <c r="V15">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="3:23" x14ac:dyDescent="0.35">
+      <c r="W15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C16">
         <v>10</v>
       </c>
@@ -1913,22 +2718,26 @@
         <v>0</v>
       </c>
       <c r="R16" s="14">
-        <f>IF([1]punteo!M15="",0,[2]punteo!M15)</f>
-        <v>0</v>
-      </c>
-      <c r="T16">
+        <f>IF([2]punteo!L15="",0,[2]punteo!L15)</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="14">
+        <f>IF([3]punteo!L15="",0,[3]punteo!L15)</f>
+        <v>100</v>
+      </c>
+      <c r="U16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U16">
+      <c r="V16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C17">
         <v>11</v>
       </c>
@@ -1973,22 +2782,26 @@
         <v>0</v>
       </c>
       <c r="R17" s="14">
-        <f>IF([1]punteo!M16="",0,[2]punteo!M16)</f>
-        <v>0</v>
-      </c>
-      <c r="T17">
+        <f>IF([2]punteo!L16="",0,[2]punteo!L16)</f>
+        <v>0</v>
+      </c>
+      <c r="S17" s="14">
+        <f>IF([3]punteo!L16="",0,[3]punteo!L16)</f>
+        <v>0</v>
+      </c>
+      <c r="U17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U17">
+      <c r="V17">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C18">
         <v>12</v>
       </c>
@@ -2036,22 +2849,26 @@
         <v>0</v>
       </c>
       <c r="R18" s="14">
-        <f>IF([1]punteo!M17="",0,[2]punteo!M17)</f>
-        <v>0</v>
-      </c>
-      <c r="T18">
+        <f>IF([2]punteo!L17="",0,[2]punteo!L17)</f>
+        <v>0</v>
+      </c>
+      <c r="S18" s="14">
+        <f>IF([3]punteo!L17="",0,[3]punteo!L17)</f>
+        <v>100</v>
+      </c>
+      <c r="U18">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U18">
+      <c r="V18">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -2105,22 +2922,26 @@
         <v>100</v>
       </c>
       <c r="R19" s="14">
-        <f>IF([1]punteo!M18="",0,[2]punteo!M18)</f>
-        <v>0</v>
-      </c>
-      <c r="T19">
+        <f>IF([2]punteo!L18="",0,[2]punteo!L18)</f>
+        <v>100</v>
+      </c>
+      <c r="S19" s="14">
+        <f>IF([3]punteo!L18="",0,[3]punteo!L18)</f>
+        <v>100</v>
+      </c>
+      <c r="U19">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U19">
+      <c r="V19">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C20">
         <v>14</v>
       </c>
@@ -2168,22 +2989,26 @@
         <v>100</v>
       </c>
       <c r="R20" s="14">
-        <f>IF([1]punteo!M19="",0,[2]punteo!M19)</f>
-        <v>0</v>
-      </c>
-      <c r="T20">
+        <f>IF([2]punteo!L19="",0,[2]punteo!L19)</f>
+        <v>100</v>
+      </c>
+      <c r="S20" s="14">
+        <f>IF([3]punteo!L19="",0,[3]punteo!L19)</f>
+        <v>100</v>
+      </c>
+      <c r="U20">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U20">
+      <c r="V20">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C21">
         <v>15</v>
       </c>
@@ -2231,22 +3056,26 @@
         <v>0</v>
       </c>
       <c r="R21" s="14">
-        <f>IF([1]punteo!M20="",0,[2]punteo!M20)</f>
-        <v>0</v>
-      </c>
-      <c r="T21">
+        <f>IF([2]punteo!L20="",0,[2]punteo!L20)</f>
+        <v>0</v>
+      </c>
+      <c r="S21" s="14">
+        <f>IF([3]punteo!L20="",0,[3]punteo!L20)</f>
+        <v>0</v>
+      </c>
+      <c r="U21">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U21">
+      <c r="V21">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>90</v>
       </c>
@@ -2300,22 +3129,26 @@
         <v>80</v>
       </c>
       <c r="R22" s="14">
-        <f>IF([1]punteo!M21="",0,[2]punteo!M21)</f>
-        <v>0</v>
-      </c>
-      <c r="T22">
+        <f>IF([2]punteo!L21="",0,[2]punteo!L21)</f>
+        <v>100</v>
+      </c>
+      <c r="S22" s="14">
+        <f>IF([3]punteo!L21="",0,[3]punteo!L21)</f>
+        <v>100</v>
+      </c>
+      <c r="U22">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U22">
+      <c r="V22">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C23">
         <v>17</v>
       </c>
@@ -2363,22 +3196,26 @@
         <v>100</v>
       </c>
       <c r="R23" s="14">
-        <f>IF([1]punteo!M22="",0,[2]punteo!M22)</f>
-        <v>0</v>
-      </c>
-      <c r="T23">
+        <f>IF([2]punteo!L22="",0,[2]punteo!L22)</f>
+        <v>100</v>
+      </c>
+      <c r="S23" s="14">
+        <f>IF([3]punteo!L22="",0,[3]punteo!L22)</f>
+        <v>100</v>
+      </c>
+      <c r="U23">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U23">
+      <c r="V23">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -2432,22 +3269,26 @@
         <v>80</v>
       </c>
       <c r="R24" s="14">
-        <f>IF([1]punteo!M23="",0,[2]punteo!M23)</f>
-        <v>0</v>
-      </c>
-      <c r="T24">
+        <f>IF([2]punteo!L23="",0,[2]punteo!L23)</f>
+        <v>100</v>
+      </c>
+      <c r="S24" s="14">
+        <f>IF([3]punteo!L23="",0,[3]punteo!L23)</f>
+        <v>100</v>
+      </c>
+      <c r="U24">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U24">
+      <c r="V24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B25" s="13"/>
       <c r="C25">
         <v>19</v>
@@ -2496,22 +3337,26 @@
         <v>0</v>
       </c>
       <c r="R25" s="14">
-        <f>IF([1]punteo!M24="",0,[2]punteo!M24)</f>
-        <v>0</v>
-      </c>
-      <c r="T25">
+        <f>IF([2]punteo!L24="",0,[2]punteo!L24)</f>
+        <v>0</v>
+      </c>
+      <c r="S25" s="14">
+        <f>IF([3]punteo!L24="",0,[3]punteo!L24)</f>
+        <v>0</v>
+      </c>
+      <c r="U25">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U25">
+      <c r="V25">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C26">
         <v>20</v>
       </c>
@@ -2559,22 +3404,26 @@
         <v>100</v>
       </c>
       <c r="R26" s="14">
-        <f>IF([1]punteo!M25="",0,[2]punteo!M25)</f>
-        <v>0</v>
-      </c>
-      <c r="T26">
+        <f>IF([2]punteo!L25="",0,[2]punteo!L25)</f>
+        <v>0</v>
+      </c>
+      <c r="S26" s="14">
+        <f>IF([3]punteo!L25="",0,[3]punteo!L25)</f>
+        <v>100</v>
+      </c>
+      <c r="U26">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U26">
+      <c r="V26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C27">
         <v>21</v>
       </c>
@@ -2622,22 +3471,26 @@
         <v>80</v>
       </c>
       <c r="R27" s="14">
-        <f>IF([1]punteo!M26="",0,[2]punteo!M26)</f>
-        <v>0</v>
-      </c>
-      <c r="T27">
+        <f>IF([2]punteo!L26="",0,[2]punteo!L26)</f>
+        <v>100</v>
+      </c>
+      <c r="S27" s="14">
+        <f>IF([3]punteo!L26="",0,[3]punteo!L26)</f>
+        <v>100</v>
+      </c>
+      <c r="U27">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U27">
+      <c r="V27">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V27" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W27" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>88</v>
       </c>
@@ -2688,22 +3541,26 @@
         <v>80</v>
       </c>
       <c r="R28" s="14">
-        <f>IF([1]punteo!M27="",0,[2]punteo!M27)</f>
-        <v>0</v>
-      </c>
-      <c r="T28">
+        <f>IF([2]punteo!L27="",0,[2]punteo!L27)</f>
+        <v>0</v>
+      </c>
+      <c r="S28" s="14">
+        <f>IF([3]punteo!L27="",0,[3]punteo!L27)</f>
+        <v>100</v>
+      </c>
+      <c r="U28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U28">
+      <c r="V28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C29">
         <v>23</v>
       </c>
@@ -2751,22 +3608,26 @@
         <v>0</v>
       </c>
       <c r="R29" s="14">
-        <f>IF([1]punteo!M28="",0,[2]punteo!M28)</f>
-        <v>0</v>
-      </c>
-      <c r="T29">
+        <f>IF([2]punteo!L28="",0,[2]punteo!L28)</f>
+        <v>0</v>
+      </c>
+      <c r="S29" s="14">
+        <f>IF([3]punteo!L28="",0,[3]punteo!L28)</f>
+        <v>0</v>
+      </c>
+      <c r="U29">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U29">
+      <c r="V29">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C30">
         <v>24</v>
       </c>
@@ -2814,22 +3675,26 @@
         <v>0</v>
       </c>
       <c r="R30" s="14">
-        <f>IF([1]punteo!M29="",0,[2]punteo!M29)</f>
-        <v>0</v>
-      </c>
-      <c r="T30">
+        <f>IF([2]punteo!L29="",0,[2]punteo!L29)</f>
+        <v>0</v>
+      </c>
+      <c r="S30" s="14">
+        <f>IF([3]punteo!L29="",0,[3]punteo!L29)</f>
+        <v>0</v>
+      </c>
+      <c r="U30">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U30">
+      <c r="V30">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V30" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W30" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>84</v>
       </c>
@@ -2880,22 +3745,26 @@
         <v>80</v>
       </c>
       <c r="R31" s="14">
-        <f>IF([1]punteo!M30="",0,[2]punteo!M30)</f>
-        <v>0</v>
-      </c>
-      <c r="T31">
+        <f>IF([2]punteo!L30="",0,[2]punteo!L30)</f>
+        <v>0</v>
+      </c>
+      <c r="S31" s="14">
+        <f>IF([3]punteo!L30="",0,[3]punteo!L30)</f>
+        <v>100</v>
+      </c>
+      <c r="U31">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U31">
+      <c r="V31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C32">
         <v>26</v>
       </c>
@@ -2943,22 +3812,26 @@
         <v>0</v>
       </c>
       <c r="R32" s="14">
-        <f>IF([1]punteo!M31="",0,[2]punteo!M31)</f>
-        <v>0</v>
-      </c>
-      <c r="T32">
+        <f>IF([2]punteo!L31="",0,[2]punteo!L31)</f>
+        <v>0</v>
+      </c>
+      <c r="S32" s="14">
+        <f>IF([3]punteo!L31="",0,[3]punteo!L31)</f>
+        <v>0</v>
+      </c>
+      <c r="U32">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U32">
+      <c r="V32">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V32" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W32" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>90</v>
       </c>
@@ -3009,22 +3882,26 @@
         <v>80</v>
       </c>
       <c r="R33" s="14">
-        <f>IF([1]punteo!M32="",0,[2]punteo!M32)</f>
-        <v>0</v>
-      </c>
-      <c r="T33">
+        <f>IF([2]punteo!L32="",0,[2]punteo!L32)</f>
+        <v>100</v>
+      </c>
+      <c r="S33" s="14">
+        <f>IF([3]punteo!L32="",0,[3]punteo!L32)</f>
+        <v>100</v>
+      </c>
+      <c r="U33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U33">
+      <c r="V33">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -3078,22 +3955,26 @@
         <v>90</v>
       </c>
       <c r="R34" s="14">
-        <f>IF([1]punteo!M33="",0,[2]punteo!M33)</f>
-        <v>0</v>
-      </c>
-      <c r="T34">
+        <f>IF([2]punteo!L33="",0,[2]punteo!L33)</f>
+        <v>100</v>
+      </c>
+      <c r="S34" s="14">
+        <f>IF([3]punteo!L33="",0,[3]punteo!L33)</f>
+        <v>100</v>
+      </c>
+      <c r="U34">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U34">
+      <c r="V34">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C35">
         <v>29</v>
       </c>
@@ -3141,22 +4022,26 @@
         <v>80</v>
       </c>
       <c r="R35" s="14">
-        <f>IF([1]punteo!M34="",0,[2]punteo!M34)</f>
-        <v>0</v>
-      </c>
-      <c r="T35">
+        <f>IF([2]punteo!L34="",0,[2]punteo!L34)</f>
+        <v>100</v>
+      </c>
+      <c r="S35" s="14">
+        <f>IF([3]punteo!L34="",0,[3]punteo!L34)</f>
+        <v>100</v>
+      </c>
+      <c r="U35">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U35">
+      <c r="V35">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C36">
         <v>30</v>
       </c>
@@ -3204,22 +4089,26 @@
         <v>80</v>
       </c>
       <c r="R36" s="14">
-        <f>IF([1]punteo!M35="",0,[2]punteo!M35)</f>
-        <v>0</v>
-      </c>
-      <c r="T36">
+        <f>IF([2]punteo!L35="",0,[2]punteo!L35)</f>
+        <v>100</v>
+      </c>
+      <c r="S36" s="14">
+        <f>IF([3]punteo!L35="",0,[3]punteo!L35)</f>
+        <v>100</v>
+      </c>
+      <c r="U36">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U36">
+      <c r="V36">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -3273,22 +4162,26 @@
         <v>100</v>
       </c>
       <c r="R37" s="14">
-        <f>IF([1]punteo!M36="",0,[2]punteo!M36)</f>
-        <v>0</v>
-      </c>
-      <c r="T37">
+        <f>IF([2]punteo!L36="",0,[2]punteo!L36)</f>
+        <v>100</v>
+      </c>
+      <c r="S37" s="14">
+        <f>IF([3]punteo!L36="",0,[3]punteo!L36)</f>
+        <v>100</v>
+      </c>
+      <c r="U37">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U37">
+      <c r="V37">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C38">
         <v>32</v>
       </c>
@@ -3336,22 +4229,26 @@
         <v>100</v>
       </c>
       <c r="R38" s="14">
-        <f>IF([1]punteo!M37="",0,[2]punteo!M37)</f>
-        <v>0</v>
-      </c>
-      <c r="T38">
+        <f>IF([2]punteo!L37="",0,[2]punteo!L37)</f>
+        <v>100</v>
+      </c>
+      <c r="S38" s="14">
+        <f>IF([3]punteo!L37="",0,[3]punteo!L37)</f>
+        <v>100</v>
+      </c>
+      <c r="U38">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U38">
+      <c r="V38">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C39">
         <v>33</v>
       </c>
@@ -3399,22 +4296,26 @@
         <v>80</v>
       </c>
       <c r="R39" s="14">
-        <f>IF([1]punteo!M38="",0,[2]punteo!M38)</f>
-        <v>0</v>
-      </c>
-      <c r="T39">
+        <f>IF([2]punteo!L38="",0,[2]punteo!L38)</f>
+        <v>100</v>
+      </c>
+      <c r="S39" s="14">
+        <f>IF([3]punteo!L38="",0,[3]punteo!L38)</f>
+        <v>100</v>
+      </c>
+      <c r="U39">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U39">
+      <c r="V39">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -3468,22 +4369,26 @@
         <v>95</v>
       </c>
       <c r="R40" s="14">
-        <f>IF([1]punteo!M39="",0,[2]punteo!M39)</f>
-        <v>0</v>
-      </c>
-      <c r="T40">
+        <f>IF([2]punteo!L39="",0,[2]punteo!L39)</f>
+        <v>100</v>
+      </c>
+      <c r="S40" s="14">
+        <f>IF([3]punteo!L39="",0,[3]punteo!L39)</f>
+        <v>100</v>
+      </c>
+      <c r="U40">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U40">
+      <c r="V40">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -3537,22 +4442,26 @@
         <v>100</v>
       </c>
       <c r="R41" s="14">
-        <f>IF([1]punteo!M40="",0,[2]punteo!M40)</f>
-        <v>0</v>
-      </c>
-      <c r="T41">
+        <f>IF([2]punteo!L40="",0,[2]punteo!L40)</f>
+        <v>100</v>
+      </c>
+      <c r="S41" s="14">
+        <f>IF([3]punteo!L40="",0,[3]punteo!L40)</f>
+        <v>100</v>
+      </c>
+      <c r="U41">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U41">
+      <c r="V41">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C42">
         <v>36</v>
       </c>
@@ -3600,22 +4509,26 @@
         <v>0</v>
       </c>
       <c r="R42" s="14">
-        <f>IF([1]punteo!M41="",0,[2]punteo!M41)</f>
-        <v>0</v>
-      </c>
-      <c r="T42">
+        <f>IF([2]punteo!L41="",0,[2]punteo!L41)</f>
+        <v>0</v>
+      </c>
+      <c r="S42" s="14">
+        <f>IF([3]punteo!L41="",0,[3]punteo!L41)</f>
+        <v>0</v>
+      </c>
+      <c r="U42">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U42">
+      <c r="V42">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C43">
         <v>37</v>
       </c>
@@ -3657,22 +4570,26 @@
         <v>0</v>
       </c>
       <c r="R43" s="14">
-        <f>IF([1]punteo!M42="",0,[2]punteo!M42)</f>
-        <v>0</v>
-      </c>
-      <c r="T43">
+        <f>IF([2]punteo!L42="",0,[2]punteo!L42)</f>
+        <v>0</v>
+      </c>
+      <c r="S43" s="14">
+        <f>IF([3]punteo!L42="",0,[3]punteo!L42)</f>
+        <v>0</v>
+      </c>
+      <c r="U43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U43">
+      <c r="V43">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V43" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W43" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C44">
         <v>38</v>
       </c>
@@ -3720,22 +4637,26 @@
         <v>80</v>
       </c>
       <c r="R44" s="14">
-        <f>IF([1]punteo!M43="",0,[2]punteo!M43)</f>
-        <v>0</v>
-      </c>
-      <c r="T44">
+        <f>IF([2]punteo!L43="",0,[2]punteo!L43)</f>
+        <v>100</v>
+      </c>
+      <c r="S44" s="14">
+        <f>IF([3]punteo!L43="",0,[3]punteo!L43)</f>
+        <v>100</v>
+      </c>
+      <c r="U44">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U44">
+      <c r="V44">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -3786,22 +4707,26 @@
         <v>0</v>
       </c>
       <c r="R45" s="14">
-        <f>IF([1]punteo!M44="",0,[2]punteo!M44)</f>
-        <v>0</v>
-      </c>
-      <c r="T45">
+        <f>IF([2]punteo!L44="",0,[2]punteo!L44)</f>
+        <v>0</v>
+      </c>
+      <c r="S45" s="14">
+        <f>IF([3]punteo!L44="",0,[3]punteo!L44)</f>
+        <v>100</v>
+      </c>
+      <c r="U45">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U45">
+      <c r="V45">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C46">
         <v>40</v>
       </c>
@@ -3849,22 +4774,26 @@
         <v>0</v>
       </c>
       <c r="R46" s="14">
-        <f>IF([1]punteo!M45="",0,[2]punteo!M45)</f>
-        <v>0</v>
-      </c>
-      <c r="T46">
+        <f>IF([2]punteo!L45="",0,[2]punteo!L45)</f>
+        <v>0</v>
+      </c>
+      <c r="S46" s="14">
+        <f>IF([3]punteo!L45="",0,[3]punteo!L45)</f>
+        <v>0</v>
+      </c>
+      <c r="U46">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U46">
+      <c r="V46">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C47">
         <v>41</v>
       </c>
@@ -3906,22 +4835,26 @@
         <v>0</v>
       </c>
       <c r="R47" s="14">
-        <f>IF([1]punteo!M46="",0,[2]punteo!M46)</f>
-        <v>0</v>
-      </c>
-      <c r="T47">
+        <f>IF([2]punteo!L46="",0,[2]punteo!L46)</f>
+        <v>0</v>
+      </c>
+      <c r="S47" s="14">
+        <f>IF([3]punteo!L46="",0,[3]punteo!L46)</f>
+        <v>0</v>
+      </c>
+      <c r="U47">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U47">
+      <c r="V47">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -3975,22 +4908,26 @@
         <v>80</v>
       </c>
       <c r="R48" s="14">
-        <f>IF([1]punteo!M47="",0,[2]punteo!M47)</f>
-        <v>0</v>
-      </c>
-      <c r="T48">
+        <f>IF([2]punteo!L47="",0,[2]punteo!L47)</f>
+        <v>100</v>
+      </c>
+      <c r="S48" s="14">
+        <f>IF([3]punteo!L47="",0,[3]punteo!L47)</f>
+        <v>100</v>
+      </c>
+      <c r="U48">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U48">
+      <c r="V48">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -4044,22 +4981,26 @@
         <v>0</v>
       </c>
       <c r="R49" s="14">
-        <f>IF([1]punteo!M48="",0,[2]punteo!M48)</f>
-        <v>0</v>
-      </c>
-      <c r="T49">
+        <f>IF([2]punteo!L48="",0,[2]punteo!L48)</f>
+        <v>0</v>
+      </c>
+      <c r="S49" s="14">
+        <f>IF([3]punteo!L48="",0,[3]punteo!L48)</f>
+        <v>0</v>
+      </c>
+      <c r="U49">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U49">
+      <c r="V49">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V49" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W49" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C50">
         <v>44</v>
       </c>
@@ -4107,22 +5048,26 @@
         <v>100</v>
       </c>
       <c r="R50" s="14">
-        <f>IF([1]punteo!M49="",0,[2]punteo!M49)</f>
-        <v>0</v>
-      </c>
-      <c r="T50">
+        <f>IF([2]punteo!L49="",0,[2]punteo!L49)</f>
+        <v>100</v>
+      </c>
+      <c r="S50" s="14">
+        <f>IF([3]punteo!L49="",0,[3]punteo!L49)</f>
+        <v>100</v>
+      </c>
+      <c r="U50">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U50">
+      <c r="V50">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -4176,22 +5121,26 @@
         <v>100</v>
       </c>
       <c r="R51" s="14">
-        <f>IF([1]punteo!M50="",0,[2]punteo!M50)</f>
-        <v>0</v>
-      </c>
-      <c r="T51">
+        <f>IF([2]punteo!L50="",0,[2]punteo!L50)</f>
+        <v>100</v>
+      </c>
+      <c r="S51" s="14">
+        <f>IF([3]punteo!L50="",0,[3]punteo!L50)</f>
+        <v>100</v>
+      </c>
+      <c r="U51">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U51">
+      <c r="V51">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C52">
         <v>46</v>
       </c>
@@ -4239,22 +5188,26 @@
         <v>100</v>
       </c>
       <c r="R52" s="14">
-        <f>IF([1]punteo!M51="",0,[2]punteo!M51)</f>
-        <v>0</v>
-      </c>
-      <c r="T52">
+        <f>IF([2]punteo!L51="",0,[2]punteo!L51)</f>
+        <v>100</v>
+      </c>
+      <c r="S52" s="14">
+        <f>IF([3]punteo!L51="",0,[3]punteo!L51)</f>
+        <v>100</v>
+      </c>
+      <c r="U52">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U52">
+      <c r="V52">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C53">
         <v>47</v>
       </c>
@@ -4299,22 +5252,26 @@
         <v>100</v>
       </c>
       <c r="R53" s="14">
-        <f>IF([1]punteo!M52="",0,[2]punteo!M52)</f>
-        <v>0</v>
-      </c>
-      <c r="T53">
+        <f>IF([2]punteo!L52="",0,[2]punteo!L52)</f>
+        <v>100</v>
+      </c>
+      <c r="S53" s="14">
+        <f>IF([3]punteo!L52="",0,[3]punteo!L52)</f>
+        <v>100</v>
+      </c>
+      <c r="U53">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U53">
+      <c r="V53">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C54">
         <v>48</v>
       </c>
@@ -4362,22 +5319,26 @@
         <v>100</v>
       </c>
       <c r="R54" s="14">
-        <f>IF([1]punteo!M53="",0,[2]punteo!M53)</f>
-        <v>0</v>
-      </c>
-      <c r="T54">
+        <f>IF([2]punteo!L53="",0,[2]punteo!L53)</f>
+        <v>100</v>
+      </c>
+      <c r="S54" s="14">
+        <f>IF([3]punteo!L53="",0,[3]punteo!L53)</f>
+        <v>100</v>
+      </c>
+      <c r="U54">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U54">
+      <c r="V54">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V54" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W54" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C55">
         <v>49</v>
       </c>
@@ -4425,22 +5386,26 @@
         <v>80</v>
       </c>
       <c r="R55" s="14">
-        <f>IF([1]punteo!M54="",0,[2]punteo!M54)</f>
-        <v>0</v>
-      </c>
-      <c r="T55">
+        <f>IF([2]punteo!L54="",0,[2]punteo!L54)</f>
+        <v>100</v>
+      </c>
+      <c r="S55" s="14">
+        <f>IF([3]punteo!L54="",0,[3]punteo!L54)</f>
+        <v>100</v>
+      </c>
+      <c r="U55">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U55">
+      <c r="V55">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C56">
         <v>50</v>
       </c>
@@ -4488,22 +5453,26 @@
         <v>90</v>
       </c>
       <c r="R56" s="14">
-        <f>IF([1]punteo!M55="",0,[2]punteo!M55)</f>
-        <v>0</v>
-      </c>
-      <c r="T56">
+        <f>IF([2]punteo!L55="",0,[2]punteo!L55)</f>
+        <v>100</v>
+      </c>
+      <c r="S56" s="14">
+        <f>IF([3]punteo!L55="",0,[3]punteo!L55)</f>
+        <v>100</v>
+      </c>
+      <c r="U56">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U56">
+      <c r="V56">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C57">
         <v>51</v>
       </c>
@@ -4548,22 +5517,26 @@
         <v>80</v>
       </c>
       <c r="R57" s="14">
-        <f>IF([1]punteo!M56="",0,[2]punteo!M56)</f>
-        <v>0</v>
-      </c>
-      <c r="T57">
+        <f>IF([2]punteo!L56="",0,[2]punteo!L56)</f>
+        <v>100</v>
+      </c>
+      <c r="S57" s="14">
+        <f>IF([3]punteo!L56="",0,[3]punteo!L56)</f>
+        <v>100</v>
+      </c>
+      <c r="U57">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U57">
+      <c r="V57">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C58">
         <v>52</v>
       </c>
@@ -4611,22 +5584,26 @@
         <v>95</v>
       </c>
       <c r="R58" s="14">
-        <f>IF([1]punteo!M57="",0,[2]punteo!M57)</f>
-        <v>0</v>
-      </c>
-      <c r="T58">
+        <f>IF([2]punteo!L57="",0,[2]punteo!L57)</f>
+        <v>0</v>
+      </c>
+      <c r="S58" s="14">
+        <f>IF([3]punteo!L57="",0,[3]punteo!L57)</f>
+        <v>100</v>
+      </c>
+      <c r="U58">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U58">
+      <c r="V58">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -4677,22 +5654,26 @@
         <v>100</v>
       </c>
       <c r="R59" s="14">
-        <f>IF([1]punteo!M58="",0,[2]punteo!M58)</f>
-        <v>0</v>
-      </c>
-      <c r="T59">
+        <f>IF([2]punteo!L58="",0,[2]punteo!L58)</f>
+        <v>100</v>
+      </c>
+      <c r="S59" s="14">
+        <f>IF([3]punteo!L58="",0,[3]punteo!L58)</f>
+        <v>100</v>
+      </c>
+      <c r="U59">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U59">
+      <c r="V59">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -4746,22 +5727,26 @@
         <v>90</v>
       </c>
       <c r="R60" s="14">
-        <f>IF([1]punteo!M59="",0,[2]punteo!M59)</f>
-        <v>0</v>
-      </c>
-      <c r="T60">
+        <f>IF([2]punteo!L59="",0,[2]punteo!L59)</f>
+        <v>100</v>
+      </c>
+      <c r="S60" s="14">
+        <f>IF([3]punteo!L59="",0,[3]punteo!L59)</f>
+        <v>100</v>
+      </c>
+      <c r="U60">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U60">
+      <c r="V60">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -4812,22 +5797,26 @@
         <v>80</v>
       </c>
       <c r="R61" s="14">
-        <f>IF([1]punteo!M60="",0,[2]punteo!M60)</f>
-        <v>0</v>
-      </c>
-      <c r="T61">
+        <f>IF([2]punteo!L60="",0,[2]punteo!L60)</f>
+        <v>0</v>
+      </c>
+      <c r="S61" s="14">
+        <f>IF([3]punteo!L60="",0,[3]punteo!L60)</f>
+        <v>100</v>
+      </c>
+      <c r="U61">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U61">
+      <c r="V61">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C62">
         <v>56</v>
       </c>
@@ -4875,22 +5864,26 @@
         <v>80</v>
       </c>
       <c r="R62" s="14">
-        <f>IF([1]punteo!M61="",0,[2]punteo!M61)</f>
-        <v>0</v>
-      </c>
-      <c r="T62">
+        <f>IF([2]punteo!L61="",0,[2]punteo!L61)</f>
+        <v>100</v>
+      </c>
+      <c r="S62" s="14">
+        <f>IF([3]punteo!L61="",0,[3]punteo!L61)</f>
+        <v>100</v>
+      </c>
+      <c r="U62">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U62">
+      <c r="V62">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C63">
         <v>57</v>
       </c>
@@ -4932,22 +5925,26 @@
         <v>0</v>
       </c>
       <c r="R63" s="14">
-        <f>IF([1]punteo!M62="",0,[2]punteo!M62)</f>
-        <v>0</v>
-      </c>
-      <c r="T63">
+        <f>IF([2]punteo!L62="",0,[2]punteo!L62)</f>
+        <v>0</v>
+      </c>
+      <c r="S63" s="14">
+        <f>IF([3]punteo!L62="",0,[3]punteo!L62)</f>
+        <v>0</v>
+      </c>
+      <c r="U63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U63">
+      <c r="V63">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="W63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C64">
         <v>58</v>
       </c>
@@ -4989,22 +5986,26 @@
         <v>0</v>
       </c>
       <c r="R64" s="14">
-        <f>IF([1]punteo!M63="",0,[2]punteo!M63)</f>
-        <v>0</v>
-      </c>
-      <c r="T64">
+        <f>IF([2]punteo!L63="",0,[2]punteo!L63)</f>
+        <v>0</v>
+      </c>
+      <c r="S64" s="14">
+        <f>IF([3]punteo!L63="",0,[3]punteo!L63)</f>
+        <v>0</v>
+      </c>
+      <c r="U64">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U64">
+      <c r="V64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="W64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C65">
         <v>59</v>
       </c>
@@ -5049,22 +6050,26 @@
         <v>0</v>
       </c>
       <c r="R65" s="14">
-        <f>IF([1]punteo!M64="",0,[2]punteo!M64)</f>
-        <v>0</v>
-      </c>
-      <c r="T65">
+        <f>IF([2]punteo!L64="",0,[2]punteo!L64)</f>
+        <v>0</v>
+      </c>
+      <c r="S65" s="14">
+        <f>IF([3]punteo!L64="",0,[3]punteo!L64)</f>
+        <v>0</v>
+      </c>
+      <c r="U65">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U65">
+      <c r="V65">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V65">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="W65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C66">
         <v>60</v>
       </c>
@@ -5112,22 +6117,26 @@
         <v>95</v>
       </c>
       <c r="R66" s="14">
-        <f>IF([1]punteo!M65="",0,[2]punteo!M65)</f>
-        <v>0</v>
-      </c>
-      <c r="T66">
+        <f>IF([2]punteo!L65="",0,[2]punteo!L65)</f>
+        <v>100</v>
+      </c>
+      <c r="S66" s="14">
+        <f>IF([3]punteo!L65="",0,[3]punteo!L65)</f>
+        <v>100</v>
+      </c>
+      <c r="U66">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U66">
+      <c r="V66">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="W66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -5181,22 +6190,26 @@
         <v>0</v>
       </c>
       <c r="R67" s="14">
-        <f>IF([1]punteo!M66="",0,[2]punteo!M66)</f>
-        <v>0</v>
-      </c>
-      <c r="T67">
+        <f>IF([2]punteo!L66="",0,[2]punteo!L66)</f>
+        <v>0</v>
+      </c>
+      <c r="S67" s="14">
+        <f>IF([3]punteo!L66="",0,[3]punteo!L66)</f>
+        <v>100</v>
+      </c>
+      <c r="U67">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U67">
+      <c r="V67">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="W67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C68">
         <v>62</v>
       </c>
@@ -5244,22 +6257,26 @@
         <v>90</v>
       </c>
       <c r="R68" s="14">
-        <f>IF([1]punteo!M67="",0,[2]punteo!M67)</f>
-        <v>0</v>
-      </c>
-      <c r="T68">
+        <f>IF([2]punteo!L67="",0,[2]punteo!L67)</f>
+        <v>100</v>
+      </c>
+      <c r="S68" s="14">
+        <f>IF([3]punteo!L67="",0,[3]punteo!L67)</f>
+        <v>100</v>
+      </c>
+      <c r="U68">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U68">
+      <c r="V68">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="W68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C69">
         <v>63</v>
       </c>
@@ -5301,22 +6318,26 @@
         <v>0</v>
       </c>
       <c r="R69" s="14">
-        <f>IF([1]punteo!M68="",0,[2]punteo!M68)</f>
-        <v>0</v>
-      </c>
-      <c r="T69">
+        <f>IF([2]punteo!L68="",0,[2]punteo!L68)</f>
+        <v>0</v>
+      </c>
+      <c r="S69" s="14">
+        <f>IF([3]punteo!L68="",0,[3]punteo!L68)</f>
+        <v>0</v>
+      </c>
+      <c r="U69">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U69">
+      <c r="V69">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V69">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="W69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C70">
         <v>64</v>
       </c>
@@ -5364,22 +6385,26 @@
         <v>100</v>
       </c>
       <c r="R70" s="14">
-        <f>IF([1]punteo!M69="",0,[2]punteo!M69)</f>
-        <v>0</v>
-      </c>
-      <c r="T70">
+        <f>IF([2]punteo!L69="",0,[2]punteo!L69)</f>
+        <v>100</v>
+      </c>
+      <c r="S70" s="14">
+        <f>IF([3]punteo!L69="",0,[3]punteo!L69)</f>
+        <v>100</v>
+      </c>
+      <c r="U70">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U70">
+      <c r="V70">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="W70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C71">
         <v>65</v>
       </c>
@@ -5427,22 +6452,26 @@
         <v>80</v>
       </c>
       <c r="R71" s="14">
-        <f>IF([1]punteo!M70="",0,[2]punteo!M70)</f>
-        <v>0</v>
-      </c>
-      <c r="T71">
+        <f>IF([2]punteo!L70="",0,[2]punteo!L70)</f>
+        <v>100</v>
+      </c>
+      <c r="S71" s="14">
+        <f>IF([3]punteo!L70="",0,[3]punteo!L70)</f>
+        <v>100</v>
+      </c>
+      <c r="U71">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U71">
+      <c r="V71">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="V71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="W71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -5496,22 +6525,26 @@
         <v>100</v>
       </c>
       <c r="R72" s="14">
-        <f>IF([1]punteo!M71="",0,[2]punteo!M71)</f>
-        <v>0</v>
-      </c>
-      <c r="T72">
-        <f t="shared" ref="T72:T79" si="2">IF(O72&gt;0,1,0)</f>
-        <v>1</v>
+        <f>IF([2]punteo!L71="",0,[2]punteo!L71)</f>
+        <v>100</v>
+      </c>
+      <c r="S72" s="14">
+        <f>IF([3]punteo!L71="",0,[3]punteo!L71)</f>
+        <v>100</v>
       </c>
       <c r="U72">
-        <f t="shared" ref="U72:U79" si="3">IF(P72&gt;0,1,0)</f>
+        <f t="shared" ref="U72:U79" si="2">IF(O72&gt;0,1,0)</f>
         <v>1</v>
       </c>
       <c r="V72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.35">
+        <f t="shared" ref="V72:V79" si="3">IF(P72&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C73">
         <v>67</v>
       </c>
@@ -5556,22 +6589,26 @@
         <v>0</v>
       </c>
       <c r="R73" s="14">
-        <f>IF([1]punteo!M72="",0,[2]punteo!M72)</f>
-        <v>0</v>
-      </c>
-      <c r="T73">
+        <f>IF([2]punteo!L72="",0,[2]punteo!L72)</f>
+        <v>0</v>
+      </c>
+      <c r="S73" s="14">
+        <f>IF([3]punteo!L72="",0,[3]punteo!L72)</f>
+        <v>0</v>
+      </c>
+      <c r="U73">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U73">
+      <c r="V73">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="V73">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="W73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C74">
         <v>68</v>
       </c>
@@ -5619,22 +6656,26 @@
         <v>95</v>
       </c>
       <c r="R74" s="14">
-        <f>IF([1]punteo!M73="",0,[2]punteo!M73)</f>
-        <v>0</v>
-      </c>
-      <c r="T74">
+        <f>IF([2]punteo!L73="",0,[2]punteo!L73)</f>
+        <v>0</v>
+      </c>
+      <c r="S74" s="14">
+        <f>IF([3]punteo!L73="",0,[3]punteo!L73)</f>
+        <v>100</v>
+      </c>
+      <c r="U74">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="U74">
+      <c r="V74">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="V74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="W74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C75">
         <v>69</v>
       </c>
@@ -5682,22 +6723,26 @@
         <v>0</v>
       </c>
       <c r="R75" s="14">
-        <f>IF([1]punteo!M74="",0,[2]punteo!M74)</f>
-        <v>0</v>
-      </c>
-      <c r="T75">
+        <f>IF([2]punteo!L74="",0,[2]punteo!L74)</f>
+        <v>0</v>
+      </c>
+      <c r="S75" s="14">
+        <f>IF([3]punteo!L74="",0,[3]punteo!L74)</f>
+        <v>0</v>
+      </c>
+      <c r="U75">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="U75">
+      <c r="V75">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="V75">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="W75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>0.27777777777777779</v>
       </c>
@@ -5748,22 +6793,26 @@
         <v>100</v>
       </c>
       <c r="R76" s="14">
-        <f>IF([1]punteo!M75="",0,[2]punteo!M75)</f>
-        <v>0</v>
-      </c>
-      <c r="T76">
+        <f>IF([2]punteo!L75="",0,[2]punteo!L75)</f>
+        <v>100</v>
+      </c>
+      <c r="S76" s="14">
+        <f>IF([3]punteo!L75="",0,[3]punteo!L75)</f>
+        <v>100</v>
+      </c>
+      <c r="U76">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U76">
+      <c r="V76">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="V76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="W76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C77">
         <v>71</v>
       </c>
@@ -5805,22 +6854,26 @@
         <v>0</v>
       </c>
       <c r="R77" s="14">
-        <f>IF([1]punteo!M76="",0,[2]punteo!M76)</f>
-        <v>0</v>
-      </c>
-      <c r="T77">
+        <f>IF([2]punteo!L76="",0,[2]punteo!L76)</f>
+        <v>0</v>
+      </c>
+      <c r="S77" s="14">
+        <f>IF([3]punteo!L76="",0,[3]punteo!L76)</f>
+        <v>0</v>
+      </c>
+      <c r="U77">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U77">
+      <c r="V77">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="W77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B78" s="1" t="s">
         <v>79</v>
       </c>
@@ -5871,22 +6924,26 @@
         <v>100</v>
       </c>
       <c r="R78" s="14">
-        <f>IF([1]punteo!M77="",0,[2]punteo!M77)</f>
-        <v>0</v>
-      </c>
-      <c r="T78">
+        <f>IF([2]punteo!L77="",0,[2]punteo!L77)</f>
+        <v>100</v>
+      </c>
+      <c r="S78" s="14">
+        <f>IF([3]punteo!L77="",0,[3]punteo!L77)</f>
+        <v>100</v>
+      </c>
+      <c r="U78">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="U78">
+      <c r="V78">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="V78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="W78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B79" s="1" t="s">
         <v>79</v>
       </c>
@@ -5934,22 +6991,26 @@
         <v>0</v>
       </c>
       <c r="R79" s="14">
-        <f>IF([1]punteo!M78="",0,[2]punteo!M78)</f>
-        <v>0</v>
-      </c>
-      <c r="T79">
+        <f>IF([2]punteo!L78="",0,[2]punteo!L78)</f>
+        <v>0</v>
+      </c>
+      <c r="S79" s="14">
+        <f>IF([3]punteo!L78="",0,[3]punteo!L78)</f>
+        <v>0</v>
+      </c>
+      <c r="U79">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="U79">
+      <c r="V79">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="W79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C80" s="8" t="s">
         <v>74</v>
       </c>
@@ -5999,19 +7060,30 @@
         <f>COUNTIF(P7:P79,"&gt;0")</f>
         <v>60</v>
       </c>
-      <c r="Q80" s="10"/>
-      <c r="R80" s="10"/>
-      <c r="S80" s="9"/>
+      <c r="Q80" s="11">
+        <f>COUNTIF(Q7:Q79,"&gt;0")</f>
+        <v>47</v>
+      </c>
+      <c r="R80" s="11">
+        <f t="shared" ref="R80:S80" si="5">COUNTIF(R7:R79,"&gt;0")</f>
+        <v>39</v>
+      </c>
+      <c r="S80" s="11">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
       <c r="T80" s="9"/>
       <c r="U80" s="9"/>
       <c r="V80" s="9"/>
-      <c r="W80" s="12"/>
+      <c r="W80" s="9"/>
+      <c r="X80" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="W4:X4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/PRACTICAS DOCENCIA/LABORATORIO MB1/LISTADO COMPLETO MACROS/PUNTEOS FINALES.xlsx
+++ b/PRACTICAS DOCENCIA/LABORATORIO MB1/LISTADO COMPLETO MACROS/PUNTEOS FINALES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ubicacion C a D\Documentos\gitPrimer-Semetre-25\PRACTICAS DOCENCIA\LABORATORIO MB1\LISTADO COMPLETO MACROS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8532BAC-3D76-4041-B713-C47982B27A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B1BF53-31BC-4FEA-AEFB-C35F3C2BEDFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{F4BDE4DC-E94C-4D9E-A851-8F281B73FE4C}"/>
   </bookViews>
@@ -19,7 +19,6 @@
     <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
-    <externalReference r:id="rId5"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="122">
   <si>
     <t>No.</t>
   </si>
@@ -354,9 +353,6 @@
     <t>NOTAS FINALES</t>
   </si>
   <si>
-    <t>Extras (23/10/2025)</t>
-  </si>
-  <si>
     <t>Puntaje asignado por actividad</t>
   </si>
   <si>
@@ -372,32 +368,41 @@
     <t xml:space="preserve">HT4  </t>
   </si>
   <si>
-    <t>HT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HT </t>
-  </si>
-  <si>
     <t xml:space="preserve">TAREA </t>
   </si>
   <si>
-    <t xml:space="preserve">HT  </t>
-  </si>
-  <si>
     <t>PF</t>
   </si>
   <si>
     <t>NTF</t>
   </si>
   <si>
-    <t xml:space="preserve">Extras </t>
+    <t>HT2</t>
+  </si>
+  <si>
+    <t>HT 3</t>
+  </si>
+  <si>
+    <t>HT4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HT5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HT6 </t>
+  </si>
+  <si>
+    <t>HT7</t>
+  </si>
+  <si>
+    <t>HT8</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -423,6 +428,19 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -580,7 +598,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -591,63 +609,82 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="20" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="20" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -868,11 +905,6 @@
             <v>80</v>
           </cell>
         </row>
-        <row r="44">
-          <cell r="L44">
-            <v>0</v>
-          </cell>
-        </row>
         <row r="45">
           <cell r="L45">
             <v>0</v>
@@ -1060,7 +1092,7 @@
       <sheetName val="punteo"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="6">
           <cell r="L6">
@@ -1444,390 +1476,6 @@
       <sheetName val="punteo"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="6">
-          <cell r="L6">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="L7">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="L8">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="L9">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="L10">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="L11">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="L12">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="L13">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="L14">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="L15">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="L16">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="L17">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="L18">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="L19">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="L20">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="L21">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="L22">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="L23">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="L24">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="L25">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="L26">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="L27">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="L28">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="L29">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="L30">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="L31">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="L32">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="L33">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="L34">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="L35">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="L36">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="L37">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="L38">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="L39">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="L40">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="L41">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="L42">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="L43">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="L44">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="L45">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="L46">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="L47">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="L48">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="L49">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="L50">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="L51">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="L52">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="L53">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="L54">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="L55">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="L56">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="L57">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="L58">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="L59">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="L60">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="L61">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="L62">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="L63">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="L64">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="L65">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="L66">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="L67">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="L68">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="L69">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="L70">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="L71">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="L72">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="L73">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="L74">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="L75">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="L76">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="L77">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="L78">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="htfxasint"/>
-      <sheetName val="punteo"/>
-    </sheetNames>
-    <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="6">
@@ -1837,7 +1485,7 @@
         </row>
         <row r="7">
           <cell r="L7">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="8">
@@ -1867,17 +1515,17 @@
         </row>
         <row r="13">
           <cell r="L13">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="14">
           <cell r="L14">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="15">
           <cell r="L15">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="16">
@@ -1892,7 +1540,7 @@
         </row>
         <row r="18">
           <cell r="L18">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="19">
@@ -1907,7 +1555,7 @@
         </row>
         <row r="21">
           <cell r="L21">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="22">
@@ -1917,7 +1565,7 @@
         </row>
         <row r="23">
           <cell r="L23">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="24">
@@ -1927,17 +1575,17 @@
         </row>
         <row r="25">
           <cell r="L25">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="26">
           <cell r="L26">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="27">
           <cell r="L27">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="28">
@@ -1952,7 +1600,7 @@
         </row>
         <row r="30">
           <cell r="L30">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="31">
@@ -1967,27 +1615,27 @@
         </row>
         <row r="33">
           <cell r="L33">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="34">
           <cell r="L34">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="35">
           <cell r="L35">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="36">
           <cell r="L36">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="37">
           <cell r="L37">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="38">
@@ -1997,12 +1645,12 @@
         </row>
         <row r="39">
           <cell r="L39">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="40">
           <cell r="L40">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="41">
@@ -2017,12 +1665,12 @@
         </row>
         <row r="43">
           <cell r="L43">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="44">
           <cell r="L44">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="45">
@@ -2037,27 +1685,27 @@
         </row>
         <row r="47">
           <cell r="L47">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="48">
           <cell r="L48">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="49">
           <cell r="L49">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="50">
           <cell r="L50">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="51">
           <cell r="L51">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="52">
@@ -2067,22 +1715,22 @@
         </row>
         <row r="53">
           <cell r="L53">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="54">
           <cell r="L54">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="55">
           <cell r="L55">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="56">
           <cell r="L56">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="57">
@@ -2092,17 +1740,17 @@
         </row>
         <row r="58">
           <cell r="L58">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="59">
           <cell r="L59">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="60">
           <cell r="L60">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="61">
@@ -2122,22 +1770,22 @@
         </row>
         <row r="64">
           <cell r="L64">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="65">
           <cell r="L65">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="66">
           <cell r="L66">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="67">
           <cell r="L67">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="68">
@@ -2147,17 +1795,17 @@
         </row>
         <row r="69">
           <cell r="L69">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="70">
           <cell r="L70">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="71">
           <cell r="L71">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="72">
@@ -2177,7 +1825,7 @@
         </row>
         <row r="75">
           <cell r="L75">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="76">
@@ -2187,7 +1835,7 @@
         </row>
         <row r="77">
           <cell r="L77">
-            <v>0</v>
+            <v>100</v>
           </cell>
         </row>
         <row r="78">
@@ -2499,7 +2147,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9337005-F0FF-4A3F-B098-783C2B519B7D}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:Z78"/>
+  <dimension ref="A1:Y78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="29.26953125" style="1" customWidth="1"/>
@@ -2507,3104 +2155,3008 @@
     <col min="4" max="4" width="12.6328125" customWidth="1"/>
     <col min="5" max="5" width="33.90625" customWidth="1"/>
     <col min="6" max="9" width="7.453125" customWidth="1"/>
-    <col min="10" max="21" width="9.6328125" customWidth="1"/>
-    <col min="22" max="22" width="27.26953125" customWidth="1"/>
-    <col min="23" max="24" width="31.81640625" customWidth="1"/>
-    <col min="25" max="25" width="22.81640625" customWidth="1"/>
-    <col min="26" max="26" width="18.54296875" customWidth="1"/>
+    <col min="10" max="11" width="9.6328125" style="13" customWidth="1"/>
+    <col min="12" max="13" width="9.6328125" customWidth="1"/>
+    <col min="14" max="14" width="9.6328125" style="13" customWidth="1"/>
+    <col min="15" max="15" width="9.6328125" customWidth="1"/>
+    <col min="16" max="17" width="9.6328125" style="13" customWidth="1"/>
+    <col min="18" max="20" width="9.6328125" customWidth="1"/>
+    <col min="21" max="21" width="27.26953125" customWidth="1"/>
+    <col min="22" max="23" width="31.81640625" customWidth="1"/>
+    <col min="24" max="24" width="22.81640625" customWidth="1"/>
+    <col min="25" max="25" width="18.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="3:26" ht="101" x14ac:dyDescent="0.35">
-      <c r="C2" s="11"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="17" t="s">
+    <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="1:25" ht="109" x14ac:dyDescent="0.35">
+      <c r="A2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="M2" s="18" t="s">
+      <c r="M2" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="N2" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="O2" s="18" t="s">
+      <c r="N2" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="O2" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="P2" s="18" t="s">
+      <c r="P2" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="Q2" s="18" t="s">
+      <c r="Q2" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="R2" s="18" t="s">
+      <c r="R2" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="S2" s="18" t="s">
+      <c r="S2" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="19" t="s">
+      <c r="T2" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="U2" s="20" t="s">
-        <v>107</v>
+      <c r="V2" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="W2" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="X2" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y2" s="15" t="s">
+      <c r="X2" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="Z2" s="15"/>
+      <c r="Y2" s="11"/>
     </row>
-    <row r="3" spans="3:26" x14ac:dyDescent="0.35">
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="F3" s="23">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A3" s="15"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F3" s="27">
         <v>0.5</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="28">
         <v>0.5</v>
       </c>
-      <c r="H3" s="24">
+      <c r="H3" s="28">
         <v>0.5</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="29">
         <v>0.5</v>
       </c>
-      <c r="J3" s="23">
-        <v>1</v>
-      </c>
-      <c r="K3" s="24">
-        <v>1</v>
-      </c>
-      <c r="L3" s="24">
-        <v>1</v>
-      </c>
-      <c r="M3" s="24">
+      <c r="J3" s="30">
+        <v>1</v>
+      </c>
+      <c r="K3" s="31">
+        <v>1</v>
+      </c>
+      <c r="L3" s="28">
+        <v>1</v>
+      </c>
+      <c r="M3" s="28">
         <v>1.5</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="31">
         <v>2</v>
       </c>
-      <c r="O3" s="24">
+      <c r="O3" s="28">
         <v>2</v>
       </c>
-      <c r="P3" s="24">
+      <c r="P3" s="31">
         <v>2</v>
       </c>
-      <c r="Q3" s="24">
-        <v>1</v>
-      </c>
-      <c r="R3" s="24">
+      <c r="Q3" s="31">
+        <v>1</v>
+      </c>
+      <c r="R3" s="28">
         <v>1.5</v>
       </c>
-      <c r="S3" s="24">
+      <c r="S3" s="28">
         <v>5</v>
       </c>
-      <c r="T3" s="25">
+      <c r="T3" s="29">
         <f>SUM(F3:S3)</f>
         <v>20</v>
       </c>
-      <c r="U3" s="26">
-        <v>1</v>
+      <c r="V3" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="W3" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y3" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="X3" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y3" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="Z3" s="4" t="s">
-        <v>77</v>
-      </c>
     </row>
-    <row r="4" spans="3:26" x14ac:dyDescent="0.35">
-      <c r="C4" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="8" t="s">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A4" s="15"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="F4" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="G4" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="H4" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="H4" s="28" t="s">
+      <c r="I4" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="J4" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="K4" s="36" t="s">
+        <v>115</v>
+      </c>
+      <c r="L4" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="M4" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="N4" s="36" t="s">
         <v>112</v>
       </c>
-      <c r="J4" s="27" t="s">
+      <c r="O4" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="P4" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="R4" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="S4" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="K4" s="28" t="s">
-        <v>113</v>
-      </c>
-      <c r="L4" s="28" t="s">
+      <c r="T4" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="M4" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="N4" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="O4" s="28" t="s">
-        <v>116</v>
-      </c>
-      <c r="P4" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q4" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="R4" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="S4" s="28" t="s">
-        <v>117</v>
-      </c>
-      <c r="T4" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="U4" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="V4" s="4"/>
-      <c r="W4" s="7">
+      <c r="U4" s="4"/>
+      <c r="V4" s="6">
         <v>45911</v>
       </c>
-      <c r="X4" s="4" t="s">
+      <c r="W4" s="4" t="s">
         <v>90</v>
       </c>
+      <c r="X4" s="2">
+        <v>45930</v>
+      </c>
       <c r="Y4" s="2">
-        <v>45930</v>
-      </c>
-      <c r="Z4" s="2">
         <v>45902</v>
       </c>
     </row>
-    <row r="5" spans="3:26" x14ac:dyDescent="0.35">
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A5" s="15"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="15">
+        <v>1</v>
+      </c>
+      <c r="D5" s="15">
         <v>202030174</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
+      <c r="F5" s="15">
+        <v>0</v>
+      </c>
+      <c r="G5" s="15">
+        <v>0</v>
+      </c>
+      <c r="H5" s="15">
         <v>50</v>
       </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>100</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
+      <c r="I5" s="15">
+        <v>0</v>
+      </c>
+      <c r="J5" s="37">
+        <v>0</v>
+      </c>
+      <c r="K5" s="37">
+        <v>0</v>
+      </c>
+      <c r="L5" s="15">
+        <v>0</v>
+      </c>
+      <c r="M5" s="15">
+        <v>100</v>
+      </c>
+      <c r="N5" s="37">
+        <v>0</v>
+      </c>
+      <c r="O5" s="15">
+        <v>0</v>
+      </c>
+      <c r="P5" s="37">
         <v>100</v>
       </c>
       <c r="Q5" s="14">
         <f>IF([1]punteo!L6="",0,[1]punteo!L6)</f>
         <v>0</v>
       </c>
-      <c r="R5" s="14">
+      <c r="R5" s="10">
         <f>IF([2]punteo!L6="",0,[2]punteo!L6)</f>
         <v>0</v>
       </c>
-      <c r="S5" s="14">
+      <c r="S5" s="10">
         <f>IF([3]punteo!L6="",0,[3]punteo!L6)</f>
         <v>0</v>
       </c>
-      <c r="T5" s="14"/>
-      <c r="U5" s="14">
-        <f>IF([4]punteo!L6="",0,[4]punteo!L6)</f>
-        <v>0</v>
-      </c>
-      <c r="V5" s="14"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5">
+        <f>IF(O5&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
       <c r="W5">
-        <f>IF(O5&gt;0,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="X5">
         <f>IF(P5&gt;0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="Y5" s="3">
+      <c r="X5" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="3:26" x14ac:dyDescent="0.35">
-      <c r="C6">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A6" s="15"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="15">
         <v>2</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="15">
         <v>202032032</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F6">
-        <v>100</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
+      <c r="F6" s="15">
+        <v>100</v>
+      </c>
+      <c r="G6" s="15">
+        <v>0</v>
+      </c>
+      <c r="H6" s="15">
         <v>50</v>
       </c>
-      <c r="I6">
-        <v>100</v>
-      </c>
-      <c r="J6">
-        <v>100</v>
-      </c>
-      <c r="K6">
-        <v>100</v>
-      </c>
-      <c r="L6">
-        <v>100</v>
-      </c>
-      <c r="M6">
-        <v>100</v>
-      </c>
-      <c r="N6">
+      <c r="I6" s="15">
+        <v>100</v>
+      </c>
+      <c r="J6" s="37">
+        <v>100</v>
+      </c>
+      <c r="K6" s="37">
+        <v>100</v>
+      </c>
+      <c r="L6" s="15">
+        <v>100</v>
+      </c>
+      <c r="M6" s="15">
+        <v>100</v>
+      </c>
+      <c r="N6" s="37">
         <v>80</v>
       </c>
-      <c r="O6">
-        <v>100</v>
-      </c>
-      <c r="P6">
+      <c r="O6" s="15">
+        <v>100</v>
+      </c>
+      <c r="P6" s="37">
         <v>100</v>
       </c>
       <c r="Q6" s="14">
         <f>IF([1]punteo!L7="",0,[1]punteo!L7)</f>
         <v>100</v>
       </c>
-      <c r="R6" s="14">
+      <c r="R6" s="10">
         <f>IF([2]punteo!L7="",0,[2]punteo!L7)</f>
         <v>100</v>
       </c>
-      <c r="S6" s="14">
+      <c r="S6" s="10">
         <f>IF([3]punteo!L7="",0,[3]punteo!L7)</f>
         <v>100</v>
       </c>
-      <c r="T6" s="14"/>
-      <c r="U6" s="14">
-        <f>IF([4]punteo!L7="",0,[4]punteo!L7)</f>
-        <v>0</v>
-      </c>
-      <c r="V6" s="14"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="10"/>
+      <c r="V6">
+        <f t="shared" ref="V6:V69" si="0">IF(O6&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
       <c r="W6">
-        <f t="shared" ref="W6:W69" si="0">IF(O6&gt;0,1,0)</f>
+        <f t="shared" ref="W6:W69" si="1">IF(P6&gt;0,1,0)</f>
         <v>1</v>
       </c>
       <c r="X6">
-        <f t="shared" ref="X6:X69" si="1">IF(P6&gt;0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="Y6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="3:26" x14ac:dyDescent="0.35">
-      <c r="C7">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A7" s="15"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="15">
         <v>3</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="15">
         <v>202231116</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="F7">
-        <v>100</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>100</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
+      <c r="F7" s="15">
+        <v>100</v>
+      </c>
+      <c r="G7" s="15">
+        <v>0</v>
+      </c>
+      <c r="H7" s="15">
+        <v>100</v>
+      </c>
+      <c r="I7" s="15">
+        <v>0</v>
+      </c>
+      <c r="J7" s="37">
         <v>85</v>
       </c>
-      <c r="K7">
-        <v>100</v>
-      </c>
-      <c r="L7">
-        <v>100</v>
-      </c>
-      <c r="M7">
-        <v>100</v>
-      </c>
-      <c r="N7">
+      <c r="K7" s="37">
+        <v>100</v>
+      </c>
+      <c r="L7" s="15">
+        <v>100</v>
+      </c>
+      <c r="M7" s="15">
+        <v>100</v>
+      </c>
+      <c r="N7" s="37">
         <v>70</v>
       </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
+      <c r="O7" s="15">
+        <v>0</v>
+      </c>
+      <c r="P7" s="37">
         <v>85</v>
       </c>
       <c r="Q7" s="14">
         <f>IF([1]punteo!L8="",0,[1]punteo!L8)</f>
         <v>80</v>
       </c>
-      <c r="R7" s="14">
+      <c r="R7" s="10">
         <f>IF([2]punteo!L8="",0,[2]punteo!L8)</f>
         <v>0</v>
       </c>
-      <c r="S7" s="14">
+      <c r="S7" s="10">
         <f>IF([3]punteo!L8="",0,[3]punteo!L8)</f>
         <v>100</v>
       </c>
-      <c r="T7" s="14"/>
-      <c r="U7" s="14">
-        <f>IF([4]punteo!L8="",0,[4]punteo!L8)</f>
-        <v>100</v>
-      </c>
-      <c r="V7" s="14"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
+      <c r="V7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W7">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="X7">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="3:26" x14ac:dyDescent="0.35">
-      <c r="C8">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A8" s="15"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="15">
         <v>4</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="15">
         <v>202330276</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
+      <c r="F8" s="15">
+        <v>0</v>
+      </c>
+      <c r="G8" s="15">
+        <v>0</v>
+      </c>
+      <c r="H8" s="15">
+        <v>0</v>
+      </c>
+      <c r="I8" s="15">
+        <v>0</v>
+      </c>
+      <c r="J8" s="37">
+        <v>0</v>
+      </c>
+      <c r="K8" s="37">
+        <v>0</v>
+      </c>
+      <c r="L8" s="15">
+        <v>0</v>
+      </c>
+      <c r="M8" s="15">
+        <v>0</v>
+      </c>
+      <c r="N8" s="37">
+        <v>0</v>
+      </c>
+      <c r="O8" s="15">
+        <v>0</v>
+      </c>
+      <c r="P8" s="37">
         <v>0</v>
       </c>
       <c r="Q8" s="14">
         <f>IF([1]punteo!L9="",0,[1]punteo!L9)</f>
         <v>0</v>
       </c>
-      <c r="R8" s="14">
+      <c r="R8" s="10">
         <f>IF([2]punteo!L9="",0,[2]punteo!L9)</f>
         <v>0</v>
       </c>
-      <c r="S8" s="14">
+      <c r="S8" s="10">
         <f>IF([3]punteo!L9="",0,[3]punteo!L9)</f>
         <v>0</v>
       </c>
-      <c r="T8" s="14"/>
-      <c r="U8" s="14">
-        <f>IF([4]punteo!L9="",0,[4]punteo!L9)</f>
-        <v>0</v>
-      </c>
-      <c r="V8" s="14"/>
+      <c r="T8" s="10"/>
+      <c r="U8" s="10"/>
+      <c r="V8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="3:26" x14ac:dyDescent="0.35">
-      <c r="C9">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A9" s="15"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="15">
         <v>5</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="15">
         <v>202331587</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>100</v>
-      </c>
-      <c r="I9">
+      <c r="F9" s="15">
+        <v>0</v>
+      </c>
+      <c r="G9" s="15">
+        <v>0</v>
+      </c>
+      <c r="H9" s="15">
+        <v>100</v>
+      </c>
+      <c r="I9" s="15">
         <v>90</v>
       </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
+      <c r="J9" s="37">
+        <v>0</v>
+      </c>
+      <c r="K9" s="37">
         <v>50</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="15">
         <v>90</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="15">
         <v>80</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="37">
         <v>75</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="15">
         <v>85</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="37">
         <v>0</v>
       </c>
       <c r="Q9" s="14">
         <f>IF([1]punteo!L10="",0,[1]punteo!L10)</f>
         <v>100</v>
       </c>
-      <c r="R9" s="14">
+      <c r="R9" s="10">
         <f>IF([2]punteo!L10="",0,[2]punteo!L10)</f>
         <v>100</v>
       </c>
-      <c r="S9" s="14">
+      <c r="S9" s="10">
         <f>IF([3]punteo!L10="",0,[3]punteo!L10)</f>
         <v>100</v>
       </c>
-      <c r="T9" s="14"/>
-      <c r="U9" s="14">
-        <f>IF([4]punteo!L10="",0,[4]punteo!L10)</f>
-        <v>100</v>
-      </c>
-      <c r="V9" s="14"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
+      <c r="V9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W9">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="X9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="3:26" x14ac:dyDescent="0.35">
-      <c r="C10">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A10" s="15"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="15">
         <v>6</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="15">
         <v>202332049</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
+      <c r="F10" s="15">
+        <v>0</v>
+      </c>
+      <c r="G10" s="15">
+        <v>0</v>
+      </c>
+      <c r="H10" s="15">
+        <v>0</v>
+      </c>
+      <c r="I10" s="15">
+        <v>0</v>
+      </c>
+      <c r="J10" s="37">
+        <v>0</v>
+      </c>
+      <c r="K10" s="37">
+        <v>0</v>
+      </c>
+      <c r="L10" s="15">
+        <v>0</v>
+      </c>
+      <c r="M10" s="15">
+        <v>0</v>
+      </c>
+      <c r="N10" s="37">
+        <v>0</v>
+      </c>
+      <c r="O10" s="15">
+        <v>0</v>
+      </c>
+      <c r="P10" s="37">
         <v>0</v>
       </c>
       <c r="Q10" s="14">
         <f>IF([1]punteo!L11="",0,[1]punteo!L11)</f>
         <v>0</v>
       </c>
-      <c r="R10" s="14">
+      <c r="R10" s="10">
         <f>IF([2]punteo!L11="",0,[2]punteo!L11)</f>
         <v>0</v>
       </c>
-      <c r="S10" s="14">
+      <c r="S10" s="10">
         <f>IF([3]punteo!L11="",0,[3]punteo!L11)</f>
         <v>0</v>
       </c>
-      <c r="T10" s="14"/>
-      <c r="U10" s="14">
-        <f>IF([4]punteo!L11="",0,[4]punteo!L11)</f>
-        <v>0</v>
-      </c>
-      <c r="V10" s="14"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+      <c r="V10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="3:26" x14ac:dyDescent="0.35">
-      <c r="C11">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A11" s="15"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="15">
         <v>7</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="15">
         <v>202402553</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="F11">
-        <v>100</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>100</v>
-      </c>
-      <c r="I11">
+      <c r="F11" s="15">
+        <v>100</v>
+      </c>
+      <c r="G11" s="15">
+        <v>0</v>
+      </c>
+      <c r="H11" s="15">
+        <v>100</v>
+      </c>
+      <c r="I11" s="15">
         <v>90</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="37">
         <v>60</v>
       </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>100</v>
-      </c>
-      <c r="M11">
-        <v>100</v>
-      </c>
-      <c r="N11">
+      <c r="K11" s="37">
+        <v>0</v>
+      </c>
+      <c r="L11" s="15">
+        <v>100</v>
+      </c>
+      <c r="M11" s="15">
+        <v>100</v>
+      </c>
+      <c r="N11" s="37">
         <v>50</v>
       </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
+      <c r="O11" s="15">
+        <v>0</v>
+      </c>
+      <c r="P11" s="37">
         <v>65</v>
       </c>
       <c r="Q11" s="14">
         <f>IF([1]punteo!L12="",0,[1]punteo!L12)</f>
         <v>80</v>
       </c>
-      <c r="R11" s="14">
+      <c r="R11" s="10">
         <f>IF([2]punteo!L12="",0,[2]punteo!L12)</f>
         <v>100</v>
       </c>
-      <c r="S11" s="14">
+      <c r="S11" s="10">
         <f>IF([3]punteo!L12="",0,[3]punteo!L12)</f>
         <v>0</v>
       </c>
-      <c r="T11" s="14"/>
-      <c r="U11" s="14">
-        <f>IF([4]punteo!L12="",0,[4]punteo!L12)</f>
-        <v>0</v>
-      </c>
-      <c r="V11" s="14"/>
+      <c r="T11" s="10"/>
+      <c r="U11" s="10"/>
+      <c r="V11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W11">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="X11">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="3:26" x14ac:dyDescent="0.35">
-      <c r="C12">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A12" s="15"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="15">
         <v>8</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="15">
         <v>202430271</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>100</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>100</v>
-      </c>
-      <c r="K12">
-        <v>100</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
+      <c r="F12" s="15">
+        <v>0</v>
+      </c>
+      <c r="G12" s="15">
+        <v>100</v>
+      </c>
+      <c r="H12" s="15">
+        <v>0</v>
+      </c>
+      <c r="I12" s="15">
+        <v>0</v>
+      </c>
+      <c r="J12" s="37">
+        <v>100</v>
+      </c>
+      <c r="K12" s="37">
+        <v>100</v>
+      </c>
+      <c r="L12" s="15">
+        <v>0</v>
+      </c>
+      <c r="M12" s="15">
+        <v>0</v>
+      </c>
+      <c r="N12" s="37">
+        <v>0</v>
+      </c>
+      <c r="O12" s="15">
+        <v>0</v>
+      </c>
+      <c r="P12" s="37">
         <v>70</v>
       </c>
       <c r="Q12" s="14">
         <f>IF([1]punteo!L13="",0,[1]punteo!L13)</f>
         <v>80</v>
       </c>
-      <c r="R12" s="14">
+      <c r="R12" s="10">
         <f>IF([2]punteo!L13="",0,[2]punteo!L13)</f>
         <v>0</v>
       </c>
-      <c r="S12" s="14">
+      <c r="S12" s="10">
         <f>IF([3]punteo!L13="",0,[3]punteo!L13)</f>
         <v>100</v>
       </c>
-      <c r="T12" s="14"/>
-      <c r="U12" s="14">
-        <f>IF([4]punteo!L13="",0,[4]punteo!L13)</f>
-        <v>0</v>
-      </c>
-      <c r="V12" s="14"/>
+      <c r="T12" s="10"/>
+      <c r="U12" s="10"/>
+      <c r="V12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W12">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="X12">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y12">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="3:26" x14ac:dyDescent="0.35">
-      <c r="C13">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A13" s="15"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="15">
         <v>9</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="15">
         <v>202430532</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="F13">
-        <v>100</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>100</v>
-      </c>
-      <c r="I13">
-        <v>100</v>
-      </c>
-      <c r="J13">
-        <v>100</v>
-      </c>
-      <c r="K13">
-        <v>100</v>
-      </c>
-      <c r="L13">
-        <v>100</v>
-      </c>
-      <c r="M13">
-        <v>100</v>
-      </c>
-      <c r="N13">
-        <v>100</v>
-      </c>
-      <c r="O13">
+      <c r="F13" s="15">
+        <v>100</v>
+      </c>
+      <c r="G13" s="15">
+        <v>0</v>
+      </c>
+      <c r="H13" s="15">
+        <v>100</v>
+      </c>
+      <c r="I13" s="15">
+        <v>100</v>
+      </c>
+      <c r="J13" s="37">
+        <v>100</v>
+      </c>
+      <c r="K13" s="37">
+        <v>100</v>
+      </c>
+      <c r="L13" s="15">
+        <v>100</v>
+      </c>
+      <c r="M13" s="15">
+        <v>100</v>
+      </c>
+      <c r="N13" s="37">
+        <v>100</v>
+      </c>
+      <c r="O13" s="15">
         <v>65</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="37">
         <v>80</v>
       </c>
       <c r="Q13" s="14">
         <f>IF([1]punteo!L14="",0,[1]punteo!L14)</f>
         <v>100</v>
       </c>
-      <c r="R13" s="14">
+      <c r="R13" s="10">
         <f>IF([2]punteo!L14="",0,[2]punteo!L14)</f>
         <v>100</v>
       </c>
-      <c r="S13" s="14">
+      <c r="S13" s="10">
         <f>IF([3]punteo!L14="",0,[3]punteo!L14)</f>
         <v>100</v>
       </c>
-      <c r="T13" s="14"/>
-      <c r="U13" s="14">
-        <f>IF([4]punteo!L14="",0,[4]punteo!L14)</f>
-        <v>0</v>
-      </c>
-      <c r="V13" s="14"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
+      <c r="V13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X13">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="3:26" x14ac:dyDescent="0.35">
-      <c r="C14">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A14" s="15"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="15">
         <v>10</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="15">
         <v>202430589</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>100</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>100</v>
-      </c>
-      <c r="M14">
+      <c r="F14" s="15">
+        <v>0</v>
+      </c>
+      <c r="G14" s="15">
+        <v>0</v>
+      </c>
+      <c r="H14" s="15">
+        <v>0</v>
+      </c>
+      <c r="I14" s="15">
+        <v>100</v>
+      </c>
+      <c r="J14" s="37">
+        <v>75</v>
+      </c>
+      <c r="K14" s="37">
+        <v>90</v>
+      </c>
+      <c r="L14" s="15">
+        <v>100</v>
+      </c>
+      <c r="M14" s="15">
         <v>80</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="37">
         <v>70</v>
       </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
+      <c r="O14" s="15">
+        <v>0</v>
+      </c>
+      <c r="P14" s="37">
         <v>0</v>
       </c>
       <c r="Q14" s="14">
         <f>IF([1]punteo!L15="",0,[1]punteo!L15)</f>
         <v>0</v>
       </c>
-      <c r="R14" s="14">
+      <c r="R14" s="10">
         <f>IF([2]punteo!L15="",0,[2]punteo!L15)</f>
         <v>0</v>
       </c>
-      <c r="S14" s="14">
+      <c r="S14" s="10">
         <f>IF([3]punteo!L15="",0,[3]punteo!L15)</f>
         <v>100</v>
       </c>
-      <c r="T14" s="14"/>
-      <c r="U14" s="14">
-        <f>IF([4]punteo!L15="",0,[4]punteo!L15)</f>
-        <v>0</v>
-      </c>
-      <c r="V14" s="14"/>
+      <c r="T14" s="10"/>
+      <c r="U14" s="10"/>
+      <c r="V14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="3:26" x14ac:dyDescent="0.35">
-      <c r="C15">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A15" s="15"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="15">
         <v>11</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="15">
         <v>202430602</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>100</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
+      <c r="F15" s="15">
+        <v>0</v>
+      </c>
+      <c r="G15" s="15">
+        <v>0</v>
+      </c>
+      <c r="H15" s="15">
+        <v>100</v>
+      </c>
+      <c r="I15" s="15">
+        <v>0</v>
+      </c>
+      <c r="J15" s="37">
         <v>60</v>
       </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
+      <c r="K15" s="37">
+        <v>0</v>
+      </c>
+      <c r="L15" s="15">
         <v>90</v>
       </c>
-      <c r="M15">
-        <v>100</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
+      <c r="M15" s="15">
+        <v>100</v>
+      </c>
+      <c r="N15" s="37">
+        <v>0</v>
+      </c>
+      <c r="O15" s="15">
+        <v>0</v>
+      </c>
+      <c r="P15" s="37">
         <v>30</v>
       </c>
       <c r="Q15" s="14">
         <f>IF([1]punteo!L16="",0,[1]punteo!L16)</f>
         <v>0</v>
       </c>
-      <c r="R15" s="14">
+      <c r="R15" s="10">
         <f>IF([2]punteo!L16="",0,[2]punteo!L16)</f>
         <v>0</v>
       </c>
-      <c r="S15" s="14">
+      <c r="S15" s="10">
         <f>IF([3]punteo!L16="",0,[3]punteo!L16)</f>
         <v>0</v>
       </c>
-      <c r="T15" s="14"/>
-      <c r="U15" s="14">
-        <f>IF([4]punteo!L16="",0,[4]punteo!L16)</f>
-        <v>0</v>
-      </c>
-      <c r="V15" s="14"/>
+      <c r="T15" s="10"/>
+      <c r="U15" s="10"/>
+      <c r="V15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W15">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="X15">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y15">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="3:26" x14ac:dyDescent="0.35">
-      <c r="C16">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A16" s="15"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="15">
         <v>12</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="15">
         <v>202430633</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F16">
-        <v>100</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>100</v>
-      </c>
-      <c r="I16">
-        <v>100</v>
-      </c>
-      <c r="J16">
-        <v>100</v>
-      </c>
-      <c r="K16">
-        <v>100</v>
-      </c>
-      <c r="L16">
-        <v>100</v>
-      </c>
-      <c r="M16">
-        <v>100</v>
-      </c>
-      <c r="N16">
+      <c r="F16" s="15">
+        <v>100</v>
+      </c>
+      <c r="G16" s="15">
+        <v>0</v>
+      </c>
+      <c r="H16" s="15">
+        <v>100</v>
+      </c>
+      <c r="I16" s="15">
+        <v>100</v>
+      </c>
+      <c r="J16" s="37">
+        <v>100</v>
+      </c>
+      <c r="K16" s="37">
+        <v>100</v>
+      </c>
+      <c r="L16" s="15">
+        <v>100</v>
+      </c>
+      <c r="M16" s="15">
+        <v>100</v>
+      </c>
+      <c r="N16" s="37">
         <v>50</v>
       </c>
-      <c r="O16">
-        <v>100</v>
-      </c>
-      <c r="P16">
+      <c r="O16" s="15">
+        <v>100</v>
+      </c>
+      <c r="P16" s="37">
         <v>50</v>
       </c>
       <c r="Q16" s="14">
         <f>IF([1]punteo!L17="",0,[1]punteo!L17)</f>
         <v>0</v>
       </c>
-      <c r="R16" s="14">
+      <c r="R16" s="10">
         <f>IF([2]punteo!L17="",0,[2]punteo!L17)</f>
         <v>0</v>
       </c>
-      <c r="S16" s="14">
+      <c r="S16" s="10">
         <f>IF([3]punteo!L17="",0,[3]punteo!L17)</f>
         <v>100</v>
       </c>
-      <c r="T16" s="14"/>
-      <c r="U16" s="14">
-        <f>IF([4]punteo!L17="",0,[4]punteo!L17)</f>
-        <v>100</v>
-      </c>
-      <c r="V16" s="14"/>
+      <c r="T16" s="10"/>
+      <c r="U16" s="10"/>
+      <c r="V16">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X16">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y16">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A17" s="6">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A17" s="38">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="15">
         <v>13</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="15">
         <v>202430645</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F17">
-        <v>100</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
+      <c r="F17" s="15">
+        <v>100</v>
+      </c>
+      <c r="G17" s="15">
+        <v>0</v>
+      </c>
+      <c r="H17" s="15">
         <v>50</v>
       </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>100</v>
-      </c>
-      <c r="K17">
+      <c r="I17" s="15">
+        <v>90</v>
+      </c>
+      <c r="J17" s="37">
+        <v>100</v>
+      </c>
+      <c r="K17" s="37">
         <v>85</v>
       </c>
-      <c r="L17">
-        <v>100</v>
-      </c>
-      <c r="M17">
-        <v>100</v>
-      </c>
-      <c r="N17">
+      <c r="L17" s="15">
+        <v>100</v>
+      </c>
+      <c r="M17" s="15">
+        <v>100</v>
+      </c>
+      <c r="N17" s="37">
         <v>70</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="15">
         <v>75</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="37">
         <v>70</v>
       </c>
       <c r="Q17" s="14">
         <f>IF([1]punteo!L18="",0,[1]punteo!L18)</f>
         <v>100</v>
       </c>
-      <c r="R17" s="14">
+      <c r="R17" s="10">
         <f>IF([2]punteo!L18="",0,[2]punteo!L18)</f>
         <v>100</v>
       </c>
-      <c r="S17" s="14">
+      <c r="S17" s="10">
         <f>IF([3]punteo!L18="",0,[3]punteo!L18)</f>
         <v>100</v>
       </c>
-      <c r="T17" s="14"/>
-      <c r="U17" s="14">
-        <f>IF([4]punteo!L18="",0,[4]punteo!L18)</f>
-        <v>0</v>
-      </c>
-      <c r="V17" s="14"/>
+      <c r="T17" s="10"/>
+      <c r="U17" s="10"/>
+      <c r="V17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X17">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y17">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C18">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A18" s="15"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="15">
         <v>14</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="15">
         <v>202430733</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F18">
-        <v>100</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
+      <c r="F18" s="15">
+        <v>100</v>
+      </c>
+      <c r="G18" s="15">
+        <v>0</v>
+      </c>
+      <c r="H18" s="15">
         <v>50</v>
       </c>
-      <c r="I18">
-        <v>100</v>
-      </c>
-      <c r="J18">
+      <c r="I18" s="15">
+        <v>100</v>
+      </c>
+      <c r="J18" s="37">
         <v>85</v>
       </c>
-      <c r="K18">
-        <v>100</v>
-      </c>
-      <c r="L18">
-        <v>100</v>
-      </c>
-      <c r="M18">
-        <v>100</v>
-      </c>
-      <c r="N18">
+      <c r="K18" s="37">
+        <v>100</v>
+      </c>
+      <c r="L18" s="15">
+        <v>100</v>
+      </c>
+      <c r="M18" s="15">
+        <v>100</v>
+      </c>
+      <c r="N18" s="37">
         <v>50</v>
       </c>
-      <c r="O18">
-        <v>100</v>
-      </c>
-      <c r="P18">
+      <c r="O18" s="15">
+        <v>100</v>
+      </c>
+      <c r="P18" s="37">
         <v>100</v>
       </c>
       <c r="Q18" s="14">
         <f>IF([1]punteo!L19="",0,[1]punteo!L19)</f>
         <v>100</v>
       </c>
-      <c r="R18" s="14">
+      <c r="R18" s="10">
         <f>IF([2]punteo!L19="",0,[2]punteo!L19)</f>
         <v>100</v>
       </c>
-      <c r="S18" s="14">
+      <c r="S18" s="10">
         <f>IF([3]punteo!L19="",0,[3]punteo!L19)</f>
         <v>100</v>
       </c>
-      <c r="T18" s="14"/>
-      <c r="U18" s="14">
-        <f>IF([4]punteo!L19="",0,[4]punteo!L19)</f>
-        <v>100</v>
-      </c>
-      <c r="V18" s="14"/>
+      <c r="T18" s="10"/>
+      <c r="U18" s="10"/>
+      <c r="V18">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X18">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C19">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A19" s="15"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="15">
         <v>15</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="15">
         <v>202430804</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F19">
-        <v>100</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>100</v>
-      </c>
-      <c r="K19">
-        <v>100</v>
-      </c>
-      <c r="L19">
-        <v>100</v>
-      </c>
-      <c r="M19">
-        <v>100</v>
-      </c>
-      <c r="N19">
+      <c r="F19" s="15">
+        <v>100</v>
+      </c>
+      <c r="G19" s="15">
+        <v>0</v>
+      </c>
+      <c r="H19" s="15">
+        <v>0</v>
+      </c>
+      <c r="I19" s="15">
+        <v>0</v>
+      </c>
+      <c r="J19" s="37">
+        <v>100</v>
+      </c>
+      <c r="K19" s="37">
+        <v>100</v>
+      </c>
+      <c r="L19" s="15">
+        <v>100</v>
+      </c>
+      <c r="M19" s="15">
+        <v>100</v>
+      </c>
+      <c r="N19" s="37">
         <v>80</v>
       </c>
-      <c r="O19">
-        <v>100</v>
-      </c>
-      <c r="P19">
+      <c r="O19" s="15">
+        <v>100</v>
+      </c>
+      <c r="P19" s="37">
         <v>100</v>
       </c>
       <c r="Q19" s="14">
         <f>IF([1]punteo!L20="",0,[1]punteo!L20)</f>
         <v>0</v>
       </c>
-      <c r="R19" s="14">
+      <c r="R19" s="10">
         <f>IF([2]punteo!L20="",0,[2]punteo!L20)</f>
         <v>0</v>
       </c>
-      <c r="S19" s="14">
+      <c r="S19" s="10">
         <f>IF([3]punteo!L20="",0,[3]punteo!L20)</f>
         <v>0</v>
       </c>
-      <c r="T19" s="14"/>
-      <c r="U19" s="14">
-        <f>IF([4]punteo!L20="",0,[4]punteo!L20)</f>
-        <v>0</v>
-      </c>
-      <c r="V19" s="14"/>
+      <c r="T19" s="10"/>
+      <c r="U19" s="10"/>
+      <c r="V19">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X19">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y19">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A20" s="6" t="s">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A20" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="15">
         <v>16</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="15">
         <v>202430829</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="F20">
-        <v>100</v>
-      </c>
-      <c r="G20">
-        <v>100</v>
-      </c>
-      <c r="H20">
-        <v>100</v>
-      </c>
-      <c r="I20">
+      <c r="F20" s="15">
+        <v>100</v>
+      </c>
+      <c r="G20" s="15">
+        <v>100</v>
+      </c>
+      <c r="H20" s="15">
+        <v>100</v>
+      </c>
+      <c r="I20" s="15">
         <v>90</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="37">
         <v>85</v>
       </c>
-      <c r="K20">
-        <v>100</v>
-      </c>
-      <c r="L20">
-        <v>100</v>
-      </c>
-      <c r="M20">
-        <v>100</v>
-      </c>
-      <c r="N20">
+      <c r="K20" s="37">
+        <v>100</v>
+      </c>
+      <c r="L20" s="15">
+        <v>100</v>
+      </c>
+      <c r="M20" s="15">
+        <v>100</v>
+      </c>
+      <c r="N20" s="37">
         <v>70</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="15">
         <v>85</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="37">
         <v>85</v>
       </c>
       <c r="Q20" s="14">
         <f>IF([1]punteo!L21="",0,[1]punteo!L21)</f>
         <v>80</v>
       </c>
-      <c r="R20" s="14">
+      <c r="R20" s="10">
         <f>IF([2]punteo!L21="",0,[2]punteo!L21)</f>
         <v>100</v>
       </c>
-      <c r="S20" s="14">
+      <c r="S20" s="10">
         <f>IF([3]punteo!L21="",0,[3]punteo!L21)</f>
         <v>100</v>
       </c>
-      <c r="T20" s="14"/>
-      <c r="U20" s="14">
-        <f>IF([4]punteo!L21="",0,[4]punteo!L21)</f>
-        <v>0</v>
-      </c>
-      <c r="V20" s="14"/>
+      <c r="T20" s="10"/>
+      <c r="U20" s="10"/>
+      <c r="V20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X20">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C21">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A21" s="15"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="15">
         <v>17</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="15">
         <v>202431169</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="F21">
-        <v>100</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
+      <c r="F21" s="15">
+        <v>100</v>
+      </c>
+      <c r="G21" s="15">
+        <v>0</v>
+      </c>
+      <c r="H21" s="15">
         <v>50</v>
       </c>
-      <c r="I21">
-        <v>100</v>
-      </c>
-      <c r="J21">
+      <c r="I21" s="15">
+        <v>100</v>
+      </c>
+      <c r="J21" s="37">
         <v>85</v>
       </c>
-      <c r="K21">
-        <v>100</v>
-      </c>
-      <c r="L21">
-        <v>100</v>
-      </c>
-      <c r="M21">
-        <v>100</v>
-      </c>
-      <c r="N21">
+      <c r="K21" s="37">
+        <v>100</v>
+      </c>
+      <c r="L21" s="15">
+        <v>100</v>
+      </c>
+      <c r="M21" s="15">
+        <v>100</v>
+      </c>
+      <c r="N21" s="37">
         <v>50</v>
       </c>
-      <c r="O21">
-        <v>100</v>
-      </c>
-      <c r="P21">
+      <c r="O21" s="15">
+        <v>100</v>
+      </c>
+      <c r="P21" s="37">
         <v>100</v>
       </c>
       <c r="Q21" s="14">
         <f>IF([1]punteo!L22="",0,[1]punteo!L22)</f>
         <v>100</v>
       </c>
-      <c r="R21" s="14">
+      <c r="R21" s="10">
         <f>IF([2]punteo!L22="",0,[2]punteo!L22)</f>
         <v>100</v>
       </c>
-      <c r="S21" s="14">
+      <c r="S21" s="10">
         <f>IF([3]punteo!L22="",0,[3]punteo!L22)</f>
         <v>100</v>
       </c>
-      <c r="T21" s="14"/>
-      <c r="U21" s="14">
-        <f>IF([4]punteo!L22="",0,[4]punteo!L22)</f>
-        <v>100</v>
-      </c>
-      <c r="V21" s="14"/>
+      <c r="T21" s="10"/>
+      <c r="U21" s="10"/>
+      <c r="V21">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X21">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A22" s="6">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A22" s="38">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="15">
         <v>18</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="15">
         <v>202431502</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="F22">
-        <v>100</v>
-      </c>
-      <c r="G22">
-        <v>100</v>
-      </c>
-      <c r="H22">
-        <v>100</v>
-      </c>
-      <c r="I22">
-        <v>100</v>
-      </c>
-      <c r="J22">
-        <v>100</v>
-      </c>
-      <c r="K22">
-        <v>100</v>
-      </c>
-      <c r="L22">
-        <v>100</v>
-      </c>
-      <c r="M22">
-        <v>100</v>
-      </c>
-      <c r="N22">
+      <c r="F22" s="15">
+        <v>100</v>
+      </c>
+      <c r="G22" s="15">
+        <v>100</v>
+      </c>
+      <c r="H22" s="15">
+        <v>100</v>
+      </c>
+      <c r="I22" s="15">
+        <v>100</v>
+      </c>
+      <c r="J22" s="37">
+        <v>100</v>
+      </c>
+      <c r="K22" s="37">
+        <v>100</v>
+      </c>
+      <c r="L22" s="15">
+        <v>100</v>
+      </c>
+      <c r="M22" s="15">
+        <v>100</v>
+      </c>
+      <c r="N22" s="37">
         <v>50</v>
       </c>
-      <c r="O22">
+      <c r="O22" s="15">
         <v>90</v>
       </c>
-      <c r="P22">
+      <c r="P22" s="37">
         <v>45</v>
       </c>
       <c r="Q22" s="14">
         <f>IF([1]punteo!L23="",0,[1]punteo!L23)</f>
         <v>80</v>
       </c>
-      <c r="R22" s="14">
+      <c r="R22" s="10">
         <f>IF([2]punteo!L23="",0,[2]punteo!L23)</f>
         <v>100</v>
       </c>
-      <c r="S22" s="14">
+      <c r="S22" s="10">
         <f>IF([3]punteo!L23="",0,[3]punteo!L23)</f>
         <v>100</v>
       </c>
-      <c r="T22" s="14"/>
-      <c r="U22" s="14">
-        <f>IF([4]punteo!L23="",0,[4]punteo!L23)</f>
-        <v>0</v>
-      </c>
-      <c r="V22" s="14"/>
+      <c r="T22" s="10"/>
+      <c r="U22" s="10"/>
+      <c r="V22">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X22">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y22">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="B23" s="13"/>
-      <c r="C23">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A23" s="15"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="15">
         <v>19</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="15">
         <v>202431726</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="F23">
-        <v>100</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>100</v>
-      </c>
-      <c r="I23">
-        <v>100</v>
-      </c>
-      <c r="J23">
+      <c r="F23" s="15">
+        <v>100</v>
+      </c>
+      <c r="G23" s="15">
+        <v>0</v>
+      </c>
+      <c r="H23" s="15">
+        <v>100</v>
+      </c>
+      <c r="I23" s="15">
+        <v>100</v>
+      </c>
+      <c r="J23" s="37">
         <v>75</v>
       </c>
-      <c r="K23">
-        <v>100</v>
-      </c>
-      <c r="L23">
-        <v>100</v>
-      </c>
-      <c r="M23">
-        <v>100</v>
-      </c>
-      <c r="N23">
+      <c r="K23" s="37">
+        <v>100</v>
+      </c>
+      <c r="L23" s="15">
+        <v>100</v>
+      </c>
+      <c r="M23" s="15">
+        <v>100</v>
+      </c>
+      <c r="N23" s="37">
         <v>90</v>
       </c>
-      <c r="O23">
+      <c r="O23" s="15">
         <v>95</v>
       </c>
-      <c r="P23">
+      <c r="P23" s="37">
         <v>90</v>
       </c>
       <c r="Q23" s="14">
         <f>IF([1]punteo!L24="",0,[1]punteo!L24)</f>
         <v>0</v>
       </c>
-      <c r="R23" s="14">
+      <c r="R23" s="10">
         <f>IF([2]punteo!L24="",0,[2]punteo!L24)</f>
         <v>0</v>
       </c>
-      <c r="S23" s="14">
+      <c r="S23" s="10">
         <f>IF([3]punteo!L24="",0,[3]punteo!L24)</f>
         <v>0</v>
       </c>
-      <c r="T23" s="14"/>
-      <c r="U23" s="14">
-        <f>IF([4]punteo!L24="",0,[4]punteo!L24)</f>
-        <v>0</v>
-      </c>
-      <c r="V23" s="14"/>
+      <c r="T23" s="10"/>
+      <c r="U23" s="10"/>
+      <c r="V23">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X23">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y23">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A24" s="15"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="15">
         <v>20</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="15">
         <v>202431817</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>100</v>
-      </c>
-      <c r="I24">
-        <v>100</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>100</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24">
+      <c r="F24" s="15">
+        <v>0</v>
+      </c>
+      <c r="G24" s="15">
+        <v>0</v>
+      </c>
+      <c r="H24" s="15">
+        <v>100</v>
+      </c>
+      <c r="I24" s="15">
+        <v>100</v>
+      </c>
+      <c r="J24" s="37">
+        <v>0</v>
+      </c>
+      <c r="K24" s="37">
+        <v>0</v>
+      </c>
+      <c r="L24" s="15">
+        <v>100</v>
+      </c>
+      <c r="M24" s="15">
+        <v>0</v>
+      </c>
+      <c r="N24" s="37">
+        <v>0</v>
+      </c>
+      <c r="O24" s="15">
         <v>15</v>
       </c>
-      <c r="P24">
+      <c r="P24" s="37">
         <v>90</v>
       </c>
       <c r="Q24" s="14">
         <f>IF([1]punteo!L25="",0,[1]punteo!L25)</f>
         <v>100</v>
       </c>
-      <c r="R24" s="14">
+      <c r="R24" s="10">
         <f>IF([2]punteo!L25="",0,[2]punteo!L25)</f>
         <v>0</v>
       </c>
-      <c r="S24" s="14">
+      <c r="S24" s="10">
         <f>IF([3]punteo!L25="",0,[3]punteo!L25)</f>
         <v>100</v>
       </c>
-      <c r="T24" s="14"/>
-      <c r="U24" s="14">
-        <f>IF([4]punteo!L25="",0,[4]punteo!L25)</f>
-        <v>0</v>
-      </c>
-      <c r="V24" s="14"/>
+      <c r="T24" s="10"/>
+      <c r="U24" s="10"/>
+      <c r="V24">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X24">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y24">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A25" s="15"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="15">
         <v>21</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="15">
         <v>202431819</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25">
-        <v>100</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>100</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>100</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
+      <c r="F25" s="15">
+        <v>0</v>
+      </c>
+      <c r="G25" s="15">
+        <v>100</v>
+      </c>
+      <c r="H25" s="15">
+        <v>0</v>
+      </c>
+      <c r="I25" s="15">
+        <v>0</v>
+      </c>
+      <c r="J25" s="37">
+        <v>0</v>
+      </c>
+      <c r="K25" s="37">
+        <v>100</v>
+      </c>
+      <c r="L25" s="15">
+        <v>0</v>
+      </c>
+      <c r="M25" s="15">
+        <v>100</v>
+      </c>
+      <c r="N25" s="37">
+        <v>0</v>
+      </c>
+      <c r="O25" s="15">
         <v>85</v>
       </c>
-      <c r="P25">
+      <c r="P25" s="37">
         <v>70</v>
       </c>
       <c r="Q25" s="14">
         <f>IF([1]punteo!L26="",0,[1]punteo!L26)</f>
         <v>80</v>
       </c>
-      <c r="R25" s="14">
+      <c r="R25" s="10">
         <f>IF([2]punteo!L26="",0,[2]punteo!L26)</f>
         <v>100</v>
       </c>
-      <c r="S25" s="14">
+      <c r="S25" s="10">
         <f>IF([3]punteo!L26="",0,[3]punteo!L26)</f>
         <v>100</v>
       </c>
-      <c r="T25" s="14"/>
-      <c r="U25" s="14">
-        <f>IF([4]punteo!L26="",0,[4]punteo!L26)</f>
-        <v>0</v>
-      </c>
-      <c r="V25" s="14"/>
+      <c r="T25" s="10"/>
+      <c r="U25" s="10"/>
+      <c r="V25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W25">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="X25">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="Y25" s="3">
+      <c r="X25" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A26" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="15">
         <v>22</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="15">
         <v>202431863</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F26">
-        <v>100</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>100</v>
-      </c>
-      <c r="J26">
+      <c r="F26" s="15">
+        <v>100</v>
+      </c>
+      <c r="G26" s="15">
+        <v>0</v>
+      </c>
+      <c r="H26" s="15">
+        <v>0</v>
+      </c>
+      <c r="I26" s="15">
+        <v>100</v>
+      </c>
+      <c r="J26" s="37">
         <v>50</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="37">
         <v>50</v>
       </c>
-      <c r="L26">
+      <c r="L26" s="15">
         <v>50</v>
       </c>
-      <c r="M26">
-        <v>100</v>
-      </c>
-      <c r="N26">
+      <c r="M26" s="15">
+        <v>100</v>
+      </c>
+      <c r="N26" s="37">
         <v>25</v>
       </c>
-      <c r="O26">
+      <c r="O26" s="15">
         <v>25</v>
       </c>
-      <c r="P26">
+      <c r="P26" s="37">
         <v>100</v>
       </c>
       <c r="Q26" s="14">
         <f>IF([1]punteo!L27="",0,[1]punteo!L27)</f>
         <v>80</v>
       </c>
-      <c r="R26" s="14">
+      <c r="R26" s="10">
         <f>IF([2]punteo!L27="",0,[2]punteo!L27)</f>
         <v>0</v>
       </c>
-      <c r="S26" s="14">
+      <c r="S26" s="10">
         <f>IF([3]punteo!L27="",0,[3]punteo!L27)</f>
         <v>100</v>
       </c>
-      <c r="T26" s="14"/>
-      <c r="U26" s="14">
-        <f>IF([4]punteo!L27="",0,[4]punteo!L27)</f>
-        <v>0</v>
-      </c>
-      <c r="V26" s="14"/>
+      <c r="T26" s="10"/>
+      <c r="U26" s="10"/>
+      <c r="V26">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X26">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y26">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C27">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A27" s="15"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="15">
         <v>23</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="15">
         <v>202432080</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="F27">
-        <v>100</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>100</v>
-      </c>
-      <c r="L27">
-        <v>100</v>
-      </c>
-      <c r="M27">
-        <v>100</v>
-      </c>
-      <c r="N27">
+      <c r="F27" s="15">
+        <v>100</v>
+      </c>
+      <c r="G27" s="15">
+        <v>0</v>
+      </c>
+      <c r="H27" s="15">
+        <v>0</v>
+      </c>
+      <c r="I27" s="15">
+        <v>0</v>
+      </c>
+      <c r="J27" s="37">
+        <v>0</v>
+      </c>
+      <c r="K27" s="37">
+        <v>100</v>
+      </c>
+      <c r="L27" s="15">
+        <v>100</v>
+      </c>
+      <c r="M27" s="15">
+        <v>100</v>
+      </c>
+      <c r="N27" s="37">
         <v>70</v>
       </c>
-      <c r="O27">
-        <v>100</v>
-      </c>
-      <c r="P27">
+      <c r="O27" s="15">
+        <v>100</v>
+      </c>
+      <c r="P27" s="37">
         <v>100</v>
       </c>
       <c r="Q27" s="14">
         <f>IF([1]punteo!L28="",0,[1]punteo!L28)</f>
         <v>0</v>
       </c>
-      <c r="R27" s="14">
+      <c r="R27" s="10">
         <f>IF([2]punteo!L28="",0,[2]punteo!L28)</f>
         <v>0</v>
       </c>
-      <c r="S27" s="14">
+      <c r="S27" s="10">
         <f>IF([3]punteo!L28="",0,[3]punteo!L28)</f>
         <v>0</v>
       </c>
-      <c r="T27" s="14"/>
-      <c r="U27" s="14">
-        <f>IF([4]punteo!L28="",0,[4]punteo!L28)</f>
-        <v>0</v>
-      </c>
-      <c r="V27" s="14"/>
+      <c r="T27" s="10"/>
+      <c r="U27" s="10"/>
+      <c r="V27">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X27">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y27">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C28">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A28" s="15"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="15">
         <v>24</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="15">
         <v>202432085</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="F28">
-        <v>100</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>100</v>
-      </c>
-      <c r="I28">
-        <v>100</v>
-      </c>
-      <c r="J28">
+      <c r="F28" s="15">
+        <v>100</v>
+      </c>
+      <c r="G28" s="15">
+        <v>0</v>
+      </c>
+      <c r="H28" s="15">
+        <v>100</v>
+      </c>
+      <c r="I28" s="15">
+        <v>100</v>
+      </c>
+      <c r="J28" s="37">
         <v>75</v>
       </c>
-      <c r="K28">
-        <v>100</v>
-      </c>
-      <c r="L28">
+      <c r="K28" s="37">
+        <v>100</v>
+      </c>
+      <c r="L28" s="15">
         <v>90</v>
       </c>
-      <c r="M28">
-        <v>100</v>
-      </c>
-      <c r="N28">
+      <c r="M28" s="15">
+        <v>100</v>
+      </c>
+      <c r="N28" s="37">
         <v>70</v>
       </c>
-      <c r="O28">
+      <c r="O28" s="15">
         <v>95</v>
       </c>
-      <c r="P28">
+      <c r="P28" s="37">
         <v>90</v>
       </c>
       <c r="Q28" s="14">
         <f>IF([1]punteo!L29="",0,[1]punteo!L29)</f>
         <v>0</v>
       </c>
-      <c r="R28" s="14">
+      <c r="R28" s="10">
         <f>IF([2]punteo!L29="",0,[2]punteo!L29)</f>
         <v>0</v>
       </c>
-      <c r="S28" s="14">
+      <c r="S28" s="10">
         <f>IF([3]punteo!L29="",0,[3]punteo!L29)</f>
         <v>0</v>
       </c>
-      <c r="T28" s="14"/>
-      <c r="U28" s="14">
-        <f>IF([4]punteo!L29="",0,[4]punteo!L29)</f>
-        <v>0</v>
-      </c>
-      <c r="V28" s="14"/>
+      <c r="T28" s="10"/>
+      <c r="U28" s="10"/>
+      <c r="V28">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W28">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="X28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="Y28" s="3">
+      <c r="X28" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A29" s="6" t="s">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A29" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="15">
         <v>25</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="15">
         <v>202432137</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="F29">
-        <v>100</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>100</v>
-      </c>
-      <c r="J29">
+      <c r="F29" s="15">
+        <v>100</v>
+      </c>
+      <c r="G29" s="15">
+        <v>0</v>
+      </c>
+      <c r="H29" s="15">
+        <v>0</v>
+      </c>
+      <c r="I29" s="15">
+        <v>100</v>
+      </c>
+      <c r="J29" s="37">
         <v>50</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="37">
         <v>50</v>
       </c>
-      <c r="L29">
+      <c r="L29" s="15">
         <v>50</v>
       </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
-      <c r="N29">
+      <c r="M29" s="15">
+        <v>0</v>
+      </c>
+      <c r="N29" s="37">
         <v>25</v>
       </c>
-      <c r="O29">
+      <c r="O29" s="15">
         <v>25</v>
       </c>
-      <c r="P29">
+      <c r="P29" s="37">
         <v>100</v>
       </c>
       <c r="Q29" s="14">
         <f>IF([1]punteo!L30="",0,[1]punteo!L30)</f>
         <v>80</v>
       </c>
-      <c r="R29" s="14">
+      <c r="R29" s="10">
         <f>IF([2]punteo!L30="",0,[2]punteo!L30)</f>
         <v>0</v>
       </c>
-      <c r="S29" s="14">
+      <c r="S29" s="10">
         <f>IF([3]punteo!L30="",0,[3]punteo!L30)</f>
         <v>100</v>
       </c>
-      <c r="T29" s="14"/>
-      <c r="U29" s="14">
-        <f>IF([4]punteo!L30="",0,[4]punteo!L30)</f>
-        <v>0</v>
-      </c>
-      <c r="V29" s="14"/>
+      <c r="T29" s="10"/>
+      <c r="U29" s="10"/>
+      <c r="V29">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X29">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y29">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C30">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A30" s="15"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="15">
         <v>26</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="15">
         <v>202530125</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>100</v>
-      </c>
-      <c r="I30">
-        <v>100</v>
-      </c>
-      <c r="J30">
-        <v>100</v>
-      </c>
-      <c r="K30">
+      <c r="F30" s="15">
+        <v>0</v>
+      </c>
+      <c r="G30" s="15">
+        <v>0</v>
+      </c>
+      <c r="H30" s="15">
+        <v>100</v>
+      </c>
+      <c r="I30" s="15">
+        <v>100</v>
+      </c>
+      <c r="J30" s="37">
+        <v>100</v>
+      </c>
+      <c r="K30" s="37">
         <v>75</v>
       </c>
-      <c r="L30">
+      <c r="L30" s="15">
         <v>90</v>
       </c>
-      <c r="M30">
-        <v>100</v>
-      </c>
-      <c r="N30">
+      <c r="M30" s="15">
+        <v>100</v>
+      </c>
+      <c r="N30" s="37">
         <v>80</v>
       </c>
-      <c r="O30">
+      <c r="O30" s="15">
         <v>90</v>
       </c>
-      <c r="P30">
+      <c r="P30" s="37">
         <v>60</v>
       </c>
       <c r="Q30" s="14">
         <f>IF([1]punteo!L31="",0,[1]punteo!L31)</f>
         <v>0</v>
       </c>
-      <c r="R30" s="14">
+      <c r="R30" s="10">
         <f>IF([2]punteo!L31="",0,[2]punteo!L31)</f>
         <v>0</v>
       </c>
-      <c r="S30" s="14">
+      <c r="S30" s="10">
         <f>IF([3]punteo!L31="",0,[3]punteo!L31)</f>
         <v>0</v>
       </c>
-      <c r="T30" s="14"/>
-      <c r="U30" s="14">
-        <f>IF([4]punteo!L31="",0,[4]punteo!L31)</f>
-        <v>0</v>
-      </c>
-      <c r="V30" s="14"/>
+      <c r="T30" s="10"/>
+      <c r="U30" s="10"/>
+      <c r="V30">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W30">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="X30">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="Y30" s="3">
+      <c r="X30" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A31" s="6" t="s">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A31" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="15">
         <v>27</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="15">
         <v>202530235</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F31">
-        <v>100</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>100</v>
-      </c>
-      <c r="I31">
-        <v>100</v>
-      </c>
-      <c r="J31">
-        <v>100</v>
-      </c>
-      <c r="K31">
-        <v>100</v>
-      </c>
-      <c r="L31">
-        <v>100</v>
-      </c>
-      <c r="M31">
-        <v>100</v>
-      </c>
-      <c r="N31">
-        <v>100</v>
-      </c>
-      <c r="O31">
-        <v>0</v>
-      </c>
-      <c r="P31">
+      <c r="F31" s="15">
+        <v>100</v>
+      </c>
+      <c r="G31" s="15">
+        <v>0</v>
+      </c>
+      <c r="H31" s="15">
+        <v>100</v>
+      </c>
+      <c r="I31" s="15">
+        <v>100</v>
+      </c>
+      <c r="J31" s="37">
+        <v>100</v>
+      </c>
+      <c r="K31" s="37">
+        <v>100</v>
+      </c>
+      <c r="L31" s="15">
+        <v>100</v>
+      </c>
+      <c r="M31" s="15">
+        <v>100</v>
+      </c>
+      <c r="N31" s="37">
+        <v>100</v>
+      </c>
+      <c r="O31" s="15">
+        <v>0</v>
+      </c>
+      <c r="P31" s="37">
         <v>100</v>
       </c>
       <c r="Q31" s="14">
         <f>IF([1]punteo!L32="",0,[1]punteo!L32)</f>
         <v>80</v>
       </c>
-      <c r="R31" s="14">
+      <c r="R31" s="10">
         <f>IF([2]punteo!L32="",0,[2]punteo!L32)</f>
         <v>100</v>
       </c>
-      <c r="S31" s="14">
+      <c r="S31" s="10">
         <f>IF([3]punteo!L32="",0,[3]punteo!L32)</f>
         <v>100</v>
       </c>
-      <c r="T31" s="14"/>
-      <c r="U31" s="14">
-        <f>IF([4]punteo!L32="",0,[4]punteo!L32)</f>
-        <v>100</v>
-      </c>
-      <c r="V31" s="14"/>
+      <c r="T31" s="10"/>
+      <c r="U31" s="10"/>
+      <c r="V31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W31">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="X31">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y31">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A32" s="6">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A32" s="38">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="15">
         <v>28</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="15">
         <v>202530265</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F32">
-        <v>100</v>
-      </c>
-      <c r="G32">
-        <v>100</v>
-      </c>
-      <c r="H32">
-        <v>100</v>
-      </c>
-      <c r="I32">
-        <v>100</v>
-      </c>
-      <c r="J32">
-        <v>100</v>
-      </c>
-      <c r="K32">
+      <c r="F32" s="15">
+        <v>100</v>
+      </c>
+      <c r="G32" s="15">
+        <v>100</v>
+      </c>
+      <c r="H32" s="15">
+        <v>100</v>
+      </c>
+      <c r="I32" s="15">
+        <v>100</v>
+      </c>
+      <c r="J32" s="37">
+        <v>100</v>
+      </c>
+      <c r="K32" s="37">
         <v>90</v>
       </c>
-      <c r="L32">
-        <v>100</v>
-      </c>
-      <c r="M32">
-        <v>100</v>
-      </c>
-      <c r="N32">
+      <c r="L32" s="15">
+        <v>100</v>
+      </c>
+      <c r="M32" s="15">
+        <v>100</v>
+      </c>
+      <c r="N32" s="37">
         <v>70</v>
       </c>
-      <c r="O32">
-        <v>100</v>
-      </c>
-      <c r="P32">
+      <c r="O32" s="15">
+        <v>100</v>
+      </c>
+      <c r="P32" s="37">
         <v>100</v>
       </c>
       <c r="Q32" s="14">
         <f>IF([1]punteo!L33="",0,[1]punteo!L33)</f>
         <v>90</v>
       </c>
-      <c r="R32" s="14">
+      <c r="R32" s="10">
         <f>IF([2]punteo!L33="",0,[2]punteo!L33)</f>
         <v>100</v>
       </c>
-      <c r="S32" s="14">
+      <c r="S32" s="10">
         <f>IF([3]punteo!L33="",0,[3]punteo!L33)</f>
         <v>100</v>
       </c>
-      <c r="T32" s="14"/>
-      <c r="U32" s="14">
-        <f>IF([4]punteo!L33="",0,[4]punteo!L33)</f>
-        <v>0</v>
-      </c>
-      <c r="V32" s="14"/>
+      <c r="T32" s="10"/>
+      <c r="U32" s="10"/>
+      <c r="V32">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W32">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X32">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y32">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C33">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A33" s="15"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="15">
         <v>29</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="15">
         <v>202530315</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F33">
-        <v>100</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>100</v>
-      </c>
-      <c r="I33">
-        <v>100</v>
-      </c>
-      <c r="J33">
-        <v>100</v>
-      </c>
-      <c r="K33">
-        <v>100</v>
-      </c>
-      <c r="L33">
-        <v>100</v>
-      </c>
-      <c r="M33">
-        <v>100</v>
-      </c>
-      <c r="N33">
+      <c r="F33" s="15">
+        <v>100</v>
+      </c>
+      <c r="G33" s="15">
+        <v>0</v>
+      </c>
+      <c r="H33" s="15">
+        <v>100</v>
+      </c>
+      <c r="I33" s="15">
+        <v>100</v>
+      </c>
+      <c r="J33" s="37">
+        <v>100</v>
+      </c>
+      <c r="K33" s="37">
+        <v>100</v>
+      </c>
+      <c r="L33" s="15">
+        <v>100</v>
+      </c>
+      <c r="M33" s="15">
+        <v>100</v>
+      </c>
+      <c r="N33" s="37">
         <v>50</v>
       </c>
-      <c r="O33">
-        <v>100</v>
-      </c>
-      <c r="P33">
+      <c r="O33" s="15">
+        <v>100</v>
+      </c>
+      <c r="P33" s="37">
         <v>50</v>
       </c>
       <c r="Q33" s="14">
         <f>IF([1]punteo!L34="",0,[1]punteo!L34)</f>
         <v>80</v>
       </c>
-      <c r="R33" s="14">
+      <c r="R33" s="10">
         <f>IF([2]punteo!L34="",0,[2]punteo!L34)</f>
         <v>100</v>
       </c>
-      <c r="S33" s="14">
+      <c r="S33" s="10">
         <f>IF([3]punteo!L34="",0,[3]punteo!L34)</f>
         <v>100</v>
       </c>
-      <c r="T33" s="14"/>
-      <c r="U33" s="14">
-        <f>IF([4]punteo!L34="",0,[4]punteo!L34)</f>
-        <v>0</v>
-      </c>
-      <c r="V33" s="14"/>
+      <c r="T33" s="10"/>
+      <c r="U33" s="10"/>
+      <c r="V33">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X33">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y33">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C34">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A34" s="15"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="15">
         <v>30</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="15">
         <v>202530329</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="F34">
-        <v>100</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>100</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>100</v>
-      </c>
-      <c r="K34">
+      <c r="F34" s="15">
+        <v>100</v>
+      </c>
+      <c r="G34" s="15">
+        <v>0</v>
+      </c>
+      <c r="H34" s="15">
+        <v>100</v>
+      </c>
+      <c r="I34" s="15">
+        <v>0</v>
+      </c>
+      <c r="J34" s="37">
+        <v>100</v>
+      </c>
+      <c r="K34" s="37">
         <v>95</v>
       </c>
-      <c r="L34">
-        <v>100</v>
-      </c>
-      <c r="M34">
-        <v>100</v>
-      </c>
-      <c r="N34">
+      <c r="L34" s="15">
+        <v>100</v>
+      </c>
+      <c r="M34" s="15">
+        <v>100</v>
+      </c>
+      <c r="N34" s="37">
         <v>70</v>
       </c>
-      <c r="O34">
+      <c r="O34" s="15">
         <v>85</v>
       </c>
-      <c r="P34">
+      <c r="P34" s="37">
         <v>65</v>
       </c>
       <c r="Q34" s="14">
         <f>IF([1]punteo!L35="",0,[1]punteo!L35)</f>
         <v>80</v>
       </c>
-      <c r="R34" s="14">
+      <c r="R34" s="10">
         <f>IF([2]punteo!L35="",0,[2]punteo!L35)</f>
         <v>100</v>
       </c>
-      <c r="S34" s="14">
+      <c r="S34" s="10">
         <f>IF([3]punteo!L35="",0,[3]punteo!L35)</f>
         <v>100</v>
       </c>
-      <c r="T34" s="14"/>
-      <c r="U34" s="14">
-        <f>IF([4]punteo!L35="",0,[4]punteo!L35)</f>
-        <v>0</v>
-      </c>
-      <c r="V34" s="14"/>
+      <c r="T34" s="10"/>
+      <c r="U34" s="10"/>
+      <c r="V34">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X34">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y34">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A35" s="6">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A35" s="38">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="15">
         <v>31</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="15">
         <v>202530349</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>100</v>
-      </c>
-      <c r="I35">
-        <v>100</v>
-      </c>
-      <c r="J35">
-        <v>100</v>
-      </c>
-      <c r="K35">
+      <c r="F35" s="15">
+        <v>0</v>
+      </c>
+      <c r="G35" s="15">
+        <v>0</v>
+      </c>
+      <c r="H35" s="15">
+        <v>100</v>
+      </c>
+      <c r="I35" s="15">
+        <v>100</v>
+      </c>
+      <c r="J35" s="37">
+        <v>100</v>
+      </c>
+      <c r="K35" s="37">
         <v>75</v>
       </c>
-      <c r="L35">
-        <v>100</v>
-      </c>
-      <c r="M35">
-        <v>100</v>
-      </c>
-      <c r="N35">
+      <c r="L35" s="15">
+        <v>100</v>
+      </c>
+      <c r="M35" s="15">
+        <v>100</v>
+      </c>
+      <c r="N35" s="37">
         <v>80</v>
       </c>
-      <c r="O35">
+      <c r="O35" s="15">
         <v>90</v>
       </c>
-      <c r="P35">
+      <c r="P35" s="37">
         <v>60</v>
       </c>
       <c r="Q35" s="14">
         <f>IF([1]punteo!L36="",0,[1]punteo!L36)</f>
         <v>100</v>
       </c>
-      <c r="R35" s="14">
+      <c r="R35" s="10">
         <f>IF([2]punteo!L36="",0,[2]punteo!L36)</f>
         <v>100</v>
       </c>
-      <c r="S35" s="14">
+      <c r="S35" s="10">
         <f>IF([3]punteo!L36="",0,[3]punteo!L36)</f>
         <v>100</v>
       </c>
-      <c r="T35" s="14"/>
-      <c r="U35" s="14">
-        <f>IF([4]punteo!L36="",0,[4]punteo!L36)</f>
-        <v>0</v>
-      </c>
-      <c r="V35" s="14"/>
+      <c r="T35" s="10"/>
+      <c r="U35" s="10"/>
+      <c r="V35">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X35">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y35">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C36">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A36" s="15"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="15">
         <v>32</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="15">
         <v>202530357</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="F36">
-        <v>100</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <v>100</v>
-      </c>
-      <c r="I36">
-        <v>100</v>
-      </c>
-      <c r="J36">
-        <v>100</v>
-      </c>
-      <c r="K36">
-        <v>100</v>
-      </c>
-      <c r="L36">
-        <v>100</v>
-      </c>
-      <c r="M36">
-        <v>100</v>
-      </c>
-      <c r="N36">
+      <c r="F36" s="15">
+        <v>100</v>
+      </c>
+      <c r="G36" s="15">
+        <v>0</v>
+      </c>
+      <c r="H36" s="15">
+        <v>100</v>
+      </c>
+      <c r="I36" s="15">
+        <v>100</v>
+      </c>
+      <c r="J36" s="37">
+        <v>100</v>
+      </c>
+      <c r="K36" s="37">
+        <v>100</v>
+      </c>
+      <c r="L36" s="15">
+        <v>100</v>
+      </c>
+      <c r="M36" s="15">
+        <v>100</v>
+      </c>
+      <c r="N36" s="37">
         <v>80</v>
       </c>
-      <c r="O36">
+      <c r="O36" s="15">
         <v>65</v>
       </c>
-      <c r="P36">
+      <c r="P36" s="37">
         <v>80</v>
       </c>
       <c r="Q36" s="14">
         <f>IF([1]punteo!L37="",0,[1]punteo!L37)</f>
         <v>100</v>
       </c>
-      <c r="R36" s="14">
+      <c r="R36" s="10">
         <f>IF([2]punteo!L37="",0,[2]punteo!L37)</f>
         <v>100</v>
       </c>
-      <c r="S36" s="14">
+      <c r="S36" s="10">
         <f>IF([3]punteo!L37="",0,[3]punteo!L37)</f>
         <v>100</v>
       </c>
-      <c r="T36" s="14"/>
-      <c r="U36" s="14">
-        <f>IF([4]punteo!L37="",0,[4]punteo!L37)</f>
-        <v>0</v>
-      </c>
-      <c r="V36" s="14"/>
+      <c r="T36" s="10"/>
+      <c r="U36" s="10"/>
+      <c r="V36">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X36">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y36">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C37">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A37" s="15"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="15">
         <v>33</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="15">
         <v>202530381</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F37">
-        <v>100</v>
-      </c>
-      <c r="G37">
-        <v>100</v>
-      </c>
-      <c r="H37">
-        <v>100</v>
-      </c>
-      <c r="I37">
-        <v>100</v>
-      </c>
-      <c r="J37">
-        <v>100</v>
-      </c>
-      <c r="K37">
-        <v>100</v>
-      </c>
-      <c r="L37">
-        <v>100</v>
-      </c>
-      <c r="M37">
-        <v>100</v>
-      </c>
-      <c r="N37">
+      <c r="F37" s="15">
+        <v>100</v>
+      </c>
+      <c r="G37" s="15">
+        <v>100</v>
+      </c>
+      <c r="H37" s="15">
+        <v>100</v>
+      </c>
+      <c r="I37" s="15">
+        <v>100</v>
+      </c>
+      <c r="J37" s="37">
+        <v>100</v>
+      </c>
+      <c r="K37" s="37">
+        <v>100</v>
+      </c>
+      <c r="L37" s="15">
+        <v>100</v>
+      </c>
+      <c r="M37" s="15">
+        <v>100</v>
+      </c>
+      <c r="N37" s="37">
         <v>50</v>
       </c>
-      <c r="O37">
+      <c r="O37" s="15">
         <v>90</v>
       </c>
-      <c r="P37">
+      <c r="P37" s="37">
         <v>45</v>
       </c>
       <c r="Q37" s="14">
         <f>IF([1]punteo!L38="",0,[1]punteo!L38)</f>
         <v>80</v>
       </c>
-      <c r="R37" s="14">
+      <c r="R37" s="10">
         <f>IF([2]punteo!L38="",0,[2]punteo!L38)</f>
         <v>100</v>
       </c>
-      <c r="S37" s="14">
+      <c r="S37" s="10">
         <f>IF([3]punteo!L38="",0,[3]punteo!L38)</f>
         <v>100</v>
       </c>
-      <c r="T37" s="14"/>
-      <c r="U37" s="14">
-        <f>IF([4]punteo!L38="",0,[4]punteo!L38)</f>
-        <v>100</v>
-      </c>
-      <c r="V37" s="14"/>
+      <c r="T37" s="10"/>
+      <c r="U37" s="10"/>
+      <c r="V37">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X37">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y37">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A38" s="6">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A38" s="38">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="15">
         <v>34</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="15">
         <v>202530434</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="F38">
-        <v>100</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38">
-        <v>100</v>
-      </c>
-      <c r="I38">
+      <c r="F38" s="15">
+        <v>100</v>
+      </c>
+      <c r="G38" s="15">
+        <v>0</v>
+      </c>
+      <c r="H38" s="15">
+        <v>100</v>
+      </c>
+      <c r="I38" s="15">
         <v>90</v>
       </c>
-      <c r="J38">
+      <c r="J38" s="37">
         <v>75</v>
       </c>
-      <c r="K38">
+      <c r="K38" s="37">
         <v>55</v>
       </c>
-      <c r="L38">
-        <v>100</v>
-      </c>
-      <c r="M38">
-        <v>100</v>
-      </c>
-      <c r="N38">
+      <c r="L38" s="15">
+        <v>100</v>
+      </c>
+      <c r="M38" s="15">
+        <v>100</v>
+      </c>
+      <c r="N38" s="37">
         <v>90</v>
       </c>
-      <c r="O38">
+      <c r="O38" s="15">
         <v>75</v>
       </c>
-      <c r="P38">
+      <c r="P38" s="37">
         <v>100</v>
       </c>
       <c r="Q38" s="14">
         <f>IF([1]punteo!L39="",0,[1]punteo!L39)</f>
         <v>95</v>
       </c>
-      <c r="R38" s="14">
+      <c r="R38" s="10">
         <f>IF([2]punteo!L39="",0,[2]punteo!L39)</f>
         <v>100</v>
       </c>
-      <c r="S38" s="14">
+      <c r="S38" s="10">
         <f>IF([3]punteo!L39="",0,[3]punteo!L39)</f>
         <v>100</v>
       </c>
-      <c r="T38" s="14"/>
-      <c r="U38" s="14">
-        <f>IF([4]punteo!L39="",0,[4]punteo!L39)</f>
-        <v>0</v>
-      </c>
-      <c r="V38" s="14"/>
+      <c r="T38" s="10"/>
+      <c r="U38" s="10"/>
+      <c r="V38">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X38">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y38">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A39" s="6">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A39" s="38">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="15">
         <v>35</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="15">
         <v>202530446</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="F39">
-        <v>100</v>
-      </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-      <c r="H39">
-        <v>100</v>
-      </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-      <c r="J39">
-        <v>100</v>
-      </c>
-      <c r="K39">
-        <v>100</v>
-      </c>
-      <c r="L39">
-        <v>100</v>
-      </c>
-      <c r="M39">
-        <v>100</v>
-      </c>
-      <c r="N39">
+      <c r="F39" s="15">
+        <v>100</v>
+      </c>
+      <c r="G39" s="15">
+        <v>0</v>
+      </c>
+      <c r="H39" s="15">
+        <v>100</v>
+      </c>
+      <c r="I39" s="15">
+        <v>0</v>
+      </c>
+      <c r="J39" s="37">
+        <v>100</v>
+      </c>
+      <c r="K39" s="37">
+        <v>100</v>
+      </c>
+      <c r="L39" s="15">
+        <v>100</v>
+      </c>
+      <c r="M39" s="15">
+        <v>100</v>
+      </c>
+      <c r="N39" s="37">
         <v>50</v>
       </c>
-      <c r="O39">
+      <c r="O39" s="15">
         <v>85</v>
       </c>
-      <c r="P39">
+      <c r="P39" s="37">
         <v>80</v>
       </c>
       <c r="Q39" s="14">
         <f>IF([1]punteo!L40="",0,[1]punteo!L40)</f>
         <v>100</v>
       </c>
-      <c r="R39" s="14">
+      <c r="R39" s="10">
         <f>IF([2]punteo!L40="",0,[2]punteo!L40)</f>
         <v>100</v>
       </c>
-      <c r="S39" s="14">
+      <c r="S39" s="10">
         <f>IF([3]punteo!L40="",0,[3]punteo!L40)</f>
         <v>100</v>
       </c>
-      <c r="T39" s="14"/>
-      <c r="U39" s="14">
-        <f>IF([4]punteo!L40="",0,[4]punteo!L40)</f>
-        <v>0</v>
-      </c>
-      <c r="V39" s="14"/>
+      <c r="T39" s="10"/>
+      <c r="U39" s="10"/>
+      <c r="V39">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X39">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y39">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C40">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A40" s="15"/>
+      <c r="B40" s="16"/>
+      <c r="C40" s="15">
         <v>36</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="15">
         <v>202530522</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F40">
-        <v>100</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40">
-        <v>100</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
-        <v>100</v>
-      </c>
-      <c r="K40">
-        <v>100</v>
-      </c>
-      <c r="L40">
-        <v>100</v>
-      </c>
-      <c r="M40">
-        <v>100</v>
-      </c>
-      <c r="N40">
+      <c r="F40" s="15">
+        <v>100</v>
+      </c>
+      <c r="G40" s="15">
+        <v>0</v>
+      </c>
+      <c r="H40" s="15">
+        <v>100</v>
+      </c>
+      <c r="I40" s="15">
+        <v>0</v>
+      </c>
+      <c r="J40" s="37">
+        <v>100</v>
+      </c>
+      <c r="K40" s="37">
+        <v>100</v>
+      </c>
+      <c r="L40" s="15">
+        <v>100</v>
+      </c>
+      <c r="M40" s="15">
+        <v>100</v>
+      </c>
+      <c r="N40" s="37">
         <v>50</v>
       </c>
-      <c r="O40">
+      <c r="O40" s="15">
         <v>80</v>
       </c>
-      <c r="P40">
+      <c r="P40" s="37">
         <v>80</v>
       </c>
       <c r="Q40" s="14">
         <f>IF([1]punteo!L41="",0,[1]punteo!L41)</f>
         <v>0</v>
       </c>
-      <c r="R40" s="14">
+      <c r="R40" s="10">
         <f>IF([2]punteo!L41="",0,[2]punteo!L41)</f>
         <v>0</v>
       </c>
-      <c r="S40" s="14">
+      <c r="S40" s="10">
         <f>IF([3]punteo!L41="",0,[3]punteo!L41)</f>
         <v>0</v>
       </c>
-      <c r="T40" s="14"/>
-      <c r="U40" s="14">
-        <f>IF([4]punteo!L41="",0,[4]punteo!L41)</f>
-        <v>0</v>
-      </c>
-      <c r="V40" s="14"/>
+      <c r="T40" s="10"/>
+      <c r="U40" s="10"/>
+      <c r="V40">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W40">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X40">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y40">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C41">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A41" s="15"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="15">
         <v>37</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="15">
         <v>202530613</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="F41">
-        <v>0</v>
-      </c>
-      <c r="G41">
-        <v>100</v>
-      </c>
-      <c r="H41">
-        <v>0</v>
-      </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
-      <c r="J41">
-        <v>0</v>
-      </c>
-      <c r="K41">
-        <v>0</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41">
-        <v>0</v>
-      </c>
-      <c r="P41">
+      <c r="F41" s="15">
+        <v>0</v>
+      </c>
+      <c r="G41" s="15">
+        <v>100</v>
+      </c>
+      <c r="H41" s="15">
+        <v>0</v>
+      </c>
+      <c r="I41" s="15">
+        <v>0</v>
+      </c>
+      <c r="J41" s="37">
+        <v>0</v>
+      </c>
+      <c r="K41" s="37">
+        <v>0</v>
+      </c>
+      <c r="L41" s="15">
+        <v>0</v>
+      </c>
+      <c r="M41" s="15">
+        <v>0</v>
+      </c>
+      <c r="N41" s="37">
+        <v>0</v>
+      </c>
+      <c r="O41" s="15">
+        <v>0</v>
+      </c>
+      <c r="P41" s="37">
         <v>0</v>
       </c>
       <c r="Q41" s="14">
         <f>IF([1]punteo!L42="",0,[1]punteo!L42)</f>
         <v>0</v>
       </c>
-      <c r="R41" s="14">
+      <c r="R41" s="10">
         <f>IF([2]punteo!L42="",0,[2]punteo!L42)</f>
         <v>0</v>
       </c>
-      <c r="S41" s="14">
+      <c r="S41" s="10">
         <f>IF([3]punteo!L42="",0,[3]punteo!L42)</f>
         <v>0</v>
       </c>
-      <c r="T41" s="14"/>
-      <c r="U41" s="14">
-        <f>IF([4]punteo!L42="",0,[4]punteo!L42)</f>
-        <v>0</v>
-      </c>
-      <c r="V41" s="14"/>
+      <c r="T41" s="10"/>
+      <c r="U41" s="10"/>
+      <c r="V41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W41">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X41">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="X41" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C42">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A42" s="15"/>
+      <c r="B42" s="16"/>
+      <c r="C42" s="15">
         <v>38</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="15">
         <v>202530621</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F42">
-        <v>100</v>
-      </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42">
-        <v>100</v>
-      </c>
-      <c r="I42">
+      <c r="F42" s="15">
+        <v>100</v>
+      </c>
+      <c r="G42" s="15">
+        <v>0</v>
+      </c>
+      <c r="H42" s="15">
+        <v>100</v>
+      </c>
+      <c r="I42" s="15">
         <v>90</v>
       </c>
-      <c r="J42">
+      <c r="J42" s="37">
         <v>70</v>
       </c>
-      <c r="K42">
-        <v>100</v>
-      </c>
-      <c r="L42">
-        <v>100</v>
-      </c>
-      <c r="M42">
-        <v>100</v>
-      </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42">
+      <c r="K42" s="37">
+        <v>100</v>
+      </c>
+      <c r="L42" s="15">
+        <v>100</v>
+      </c>
+      <c r="M42" s="15">
+        <v>100</v>
+      </c>
+      <c r="N42" s="37">
+        <v>70</v>
+      </c>
+      <c r="O42" s="15">
         <v>60</v>
       </c>
-      <c r="P42">
+      <c r="P42" s="37">
         <v>65</v>
       </c>
       <c r="Q42" s="14">
         <f>IF([1]punteo!L43="",0,[1]punteo!L43)</f>
         <v>80</v>
       </c>
-      <c r="R42" s="14">
+      <c r="R42" s="10">
         <f>IF([2]punteo!L43="",0,[2]punteo!L43)</f>
         <v>100</v>
       </c>
-      <c r="S42" s="14">
+      <c r="S42" s="10">
         <f>IF([3]punteo!L43="",0,[3]punteo!L43)</f>
         <v>100</v>
       </c>
-      <c r="T42" s="14"/>
-      <c r="U42" s="14">
-        <f>IF([4]punteo!L43="",0,[4]punteo!L43)</f>
-        <v>0</v>
-      </c>
-      <c r="V42" s="14"/>
+      <c r="T42" s="10"/>
+      <c r="U42" s="10"/>
+      <c r="V42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W42">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X42">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y42">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A43" s="6">
+    <row r="43" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="39">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="37">
         <v>39</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="37">
         <v>202530673</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="F43">
-        <v>0</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
-      <c r="I43">
-        <v>100</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <v>0</v>
-      </c>
-      <c r="L43">
-        <v>100</v>
-      </c>
-      <c r="M43">
-        <v>100</v>
-      </c>
-      <c r="N43">
+      <c r="F43" s="37">
+        <v>0</v>
+      </c>
+      <c r="G43" s="37">
+        <v>0</v>
+      </c>
+      <c r="H43" s="37">
+        <v>0</v>
+      </c>
+      <c r="I43" s="37">
+        <v>100</v>
+      </c>
+      <c r="J43" s="37">
+        <v>0</v>
+      </c>
+      <c r="K43" s="37">
+        <v>100</v>
+      </c>
+      <c r="L43" s="37">
+        <v>100</v>
+      </c>
+      <c r="M43" s="37">
+        <v>100</v>
+      </c>
+      <c r="N43" s="37">
         <v>70</v>
       </c>
-      <c r="O43">
+      <c r="O43" s="37">
         <v>95</v>
       </c>
-      <c r="P43">
+      <c r="P43" s="37">
         <v>0</v>
       </c>
       <c r="Q43" s="14">
-        <f>IF([1]punteo!L44="",0,[1]punteo!L44)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="R43" s="14">
         <f>IF([2]punteo!L44="",0,[2]punteo!L44)</f>
@@ -5615,2638 +5167,2547 @@
         <v>100</v>
       </c>
       <c r="T43" s="14"/>
-      <c r="U43" s="14">
-        <f>IF([4]punteo!L44="",0,[4]punteo!L44)</f>
-        <v>0</v>
-      </c>
-      <c r="V43" s="14"/>
-      <c r="W43">
+      <c r="U43" s="14"/>
+      <c r="V43" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="X43">
+      <c r="W43" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y43">
+      <c r="X43" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C44">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A44" s="15"/>
+      <c r="B44" s="16"/>
+      <c r="C44" s="15">
         <v>40</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="15">
         <v>202530674</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="F44">
-        <v>0</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="H44">
+      <c r="F44" s="15">
+        <v>0</v>
+      </c>
+      <c r="G44" s="15">
+        <v>0</v>
+      </c>
+      <c r="H44" s="15">
         <v>50</v>
       </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
-      <c r="J44">
-        <v>100</v>
-      </c>
-      <c r="K44">
-        <v>100</v>
-      </c>
-      <c r="L44">
+      <c r="I44" s="15">
+        <v>0</v>
+      </c>
+      <c r="J44" s="37">
+        <v>100</v>
+      </c>
+      <c r="K44" s="37">
+        <v>100</v>
+      </c>
+      <c r="L44" s="15">
         <v>90</v>
       </c>
-      <c r="M44">
-        <v>100</v>
-      </c>
-      <c r="N44">
+      <c r="M44" s="15">
+        <v>100</v>
+      </c>
+      <c r="N44" s="37">
         <v>50</v>
       </c>
-      <c r="O44">
+      <c r="O44" s="15">
         <v>85</v>
       </c>
-      <c r="P44">
+      <c r="P44" s="37">
         <v>70</v>
       </c>
       <c r="Q44" s="14">
         <f>IF([1]punteo!L45="",0,[1]punteo!L45)</f>
         <v>0</v>
       </c>
-      <c r="R44" s="14">
+      <c r="R44" s="10">
         <f>IF([2]punteo!L45="",0,[2]punteo!L45)</f>
         <v>0</v>
       </c>
-      <c r="S44" s="14">
+      <c r="S44" s="10">
         <f>IF([3]punteo!L45="",0,[3]punteo!L45)</f>
         <v>0</v>
       </c>
-      <c r="T44" s="14"/>
-      <c r="U44" s="14">
-        <f>IF([4]punteo!L45="",0,[4]punteo!L45)</f>
-        <v>0</v>
-      </c>
-      <c r="V44" s="14"/>
+      <c r="T44" s="10"/>
+      <c r="U44" s="10"/>
+      <c r="V44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W44">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X44">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y44">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C45">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A45" s="15"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="15">
         <v>41</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="15">
         <v>202530677</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="F45">
-        <v>100</v>
-      </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-      <c r="H45">
-        <v>100</v>
-      </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
-      <c r="J45">
-        <v>100</v>
-      </c>
-      <c r="K45">
-        <v>0</v>
-      </c>
-      <c r="L45">
-        <v>100</v>
-      </c>
-      <c r="M45">
-        <v>0</v>
-      </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
-      <c r="O45">
-        <v>0</v>
-      </c>
-      <c r="P45">
+      <c r="F45" s="15">
+        <v>100</v>
+      </c>
+      <c r="G45" s="15">
+        <v>0</v>
+      </c>
+      <c r="H45" s="15">
+        <v>100</v>
+      </c>
+      <c r="I45" s="15">
+        <v>0</v>
+      </c>
+      <c r="J45" s="37">
+        <v>100</v>
+      </c>
+      <c r="K45" s="37">
+        <v>0</v>
+      </c>
+      <c r="L45" s="15">
+        <v>100</v>
+      </c>
+      <c r="M45" s="15">
+        <v>0</v>
+      </c>
+      <c r="N45" s="37">
+        <v>0</v>
+      </c>
+      <c r="O45" s="15">
+        <v>0</v>
+      </c>
+      <c r="P45" s="37">
         <v>0</v>
       </c>
       <c r="Q45" s="14">
         <f>IF([1]punteo!L46="",0,[1]punteo!L46)</f>
         <v>0</v>
       </c>
-      <c r="R45" s="14">
+      <c r="R45" s="10">
         <f>IF([2]punteo!L46="",0,[2]punteo!L46)</f>
         <v>0</v>
       </c>
-      <c r="S45" s="14">
+      <c r="S45" s="10">
         <f>IF([3]punteo!L46="",0,[3]punteo!L46)</f>
         <v>0</v>
       </c>
-      <c r="T45" s="14"/>
-      <c r="U45" s="14">
-        <f>IF([4]punteo!L46="",0,[4]punteo!L46)</f>
-        <v>0</v>
-      </c>
-      <c r="V45" s="14"/>
+      <c r="T45" s="10"/>
+      <c r="U45" s="10"/>
+      <c r="V45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X45">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y45">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A46" s="6">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A46" s="38">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B46" s="13" t="s">
+      <c r="B46" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="15">
         <v>42</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="15">
         <v>202530728</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="F46">
-        <v>100</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46">
-        <v>100</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46">
-        <v>0</v>
-      </c>
-      <c r="L46">
-        <v>0</v>
-      </c>
-      <c r="M46">
-        <v>100</v>
-      </c>
-      <c r="N46">
+      <c r="F46" s="15">
+        <v>100</v>
+      </c>
+      <c r="G46" s="15">
+        <v>0</v>
+      </c>
+      <c r="H46" s="15">
+        <v>100</v>
+      </c>
+      <c r="I46" s="15">
+        <v>0</v>
+      </c>
+      <c r="J46" s="37">
+        <v>100</v>
+      </c>
+      <c r="K46" s="37">
+        <v>100</v>
+      </c>
+      <c r="L46" s="15">
+        <v>0</v>
+      </c>
+      <c r="M46" s="15">
+        <v>100</v>
+      </c>
+      <c r="N46" s="37">
         <v>70</v>
       </c>
-      <c r="O46">
+      <c r="O46" s="15">
         <v>85</v>
       </c>
-      <c r="P46">
+      <c r="P46" s="37">
         <v>50</v>
       </c>
       <c r="Q46" s="14">
         <f>IF([1]punteo!L47="",0,[1]punteo!L47)</f>
         <v>80</v>
       </c>
-      <c r="R46" s="14">
+      <c r="R46" s="10">
         <f>IF([2]punteo!L47="",0,[2]punteo!L47)</f>
         <v>100</v>
       </c>
-      <c r="S46" s="14">
+      <c r="S46" s="10">
         <f>IF([3]punteo!L47="",0,[3]punteo!L47)</f>
         <v>100</v>
       </c>
-      <c r="T46" s="14"/>
-      <c r="U46" s="14">
-        <f>IF([4]punteo!L47="",0,[4]punteo!L47)</f>
-        <v>0</v>
-      </c>
-      <c r="V46" s="14"/>
+      <c r="T46" s="10"/>
+      <c r="U46" s="10"/>
+      <c r="V46">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W46">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X46">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y46">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A47" s="6">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A47" s="38">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B47" s="13" t="s">
+      <c r="B47" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="15">
         <v>43</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="15">
         <v>202530843</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="F47">
-        <v>0</v>
-      </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-      <c r="H47">
-        <v>0</v>
-      </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47">
-        <v>0</v>
-      </c>
-      <c r="L47">
-        <v>0</v>
-      </c>
-      <c r="M47">
-        <v>100</v>
-      </c>
-      <c r="N47">
+      <c r="F47" s="15">
+        <v>0</v>
+      </c>
+      <c r="G47" s="15">
+        <v>0</v>
+      </c>
+      <c r="H47" s="15">
+        <v>0</v>
+      </c>
+      <c r="I47" s="15">
+        <v>0</v>
+      </c>
+      <c r="J47" s="37">
+        <v>100</v>
+      </c>
+      <c r="K47" s="37">
+        <v>100</v>
+      </c>
+      <c r="L47" s="15">
+        <v>0</v>
+      </c>
+      <c r="M47" s="15">
+        <v>100</v>
+      </c>
+      <c r="N47" s="37">
         <v>70</v>
       </c>
-      <c r="O47">
+      <c r="O47" s="15">
         <v>85</v>
       </c>
-      <c r="P47">
+      <c r="P47" s="37">
         <v>85</v>
       </c>
       <c r="Q47" s="14">
         <f>IF([1]punteo!L48="",0,[1]punteo!L48)</f>
         <v>80</v>
       </c>
-      <c r="R47" s="14">
+      <c r="R47" s="10">
         <f>IF([2]punteo!L48="",0,[2]punteo!L48)</f>
         <v>100</v>
       </c>
-      <c r="S47" s="14">
+      <c r="S47" s="10">
         <f>IF([3]punteo!L48="",0,[3]punteo!L48)</f>
         <v>100</v>
       </c>
-      <c r="T47" s="14"/>
-      <c r="U47" s="14">
-        <f>IF([4]punteo!L48="",0,[4]punteo!L48)</f>
-        <v>0</v>
-      </c>
-      <c r="V47" s="14"/>
+      <c r="T47" s="10"/>
+      <c r="U47" s="10"/>
+      <c r="V47">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W47">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="X47">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="X47" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C48">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A48" s="15"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="15">
         <v>44</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="15">
         <v>202530866</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="F48">
-        <v>100</v>
-      </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48">
-        <v>100</v>
-      </c>
-      <c r="I48">
+      <c r="F48" s="15">
+        <v>100</v>
+      </c>
+      <c r="G48" s="15">
+        <v>0</v>
+      </c>
+      <c r="H48" s="15">
+        <v>100</v>
+      </c>
+      <c r="I48" s="15">
         <v>90</v>
       </c>
-      <c r="J48">
-        <v>100</v>
-      </c>
-      <c r="K48">
-        <v>100</v>
-      </c>
-      <c r="L48">
+      <c r="J48" s="37">
+        <v>100</v>
+      </c>
+      <c r="K48" s="37">
+        <v>100</v>
+      </c>
+      <c r="L48" s="15">
         <v>90</v>
       </c>
-      <c r="M48">
-        <v>100</v>
-      </c>
-      <c r="N48">
+      <c r="M48" s="15">
+        <v>100</v>
+      </c>
+      <c r="N48" s="37">
         <v>50</v>
       </c>
-      <c r="O48">
+      <c r="O48" s="15">
         <v>85</v>
       </c>
-      <c r="P48">
+      <c r="P48" s="37">
         <v>55</v>
       </c>
       <c r="Q48" s="14">
         <f>IF([1]punteo!L49="",0,[1]punteo!L49)</f>
         <v>100</v>
       </c>
-      <c r="R48" s="14">
+      <c r="R48" s="10">
         <f>IF([2]punteo!L49="",0,[2]punteo!L49)</f>
         <v>100</v>
       </c>
-      <c r="S48" s="14">
+      <c r="S48" s="10">
         <f>IF([3]punteo!L49="",0,[3]punteo!L49)</f>
         <v>100</v>
       </c>
-      <c r="T48" s="14"/>
-      <c r="U48" s="14">
-        <f>IF([4]punteo!L49="",0,[4]punteo!L49)</f>
-        <v>0</v>
-      </c>
-      <c r="V48" s="14"/>
+      <c r="T48" s="10"/>
+      <c r="U48" s="10"/>
+      <c r="V48">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W48">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X48">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y48">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A49" s="6">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A49" s="38">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B49" s="13" t="s">
+      <c r="B49" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="15">
         <v>45</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="15">
         <v>202530917</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="F49">
-        <v>0</v>
-      </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-      <c r="H49">
+      <c r="F49" s="15">
+        <v>0</v>
+      </c>
+      <c r="G49" s="15">
+        <v>0</v>
+      </c>
+      <c r="H49" s="15">
         <v>50</v>
       </c>
-      <c r="I49">
-        <v>100</v>
-      </c>
-      <c r="J49">
+      <c r="I49" s="15">
+        <v>100</v>
+      </c>
+      <c r="J49" s="37">
         <v>75</v>
       </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="L49">
-        <v>100</v>
-      </c>
-      <c r="M49">
-        <v>100</v>
-      </c>
-      <c r="N49">
+      <c r="K49" s="37">
+        <v>100</v>
+      </c>
+      <c r="L49" s="15">
+        <v>100</v>
+      </c>
+      <c r="M49" s="15">
+        <v>100</v>
+      </c>
+      <c r="N49" s="37">
         <v>90</v>
       </c>
-      <c r="O49">
+      <c r="O49" s="15">
         <v>95</v>
       </c>
-      <c r="P49">
+      <c r="P49" s="37">
         <v>65</v>
       </c>
       <c r="Q49" s="14">
         <f>IF([1]punteo!L50="",0,[1]punteo!L50)</f>
         <v>100</v>
       </c>
-      <c r="R49" s="14">
+      <c r="R49" s="10">
         <f>IF([2]punteo!L50="",0,[2]punteo!L50)</f>
         <v>100</v>
       </c>
-      <c r="S49" s="14">
+      <c r="S49" s="10">
         <f>IF([3]punteo!L50="",0,[3]punteo!L50)</f>
         <v>100</v>
       </c>
-      <c r="T49" s="14"/>
-      <c r="U49" s="14">
-        <f>IF([4]punteo!L50="",0,[4]punteo!L50)</f>
-        <v>0</v>
-      </c>
-      <c r="V49" s="14"/>
+      <c r="T49" s="10"/>
+      <c r="U49" s="10"/>
+      <c r="V49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W49">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X49">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y49">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C50">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A50" s="15"/>
+      <c r="B50" s="16"/>
+      <c r="C50" s="15">
         <v>46</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="15">
         <v>202531013</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="F50">
-        <v>100</v>
-      </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-      <c r="H50">
-        <v>100</v>
-      </c>
-      <c r="I50">
+      <c r="F50" s="15">
+        <v>100</v>
+      </c>
+      <c r="G50" s="15">
+        <v>0</v>
+      </c>
+      <c r="H50" s="15">
+        <v>100</v>
+      </c>
+      <c r="I50" s="15">
         <v>90</v>
       </c>
-      <c r="J50">
-        <v>100</v>
-      </c>
-      <c r="K50">
+      <c r="J50" s="37">
+        <v>100</v>
+      </c>
+      <c r="K50" s="37">
         <v>75</v>
       </c>
-      <c r="L50">
-        <v>100</v>
-      </c>
-      <c r="M50">
-        <v>100</v>
-      </c>
-      <c r="N50">
-        <v>100</v>
-      </c>
-      <c r="O50">
+      <c r="L50" s="15">
+        <v>100</v>
+      </c>
+      <c r="M50" s="15">
+        <v>100</v>
+      </c>
+      <c r="N50" s="37">
+        <v>100</v>
+      </c>
+      <c r="O50" s="15">
         <v>90</v>
       </c>
-      <c r="P50">
+      <c r="P50" s="37">
         <v>70</v>
       </c>
       <c r="Q50" s="14">
         <f>IF([1]punteo!L51="",0,[1]punteo!L51)</f>
         <v>100</v>
       </c>
-      <c r="R50" s="14">
+      <c r="R50" s="10">
         <f>IF([2]punteo!L51="",0,[2]punteo!L51)</f>
         <v>100</v>
       </c>
-      <c r="S50" s="14">
+      <c r="S50" s="10">
         <f>IF([3]punteo!L51="",0,[3]punteo!L51)</f>
         <v>100</v>
       </c>
-      <c r="T50" s="14"/>
-      <c r="U50" s="14">
-        <f>IF([4]punteo!L51="",0,[4]punteo!L51)</f>
-        <v>0</v>
-      </c>
-      <c r="V50" s="14"/>
+      <c r="T50" s="10"/>
+      <c r="U50" s="10"/>
+      <c r="V50">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X50">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y50">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C51">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A51" s="15"/>
+      <c r="B51" s="16"/>
+      <c r="C51" s="15">
         <v>47</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="15">
         <v>202531019</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="F51">
-        <v>0</v>
-      </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
-      <c r="H51">
-        <v>100</v>
-      </c>
-      <c r="I51">
+      <c r="F51" s="15">
+        <v>0</v>
+      </c>
+      <c r="G51" s="15">
+        <v>0</v>
+      </c>
+      <c r="H51" s="15">
+        <v>100</v>
+      </c>
+      <c r="I51" s="15">
         <v>90</v>
       </c>
-      <c r="J51">
-        <v>100</v>
-      </c>
-      <c r="K51">
+      <c r="J51" s="37">
+        <v>100</v>
+      </c>
+      <c r="K51" s="37">
         <v>55</v>
       </c>
-      <c r="L51">
-        <v>100</v>
-      </c>
-      <c r="M51">
-        <v>100</v>
-      </c>
-      <c r="N51">
+      <c r="L51" s="15">
+        <v>100</v>
+      </c>
+      <c r="M51" s="15">
+        <v>100</v>
+      </c>
+      <c r="N51" s="37">
         <v>95</v>
       </c>
-      <c r="O51">
-        <v>0</v>
-      </c>
-      <c r="P51">
+      <c r="O51" s="15">
+        <v>0</v>
+      </c>
+      <c r="P51" s="37">
         <v>55</v>
       </c>
       <c r="Q51" s="14">
         <f>IF([1]punteo!L52="",0,[1]punteo!L52)</f>
         <v>100</v>
       </c>
-      <c r="R51" s="14">
+      <c r="R51" s="10">
         <f>IF([2]punteo!L52="",0,[2]punteo!L52)</f>
         <v>100</v>
       </c>
-      <c r="S51" s="14">
+      <c r="S51" s="10">
         <f>IF([3]punteo!L52="",0,[3]punteo!L52)</f>
         <v>100</v>
       </c>
-      <c r="T51" s="14"/>
-      <c r="U51" s="14">
-        <f>IF([4]punteo!L52="",0,[4]punteo!L52)</f>
-        <v>100</v>
-      </c>
-      <c r="V51" s="14"/>
+      <c r="T51" s="10"/>
+      <c r="U51" s="10"/>
+      <c r="V51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W51">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="X51">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y51">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C52">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A52" s="15"/>
+      <c r="B52" s="16"/>
+      <c r="C52" s="15">
         <v>48</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="15">
         <v>202531089</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="F52">
-        <v>100</v>
-      </c>
-      <c r="G52">
-        <v>0</v>
-      </c>
-      <c r="H52">
-        <v>100</v>
-      </c>
-      <c r="I52">
+      <c r="F52" s="15">
+        <v>100</v>
+      </c>
+      <c r="G52" s="15">
+        <v>0</v>
+      </c>
+      <c r="H52" s="15">
+        <v>100</v>
+      </c>
+      <c r="I52" s="15">
         <v>90</v>
       </c>
-      <c r="J52">
+      <c r="J52" s="37">
         <v>70</v>
       </c>
-      <c r="K52">
-        <v>100</v>
-      </c>
-      <c r="L52">
+      <c r="K52" s="37">
+        <v>100</v>
+      </c>
+      <c r="L52" s="15">
         <v>90</v>
       </c>
-      <c r="M52">
-        <v>100</v>
-      </c>
-      <c r="N52">
+      <c r="M52" s="15">
+        <v>100</v>
+      </c>
+      <c r="N52" s="37">
         <v>50</v>
       </c>
-      <c r="O52">
+      <c r="O52" s="15">
         <v>85</v>
       </c>
-      <c r="P52">
+      <c r="P52" s="37">
         <v>55</v>
       </c>
       <c r="Q52" s="14">
         <f>IF([1]punteo!L53="",0,[1]punteo!L53)</f>
         <v>100</v>
       </c>
-      <c r="R52" s="14">
+      <c r="R52" s="10">
         <f>IF([2]punteo!L53="",0,[2]punteo!L53)</f>
         <v>100</v>
       </c>
-      <c r="S52" s="14">
+      <c r="S52" s="10">
         <f>IF([3]punteo!L53="",0,[3]punteo!L53)</f>
         <v>100</v>
       </c>
-      <c r="T52" s="14"/>
-      <c r="U52" s="14">
-        <f>IF([4]punteo!L53="",0,[4]punteo!L53)</f>
-        <v>0</v>
-      </c>
-      <c r="V52" s="14"/>
+      <c r="T52" s="10"/>
+      <c r="U52" s="10"/>
+      <c r="V52">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W52">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="X52">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="X52" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C53">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A53" s="15"/>
+      <c r="B53" s="16"/>
+      <c r="C53" s="15">
         <v>49</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="15">
         <v>202531127</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E53" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="F53">
-        <v>0</v>
-      </c>
-      <c r="G53">
-        <v>0</v>
-      </c>
-      <c r="H53">
-        <v>100</v>
-      </c>
-      <c r="I53">
-        <v>0</v>
-      </c>
-      <c r="J53">
-        <v>0</v>
-      </c>
-      <c r="K53">
-        <v>0</v>
-      </c>
-      <c r="L53">
-        <v>0</v>
-      </c>
-      <c r="M53">
-        <v>100</v>
-      </c>
-      <c r="N53">
+      <c r="F53" s="15">
+        <v>0</v>
+      </c>
+      <c r="G53" s="15">
+        <v>0</v>
+      </c>
+      <c r="H53" s="15">
+        <v>100</v>
+      </c>
+      <c r="I53" s="15">
+        <v>0</v>
+      </c>
+      <c r="J53" s="37">
+        <v>0</v>
+      </c>
+      <c r="K53" s="37">
+        <v>100</v>
+      </c>
+      <c r="L53" s="15">
+        <v>0</v>
+      </c>
+      <c r="M53" s="15">
+        <v>100</v>
+      </c>
+      <c r="N53" s="37">
         <v>70</v>
       </c>
-      <c r="O53">
+      <c r="O53" s="15">
         <v>85</v>
       </c>
-      <c r="P53">
+      <c r="P53" s="37">
         <v>85</v>
       </c>
       <c r="Q53" s="14">
         <f>IF([1]punteo!L54="",0,[1]punteo!L54)</f>
         <v>80</v>
       </c>
-      <c r="R53" s="14">
+      <c r="R53" s="10">
         <f>IF([2]punteo!L54="",0,[2]punteo!L54)</f>
         <v>100</v>
       </c>
-      <c r="S53" s="14">
+      <c r="S53" s="10">
         <f>IF([3]punteo!L54="",0,[3]punteo!L54)</f>
         <v>100</v>
       </c>
-      <c r="T53" s="14"/>
-      <c r="U53" s="14">
-        <f>IF([4]punteo!L54="",0,[4]punteo!L54)</f>
-        <v>0</v>
-      </c>
-      <c r="V53" s="14"/>
+      <c r="T53" s="10"/>
+      <c r="U53" s="10"/>
+      <c r="V53">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W53">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X53">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y53">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C54">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A54" s="15"/>
+      <c r="B54" s="16"/>
+      <c r="C54" s="15">
         <v>50</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="15">
         <v>202531213</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E54" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F54">
-        <v>100</v>
-      </c>
-      <c r="G54">
-        <v>100</v>
-      </c>
-      <c r="H54">
-        <v>100</v>
-      </c>
-      <c r="I54">
+      <c r="F54" s="15">
+        <v>100</v>
+      </c>
+      <c r="G54" s="15">
+        <v>100</v>
+      </c>
+      <c r="H54" s="15">
+        <v>100</v>
+      </c>
+      <c r="I54" s="15">
         <v>90</v>
       </c>
-      <c r="J54">
-        <v>100</v>
-      </c>
-      <c r="K54">
+      <c r="J54" s="37">
+        <v>100</v>
+      </c>
+      <c r="K54" s="37">
         <v>90</v>
       </c>
-      <c r="L54">
-        <v>100</v>
-      </c>
-      <c r="M54">
-        <v>100</v>
-      </c>
-      <c r="N54">
+      <c r="L54" s="15">
+        <v>100</v>
+      </c>
+      <c r="M54" s="15">
+        <v>100</v>
+      </c>
+      <c r="N54" s="37">
         <v>80</v>
       </c>
-      <c r="O54">
-        <v>100</v>
-      </c>
-      <c r="P54">
+      <c r="O54" s="15">
+        <v>100</v>
+      </c>
+      <c r="P54" s="37">
         <v>100</v>
       </c>
       <c r="Q54" s="14">
         <f>IF([1]punteo!L55="",0,[1]punteo!L55)</f>
         <v>90</v>
       </c>
-      <c r="R54" s="14">
+      <c r="R54" s="10">
         <f>IF([2]punteo!L55="",0,[2]punteo!L55)</f>
         <v>100</v>
       </c>
-      <c r="S54" s="14">
+      <c r="S54" s="10">
         <f>IF([3]punteo!L55="",0,[3]punteo!L55)</f>
         <v>100</v>
       </c>
-      <c r="T54" s="14"/>
-      <c r="U54" s="14">
-        <f>IF([4]punteo!L55="",0,[4]punteo!L55)</f>
-        <v>0</v>
-      </c>
-      <c r="V54" s="14"/>
+      <c r="T54" s="10"/>
+      <c r="U54" s="10"/>
+      <c r="V54">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W54">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X54">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y54">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C55">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A55" s="15"/>
+      <c r="B55" s="16"/>
+      <c r="C55" s="15">
         <v>51</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="15">
         <v>202531219</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E55" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F55">
-        <v>0</v>
-      </c>
-      <c r="G55">
-        <v>0</v>
-      </c>
-      <c r="H55">
-        <v>100</v>
-      </c>
-      <c r="I55">
-        <v>100</v>
-      </c>
-      <c r="J55">
-        <v>0</v>
-      </c>
-      <c r="K55">
-        <v>0</v>
-      </c>
-      <c r="L55">
-        <v>100</v>
-      </c>
-      <c r="M55">
+      <c r="F55" s="15">
+        <v>0</v>
+      </c>
+      <c r="G55" s="15">
+        <v>0</v>
+      </c>
+      <c r="H55" s="15">
+        <v>100</v>
+      </c>
+      <c r="I55" s="15">
+        <v>100</v>
+      </c>
+      <c r="J55" s="37">
+        <v>75</v>
+      </c>
+      <c r="K55" s="37">
+        <v>90</v>
+      </c>
+      <c r="L55" s="15">
+        <v>100</v>
+      </c>
+      <c r="M55" s="15">
         <v>80</v>
       </c>
-      <c r="N55">
+      <c r="N55" s="37">
         <v>70</v>
       </c>
-      <c r="O55">
+      <c r="O55" s="15">
         <v>45</v>
       </c>
-      <c r="P55">
+      <c r="P55" s="37">
         <v>0</v>
       </c>
       <c r="Q55" s="14">
         <f>IF([1]punteo!L56="",0,[1]punteo!L56)</f>
         <v>80</v>
       </c>
-      <c r="R55" s="14">
+      <c r="R55" s="10">
         <f>IF([2]punteo!L56="",0,[2]punteo!L56)</f>
         <v>100</v>
       </c>
-      <c r="S55" s="14">
+      <c r="S55" s="10">
         <f>IF([3]punteo!L56="",0,[3]punteo!L56)</f>
         <v>100</v>
       </c>
-      <c r="T55" s="14"/>
-      <c r="U55" s="14">
-        <f>IF([4]punteo!L56="",0,[4]punteo!L56)</f>
-        <v>0</v>
-      </c>
-      <c r="V55" s="14"/>
+      <c r="T55" s="10"/>
+      <c r="U55" s="10"/>
+      <c r="V55">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W55">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="X55">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y55">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C56">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A56" s="15"/>
+      <c r="B56" s="16"/>
+      <c r="C56" s="15">
         <v>52</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="15">
         <v>202531289</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E56" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="F56">
-        <v>100</v>
-      </c>
-      <c r="G56">
-        <v>0</v>
-      </c>
-      <c r="H56">
-        <v>100</v>
-      </c>
-      <c r="I56">
-        <v>100</v>
-      </c>
-      <c r="J56">
+      <c r="F56" s="15">
+        <v>100</v>
+      </c>
+      <c r="G56" s="15">
+        <v>0</v>
+      </c>
+      <c r="H56" s="15">
+        <v>100</v>
+      </c>
+      <c r="I56" s="15">
+        <v>100</v>
+      </c>
+      <c r="J56" s="37">
         <v>85</v>
       </c>
-      <c r="K56">
-        <v>100</v>
-      </c>
-      <c r="L56">
-        <v>100</v>
-      </c>
-      <c r="M56">
-        <v>100</v>
-      </c>
-      <c r="N56">
-        <v>100</v>
-      </c>
-      <c r="O56">
+      <c r="K56" s="37">
+        <v>100</v>
+      </c>
+      <c r="L56" s="15">
+        <v>100</v>
+      </c>
+      <c r="M56" s="15">
+        <v>100</v>
+      </c>
+      <c r="N56" s="37">
+        <v>100</v>
+      </c>
+      <c r="O56" s="15">
         <v>95</v>
       </c>
-      <c r="P56">
+      <c r="P56" s="37">
         <v>85</v>
       </c>
       <c r="Q56" s="14">
         <f>IF([1]punteo!L57="",0,[1]punteo!L57)</f>
         <v>95</v>
       </c>
-      <c r="R56" s="14">
+      <c r="R56" s="10">
         <f>IF([2]punteo!L57="",0,[2]punteo!L57)</f>
         <v>0</v>
       </c>
-      <c r="S56" s="14">
+      <c r="S56" s="10">
         <f>IF([3]punteo!L57="",0,[3]punteo!L57)</f>
         <v>100</v>
       </c>
-      <c r="T56" s="14"/>
-      <c r="U56" s="14">
-        <f>IF([4]punteo!L57="",0,[4]punteo!L57)</f>
-        <v>100</v>
-      </c>
-      <c r="V56" s="14"/>
+      <c r="T56" s="10"/>
+      <c r="U56" s="10"/>
+      <c r="V56">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X56">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y56">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A57" s="6">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A57" s="38">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B57" s="13" t="s">
+      <c r="B57" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="15">
         <v>53</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="15">
         <v>202531319</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E57" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F57">
-        <v>100</v>
-      </c>
-      <c r="G57">
-        <v>0</v>
-      </c>
-      <c r="H57">
+      <c r="F57" s="15">
+        <v>100</v>
+      </c>
+      <c r="G57" s="15">
+        <v>0</v>
+      </c>
+      <c r="H57" s="15">
         <v>50</v>
       </c>
-      <c r="I57">
-        <v>100</v>
-      </c>
-      <c r="J57">
+      <c r="I57" s="15">
+        <v>100</v>
+      </c>
+      <c r="J57" s="37">
         <v>75</v>
       </c>
-      <c r="K57">
-        <v>0</v>
-      </c>
-      <c r="L57">
-        <v>100</v>
-      </c>
-      <c r="M57">
-        <v>100</v>
-      </c>
-      <c r="N57">
+      <c r="K57" s="37">
+        <v>100</v>
+      </c>
+      <c r="L57" s="15">
+        <v>100</v>
+      </c>
+      <c r="M57" s="15">
+        <v>100</v>
+      </c>
+      <c r="N57" s="37">
         <v>50</v>
       </c>
-      <c r="O57">
-        <v>0</v>
-      </c>
-      <c r="P57">
+      <c r="O57" s="15">
+        <v>0</v>
+      </c>
+      <c r="P57" s="37">
         <v>50</v>
       </c>
       <c r="Q57" s="14">
         <f>IF([1]punteo!L58="",0,[1]punteo!L58)</f>
         <v>100</v>
       </c>
-      <c r="R57" s="14">
+      <c r="R57" s="10">
         <f>IF([2]punteo!L58="",0,[2]punteo!L58)</f>
         <v>100</v>
       </c>
-      <c r="S57" s="14">
+      <c r="S57" s="10">
         <f>IF([3]punteo!L58="",0,[3]punteo!L58)</f>
         <v>100</v>
       </c>
-      <c r="T57" s="14"/>
-      <c r="U57" s="14">
-        <f>IF([4]punteo!L58="",0,[4]punteo!L58)</f>
-        <v>0</v>
-      </c>
-      <c r="V57" s="14"/>
+      <c r="T57" s="10"/>
+      <c r="U57" s="10"/>
+      <c r="V57">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W57">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="X57">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y57">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A58" s="6">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A58" s="38">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B58" s="13" t="s">
+      <c r="B58" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="15">
         <v>54</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="15">
         <v>202531351</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="F58">
-        <v>100</v>
-      </c>
-      <c r="G58">
-        <v>100</v>
-      </c>
-      <c r="H58">
-        <v>100</v>
-      </c>
-      <c r="I58">
+      <c r="F58" s="15">
+        <v>100</v>
+      </c>
+      <c r="G58" s="15">
+        <v>100</v>
+      </c>
+      <c r="H58" s="15">
+        <v>100</v>
+      </c>
+      <c r="I58" s="15">
         <v>90</v>
       </c>
-      <c r="J58">
-        <v>100</v>
-      </c>
-      <c r="K58">
-        <v>100</v>
-      </c>
-      <c r="L58">
-        <v>100</v>
-      </c>
-      <c r="M58">
-        <v>100</v>
-      </c>
-      <c r="N58">
+      <c r="J58" s="37">
+        <v>100</v>
+      </c>
+      <c r="K58" s="37">
+        <v>100</v>
+      </c>
+      <c r="L58" s="15">
+        <v>100</v>
+      </c>
+      <c r="M58" s="15">
+        <v>100</v>
+      </c>
+      <c r="N58" s="37">
         <v>80</v>
       </c>
-      <c r="O58">
+      <c r="O58" s="15">
         <v>90</v>
       </c>
-      <c r="P58">
+      <c r="P58" s="37">
         <v>100</v>
       </c>
       <c r="Q58" s="14">
         <f>IF([1]punteo!L59="",0,[1]punteo!L59)</f>
         <v>90</v>
       </c>
-      <c r="R58" s="14">
+      <c r="R58" s="10">
         <f>IF([2]punteo!L59="",0,[2]punteo!L59)</f>
         <v>100</v>
       </c>
-      <c r="S58" s="14">
+      <c r="S58" s="10">
         <f>IF([3]punteo!L59="",0,[3]punteo!L59)</f>
         <v>100</v>
       </c>
-      <c r="T58" s="14"/>
-      <c r="U58" s="14">
-        <f>IF([4]punteo!L59="",0,[4]punteo!L59)</f>
-        <v>0</v>
-      </c>
-      <c r="V58" s="14"/>
+      <c r="T58" s="10"/>
+      <c r="U58" s="10"/>
+      <c r="V58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W58">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X58">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y58">
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A59" s="6">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A59" s="38">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B59" s="13" t="s">
+      <c r="B59" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="15">
         <v>55</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="15">
         <v>202531352</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E59" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="F59">
-        <v>100</v>
-      </c>
-      <c r="G59">
-        <v>0</v>
-      </c>
-      <c r="H59">
-        <v>100</v>
-      </c>
-      <c r="I59">
-        <v>100</v>
-      </c>
-      <c r="J59">
-        <v>100</v>
-      </c>
-      <c r="K59">
-        <v>100</v>
-      </c>
-      <c r="L59">
-        <v>100</v>
-      </c>
-      <c r="M59">
-        <v>100</v>
-      </c>
-      <c r="N59">
+      <c r="F59" s="15">
+        <v>100</v>
+      </c>
+      <c r="G59" s="15">
+        <v>0</v>
+      </c>
+      <c r="H59" s="15">
+        <v>100</v>
+      </c>
+      <c r="I59" s="15">
+        <v>100</v>
+      </c>
+      <c r="J59" s="37">
+        <v>100</v>
+      </c>
+      <c r="K59" s="37">
+        <v>100</v>
+      </c>
+      <c r="L59" s="15">
+        <v>100</v>
+      </c>
+      <c r="M59" s="15">
+        <v>100</v>
+      </c>
+      <c r="N59" s="37">
         <v>70</v>
       </c>
-      <c r="O59">
-        <v>0</v>
-      </c>
-      <c r="P59">
+      <c r="O59" s="15">
+        <v>0</v>
+      </c>
+      <c r="P59" s="37">
         <v>75</v>
       </c>
       <c r="Q59" s="14">
         <f>IF([1]punteo!L60="",0,[1]punteo!L60)</f>
         <v>80</v>
       </c>
-      <c r="R59" s="14">
+      <c r="R59" s="10">
         <f>IF([2]punteo!L60="",0,[2]punteo!L60)</f>
         <v>0</v>
       </c>
-      <c r="S59" s="14">
+      <c r="S59" s="10">
         <f>IF([3]punteo!L60="",0,[3]punteo!L60)</f>
         <v>100</v>
       </c>
-      <c r="T59" s="14"/>
-      <c r="U59" s="14">
-        <f>IF([4]punteo!L60="",0,[4]punteo!L60)</f>
-        <v>0</v>
-      </c>
-      <c r="V59" s="14"/>
+      <c r="T59" s="10"/>
+      <c r="U59" s="10"/>
+      <c r="V59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W59">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="X59">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y59">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C60">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A60" s="15"/>
+      <c r="B60" s="16"/>
+      <c r="C60" s="15">
         <v>56</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="15">
         <v>202531384</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E60" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F60">
-        <v>100</v>
-      </c>
-      <c r="G60">
-        <v>100</v>
-      </c>
-      <c r="H60">
+      <c r="F60" s="15">
+        <v>100</v>
+      </c>
+      <c r="G60" s="15">
+        <v>100</v>
+      </c>
+      <c r="H60" s="15">
         <v>50</v>
       </c>
-      <c r="I60">
+      <c r="I60" s="15">
         <v>90</v>
       </c>
-      <c r="J60">
-        <v>100</v>
-      </c>
-      <c r="K60">
-        <v>100</v>
-      </c>
-      <c r="L60">
-        <v>100</v>
-      </c>
-      <c r="M60">
-        <v>100</v>
-      </c>
-      <c r="N60">
+      <c r="J60" s="37">
+        <v>100</v>
+      </c>
+      <c r="K60" s="37">
+        <v>100</v>
+      </c>
+      <c r="L60" s="15">
+        <v>100</v>
+      </c>
+      <c r="M60" s="15">
+        <v>100</v>
+      </c>
+      <c r="N60" s="37">
         <v>70</v>
       </c>
-      <c r="O60">
-        <v>100</v>
-      </c>
-      <c r="P60">
+      <c r="O60" s="15">
+        <v>100</v>
+      </c>
+      <c r="P60" s="37">
         <v>90</v>
       </c>
       <c r="Q60" s="14">
         <f>IF([1]punteo!L61="",0,[1]punteo!L61)</f>
         <v>80</v>
       </c>
-      <c r="R60" s="14">
+      <c r="R60" s="10">
         <f>IF([2]punteo!L61="",0,[2]punteo!L61)</f>
         <v>100</v>
       </c>
-      <c r="S60" s="14">
+      <c r="S60" s="10">
         <f>IF([3]punteo!L61="",0,[3]punteo!L61)</f>
         <v>100</v>
       </c>
-      <c r="T60" s="14"/>
-      <c r="U60" s="14">
-        <f>IF([4]punteo!L61="",0,[4]punteo!L61)</f>
-        <v>100</v>
-      </c>
-      <c r="V60" s="14"/>
+      <c r="T60" s="10"/>
+      <c r="U60" s="10"/>
+      <c r="V60">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W60">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X60">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y60">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C61">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A61" s="15"/>
+      <c r="B61" s="16"/>
+      <c r="C61" s="15">
         <v>57</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="15">
         <v>202531399</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E61" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F61">
-        <v>0</v>
-      </c>
-      <c r="G61">
-        <v>0</v>
-      </c>
-      <c r="H61">
+      <c r="F61" s="15">
+        <v>0</v>
+      </c>
+      <c r="G61" s="15">
+        <v>0</v>
+      </c>
+      <c r="H61" s="15">
         <v>50</v>
       </c>
-      <c r="I61">
-        <v>0</v>
-      </c>
-      <c r="J61">
-        <v>0</v>
-      </c>
-      <c r="K61">
-        <v>0</v>
-      </c>
-      <c r="L61">
-        <v>0</v>
-      </c>
-      <c r="M61">
-        <v>0</v>
-      </c>
-      <c r="N61">
-        <v>0</v>
-      </c>
-      <c r="O61">
-        <v>0</v>
-      </c>
-      <c r="P61">
+      <c r="I61" s="15">
+        <v>0</v>
+      </c>
+      <c r="J61" s="37">
+        <v>0</v>
+      </c>
+      <c r="K61" s="37">
+        <v>0</v>
+      </c>
+      <c r="L61" s="15">
+        <v>0</v>
+      </c>
+      <c r="M61" s="15">
+        <v>0</v>
+      </c>
+      <c r="N61" s="37">
+        <v>0</v>
+      </c>
+      <c r="O61" s="15">
+        <v>0</v>
+      </c>
+      <c r="P61" s="37">
         <v>0</v>
       </c>
       <c r="Q61" s="14">
         <f>IF([1]punteo!L62="",0,[1]punteo!L62)</f>
         <v>0</v>
       </c>
-      <c r="R61" s="14">
+      <c r="R61" s="10">
         <f>IF([2]punteo!L62="",0,[2]punteo!L62)</f>
         <v>0</v>
       </c>
-      <c r="S61" s="14">
+      <c r="S61" s="10">
         <f>IF([3]punteo!L62="",0,[3]punteo!L62)</f>
         <v>0</v>
       </c>
-      <c r="T61" s="14"/>
-      <c r="U61" s="14">
-        <f>IF([4]punteo!L62="",0,[4]punteo!L62)</f>
-        <v>0</v>
-      </c>
-      <c r="V61" s="14"/>
+      <c r="T61" s="10"/>
+      <c r="U61" s="10"/>
+      <c r="V61">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W61">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X61">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y61">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C62">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A62" s="15"/>
+      <c r="B62" s="16"/>
+      <c r="C62" s="15">
         <v>58</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="15">
         <v>202531441</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E62" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="F62">
-        <v>0</v>
-      </c>
-      <c r="G62">
-        <v>0</v>
-      </c>
-      <c r="H62">
-        <v>0</v>
-      </c>
-      <c r="I62">
-        <v>0</v>
-      </c>
-      <c r="J62">
-        <v>0</v>
-      </c>
-      <c r="K62">
-        <v>0</v>
-      </c>
-      <c r="L62">
-        <v>0</v>
-      </c>
-      <c r="M62">
-        <v>0</v>
-      </c>
-      <c r="N62">
-        <v>0</v>
-      </c>
-      <c r="O62">
-        <v>0</v>
-      </c>
-      <c r="P62">
+      <c r="F62" s="15">
+        <v>0</v>
+      </c>
+      <c r="G62" s="15">
+        <v>0</v>
+      </c>
+      <c r="H62" s="15">
+        <v>0</v>
+      </c>
+      <c r="I62" s="15">
+        <v>0</v>
+      </c>
+      <c r="J62" s="37">
+        <v>0</v>
+      </c>
+      <c r="K62" s="37">
+        <v>0</v>
+      </c>
+      <c r="L62" s="15">
+        <v>0</v>
+      </c>
+      <c r="M62" s="15">
+        <v>0</v>
+      </c>
+      <c r="N62" s="37">
+        <v>0</v>
+      </c>
+      <c r="O62" s="15">
+        <v>0</v>
+      </c>
+      <c r="P62" s="37">
         <v>0</v>
       </c>
       <c r="Q62" s="14">
         <f>IF([1]punteo!L63="",0,[1]punteo!L63)</f>
         <v>0</v>
       </c>
-      <c r="R62" s="14">
+      <c r="R62" s="10">
         <f>IF([2]punteo!L63="",0,[2]punteo!L63)</f>
         <v>0</v>
       </c>
-      <c r="S62" s="14">
+      <c r="S62" s="10">
         <f>IF([3]punteo!L63="",0,[3]punteo!L63)</f>
         <v>0</v>
       </c>
-      <c r="T62" s="14"/>
-      <c r="U62" s="14">
-        <f>IF([4]punteo!L63="",0,[4]punteo!L63)</f>
-        <v>0</v>
-      </c>
-      <c r="V62" s="14"/>
+      <c r="T62" s="10"/>
+      <c r="U62" s="10"/>
+      <c r="V62">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W62">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X62">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y62">
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C63">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A63" s="15"/>
+      <c r="B63" s="16"/>
+      <c r="C63" s="15">
         <v>59</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="15">
         <v>202531444</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E63" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="F63">
-        <v>100</v>
-      </c>
-      <c r="G63">
-        <v>0</v>
-      </c>
-      <c r="H63">
-        <v>100</v>
-      </c>
-      <c r="I63">
+      <c r="F63" s="15">
+        <v>100</v>
+      </c>
+      <c r="G63" s="15">
+        <v>0</v>
+      </c>
+      <c r="H63" s="15">
+        <v>100</v>
+      </c>
+      <c r="I63" s="15">
         <v>90</v>
       </c>
-      <c r="J63">
-        <v>100</v>
-      </c>
-      <c r="K63">
+      <c r="J63" s="37">
+        <v>100</v>
+      </c>
+      <c r="K63" s="37">
         <v>95</v>
       </c>
-      <c r="L63">
-        <v>100</v>
-      </c>
-      <c r="M63">
-        <v>100</v>
-      </c>
-      <c r="N63">
+      <c r="L63" s="15">
+        <v>100</v>
+      </c>
+      <c r="M63" s="15">
+        <v>100</v>
+      </c>
+      <c r="N63" s="37">
         <v>50</v>
       </c>
-      <c r="O63">
-        <v>0</v>
-      </c>
-      <c r="P63">
+      <c r="O63" s="15">
+        <v>0</v>
+      </c>
+      <c r="P63" s="37">
         <v>65</v>
       </c>
       <c r="Q63" s="14">
         <f>IF([1]punteo!L64="",0,[1]punteo!L64)</f>
         <v>100</v>
       </c>
-      <c r="R63" s="14">
+      <c r="R63" s="10">
         <f>IF([2]punteo!L64="",0,[2]punteo!L64)</f>
         <v>100</v>
       </c>
-      <c r="S63" s="14">
+      <c r="S63" s="10">
         <f>IF([3]punteo!L64="",0,[3]punteo!L64)</f>
         <v>100</v>
       </c>
-      <c r="T63" s="14"/>
-      <c r="U63" s="14">
-        <f>IF([4]punteo!L64="",0,[4]punteo!L64)</f>
-        <v>0</v>
-      </c>
-      <c r="V63" s="14"/>
+      <c r="T63" s="10"/>
+      <c r="U63" s="10"/>
+      <c r="V63">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W63">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="X63">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y63">
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C64">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A64" s="15"/>
+      <c r="B64" s="16"/>
+      <c r="C64" s="15">
         <v>60</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="15">
         <v>202531566</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E64" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="F64">
-        <v>100</v>
-      </c>
-      <c r="G64">
-        <v>0</v>
-      </c>
-      <c r="H64">
-        <v>100</v>
-      </c>
-      <c r="I64">
+      <c r="F64" s="15">
+        <v>100</v>
+      </c>
+      <c r="G64" s="15">
+        <v>0</v>
+      </c>
+      <c r="H64" s="15">
+        <v>100</v>
+      </c>
+      <c r="I64" s="15">
         <v>90</v>
       </c>
-      <c r="J64">
-        <v>100</v>
-      </c>
-      <c r="K64">
+      <c r="J64" s="37">
+        <v>100</v>
+      </c>
+      <c r="K64" s="37">
         <v>85</v>
       </c>
-      <c r="L64">
-        <v>100</v>
-      </c>
-      <c r="M64">
-        <v>100</v>
-      </c>
-      <c r="N64">
+      <c r="L64" s="15">
+        <v>100</v>
+      </c>
+      <c r="M64" s="15">
+        <v>100</v>
+      </c>
+      <c r="N64" s="37">
         <v>70</v>
       </c>
-      <c r="O64">
+      <c r="O64" s="15">
         <v>75</v>
       </c>
-      <c r="P64">
+      <c r="P64" s="37">
         <v>55</v>
       </c>
       <c r="Q64" s="14">
         <f>IF([1]punteo!L65="",0,[1]punteo!L65)</f>
         <v>95</v>
       </c>
-      <c r="R64" s="14">
+      <c r="R64" s="10">
         <f>IF([2]punteo!L65="",0,[2]punteo!L65)</f>
         <v>100</v>
       </c>
-      <c r="S64" s="14">
+      <c r="S64" s="10">
         <f>IF([3]punteo!L65="",0,[3]punteo!L65)</f>
         <v>100</v>
       </c>
-      <c r="T64" s="14"/>
-      <c r="U64" s="14">
-        <f>IF([4]punteo!L65="",0,[4]punteo!L65)</f>
-        <v>0</v>
-      </c>
-      <c r="V64" s="14"/>
+      <c r="T64" s="10"/>
+      <c r="U64" s="10"/>
+      <c r="V64">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W64">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X64">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y64">
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A65" s="6">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A65" s="38">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B65" s="13" t="s">
+      <c r="B65" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="15">
         <v>61</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="15">
         <v>202531611</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E65" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="F65">
-        <v>100</v>
-      </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
-      <c r="H65">
-        <v>100</v>
-      </c>
-      <c r="I65">
-        <v>0</v>
-      </c>
-      <c r="J65">
-        <v>0</v>
-      </c>
-      <c r="K65">
-        <v>0</v>
-      </c>
-      <c r="L65">
-        <v>100</v>
-      </c>
-      <c r="M65">
-        <v>100</v>
-      </c>
-      <c r="N65">
+      <c r="F65" s="15">
+        <v>100</v>
+      </c>
+      <c r="G65" s="15">
+        <v>0</v>
+      </c>
+      <c r="H65" s="15">
+        <v>100</v>
+      </c>
+      <c r="I65" s="15">
+        <v>0</v>
+      </c>
+      <c r="J65" s="37">
+        <v>75</v>
+      </c>
+      <c r="K65" s="37">
+        <v>100</v>
+      </c>
+      <c r="L65" s="15">
+        <v>100</v>
+      </c>
+      <c r="M65" s="15">
+        <v>100</v>
+      </c>
+      <c r="N65" s="37">
         <v>70</v>
       </c>
-      <c r="O65">
+      <c r="O65" s="15">
         <v>45</v>
       </c>
-      <c r="P65">
+      <c r="P65" s="37">
         <v>75</v>
       </c>
       <c r="Q65" s="14">
         <f>IF([1]punteo!L66="",0,[1]punteo!L66)</f>
         <v>0</v>
       </c>
-      <c r="R65" s="14">
+      <c r="R65" s="10">
         <f>IF([2]punteo!L66="",0,[2]punteo!L66)</f>
         <v>0</v>
       </c>
-      <c r="S65" s="14">
+      <c r="S65" s="10">
         <f>IF([3]punteo!L66="",0,[3]punteo!L66)</f>
         <v>100</v>
       </c>
-      <c r="T65" s="14"/>
-      <c r="U65" s="14">
-        <f>IF([4]punteo!L66="",0,[4]punteo!L66)</f>
-        <v>0</v>
-      </c>
-      <c r="V65" s="14"/>
+      <c r="T65" s="10"/>
+      <c r="U65" s="10"/>
+      <c r="V65">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W65">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X65">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y65">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="C66">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A66" s="15"/>
+      <c r="B66" s="16"/>
+      <c r="C66" s="15">
         <v>62</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="15">
         <v>202531645</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E66" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="F66">
-        <v>100</v>
-      </c>
-      <c r="G66">
-        <v>100</v>
-      </c>
-      <c r="H66">
-        <v>100</v>
-      </c>
-      <c r="I66">
+      <c r="F66" s="15">
+        <v>100</v>
+      </c>
+      <c r="G66" s="15">
+        <v>100</v>
+      </c>
+      <c r="H66" s="15">
+        <v>100</v>
+      </c>
+      <c r="I66" s="15">
         <v>90</v>
       </c>
-      <c r="J66">
-        <v>100</v>
-      </c>
-      <c r="K66">
-        <v>100</v>
-      </c>
-      <c r="L66">
-        <v>100</v>
-      </c>
-      <c r="M66">
-        <v>0</v>
-      </c>
-      <c r="N66">
-        <v>0</v>
-      </c>
-      <c r="O66">
+      <c r="J66" s="37">
+        <v>100</v>
+      </c>
+      <c r="K66" s="37">
+        <v>100</v>
+      </c>
+      <c r="L66" s="15">
+        <v>100</v>
+      </c>
+      <c r="M66" s="15">
+        <v>0</v>
+      </c>
+      <c r="N66" s="37">
+        <v>0</v>
+      </c>
+      <c r="O66" s="15">
         <v>90</v>
       </c>
-      <c r="P66">
+      <c r="P66" s="37">
         <v>100</v>
       </c>
       <c r="Q66" s="14">
         <f>IF([1]punteo!L67="",0,[1]punteo!L67)</f>
         <v>90</v>
       </c>
-      <c r="R66" s="14">
+      <c r="R66" s="10">
         <f>IF([2]punteo!L67="",0,[2]punteo!L67)</f>
         <v>100</v>
       </c>
-      <c r="S66" s="14">
+      <c r="S66" s="10">
         <f>IF([3]punteo!L67="",0,[3]punteo!L67)</f>
         <v>100</v>
       </c>
-      <c r="T66" s="14"/>
-      <c r="U66" s="14">
-        <f>IF([4]punteo!L67="",0,[4]punteo!L67)</f>
-        <v>0</v>
-      </c>
-      <c r="V66" s="14"/>
+      <c r="T66" s="10"/>
+      <c r="U66" s="10"/>
+      <c r="V66">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W66">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X66">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y66">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="C67">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A67" s="15"/>
+      <c r="B67" s="16"/>
+      <c r="C67" s="15">
         <v>63</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="15">
         <v>202531663</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E67" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="F67">
-        <v>100</v>
-      </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
-      <c r="H67">
-        <v>0</v>
-      </c>
-      <c r="I67">
-        <v>0</v>
-      </c>
-      <c r="J67">
-        <v>0</v>
-      </c>
-      <c r="K67">
-        <v>0</v>
-      </c>
-      <c r="L67">
-        <v>0</v>
-      </c>
-      <c r="M67">
-        <v>0</v>
-      </c>
-      <c r="N67">
-        <v>0</v>
-      </c>
-      <c r="O67">
-        <v>0</v>
-      </c>
-      <c r="P67">
+      <c r="F67" s="15">
+        <v>100</v>
+      </c>
+      <c r="G67" s="15">
+        <v>0</v>
+      </c>
+      <c r="H67" s="15">
+        <v>0</v>
+      </c>
+      <c r="I67" s="15">
+        <v>0</v>
+      </c>
+      <c r="J67" s="37">
+        <v>0</v>
+      </c>
+      <c r="K67" s="37">
+        <v>0</v>
+      </c>
+      <c r="L67" s="15">
+        <v>0</v>
+      </c>
+      <c r="M67" s="15">
+        <v>0</v>
+      </c>
+      <c r="N67" s="37">
+        <v>0</v>
+      </c>
+      <c r="O67" s="15">
+        <v>0</v>
+      </c>
+      <c r="P67" s="37">
         <v>0</v>
       </c>
       <c r="Q67" s="14">
         <f>IF([1]punteo!L68="",0,[1]punteo!L68)</f>
         <v>0</v>
       </c>
-      <c r="R67" s="14">
+      <c r="R67" s="10">
         <f>IF([2]punteo!L68="",0,[2]punteo!L68)</f>
         <v>0</v>
       </c>
-      <c r="S67" s="14">
+      <c r="S67" s="10">
         <f>IF([3]punteo!L68="",0,[3]punteo!L68)</f>
         <v>0</v>
       </c>
-      <c r="T67" s="14"/>
-      <c r="U67" s="14">
-        <f>IF([4]punteo!L68="",0,[4]punteo!L68)</f>
-        <v>0</v>
-      </c>
-      <c r="V67" s="14"/>
+      <c r="T67" s="10"/>
+      <c r="U67" s="10"/>
+      <c r="V67">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="W67">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X67">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y67">
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="C68">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A68" s="15"/>
+      <c r="B68" s="16"/>
+      <c r="C68" s="15">
         <v>64</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="15">
         <v>202531724</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E68" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="F68">
-        <v>100</v>
-      </c>
-      <c r="G68">
-        <v>0</v>
-      </c>
-      <c r="H68">
+      <c r="F68" s="15">
+        <v>100</v>
+      </c>
+      <c r="G68" s="15">
+        <v>0</v>
+      </c>
+      <c r="H68" s="15">
         <v>50</v>
       </c>
-      <c r="I68">
+      <c r="I68" s="15">
         <v>90</v>
       </c>
-      <c r="J68">
+      <c r="J68" s="37">
         <v>40</v>
       </c>
-      <c r="K68">
+      <c r="K68" s="37">
         <v>85</v>
       </c>
-      <c r="L68">
-        <v>100</v>
-      </c>
-      <c r="M68">
-        <v>100</v>
-      </c>
-      <c r="N68">
+      <c r="L68" s="15">
+        <v>100</v>
+      </c>
+      <c r="M68" s="15">
+        <v>100</v>
+      </c>
+      <c r="N68" s="37">
         <v>70</v>
       </c>
-      <c r="O68">
+      <c r="O68" s="15">
         <v>75</v>
       </c>
-      <c r="P68">
+      <c r="P68" s="37">
         <v>70</v>
       </c>
       <c r="Q68" s="14">
         <f>IF([1]punteo!L69="",0,[1]punteo!L69)</f>
         <v>100</v>
       </c>
-      <c r="R68" s="14">
+      <c r="R68" s="10">
         <f>IF([2]punteo!L69="",0,[2]punteo!L69)</f>
         <v>100</v>
       </c>
-      <c r="S68" s="14">
+      <c r="S68" s="10">
         <f>IF([3]punteo!L69="",0,[3]punteo!L69)</f>
         <v>100</v>
       </c>
-      <c r="T68" s="14"/>
-      <c r="U68" s="14">
-        <f>IF([4]punteo!L69="",0,[4]punteo!L69)</f>
-        <v>0</v>
-      </c>
-      <c r="V68" s="14"/>
+      <c r="T68" s="10"/>
+      <c r="U68" s="10"/>
+      <c r="V68">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W68">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X68">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y68">
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="C69">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A69" s="15"/>
+      <c r="B69" s="16"/>
+      <c r="C69" s="15">
         <v>65</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="15">
         <v>202531736</v>
       </c>
-      <c r="E69" t="s">
+      <c r="E69" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="F69">
-        <v>100</v>
-      </c>
-      <c r="G69">
-        <v>0</v>
-      </c>
-      <c r="H69">
-        <v>100</v>
-      </c>
-      <c r="I69">
-        <v>0</v>
-      </c>
-      <c r="J69">
-        <v>0</v>
-      </c>
-      <c r="K69">
-        <v>100</v>
-      </c>
-      <c r="L69">
-        <v>100</v>
-      </c>
-      <c r="M69">
-        <v>100</v>
-      </c>
-      <c r="N69">
-        <v>0</v>
-      </c>
-      <c r="O69">
+      <c r="F69" s="15">
+        <v>100</v>
+      </c>
+      <c r="G69" s="15">
+        <v>0</v>
+      </c>
+      <c r="H69" s="15">
+        <v>100</v>
+      </c>
+      <c r="I69" s="15">
+        <v>0</v>
+      </c>
+      <c r="J69" s="37">
+        <v>0</v>
+      </c>
+      <c r="K69" s="37">
+        <v>100</v>
+      </c>
+      <c r="L69" s="15">
+        <v>100</v>
+      </c>
+      <c r="M69" s="15">
+        <v>100</v>
+      </c>
+      <c r="N69" s="37">
+        <v>0</v>
+      </c>
+      <c r="O69" s="15">
         <v>60</v>
       </c>
-      <c r="P69">
+      <c r="P69" s="37">
         <v>65</v>
       </c>
       <c r="Q69" s="14">
         <f>IF([1]punteo!L70="",0,[1]punteo!L70)</f>
         <v>80</v>
       </c>
-      <c r="R69" s="14">
+      <c r="R69" s="10">
         <f>IF([2]punteo!L70="",0,[2]punteo!L70)</f>
         <v>100</v>
       </c>
-      <c r="S69" s="14">
+      <c r="S69" s="10">
         <f>IF([3]punteo!L70="",0,[3]punteo!L70)</f>
         <v>100</v>
       </c>
-      <c r="T69" s="14"/>
-      <c r="U69" s="14">
-        <f>IF([4]punteo!L70="",0,[4]punteo!L70)</f>
-        <v>0</v>
-      </c>
-      <c r="V69" s="14"/>
+      <c r="T69" s="10"/>
+      <c r="U69" s="10"/>
+      <c r="V69">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="W69">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X69">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y69">
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A70" s="6">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A70" s="38">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B70" s="13" t="s">
+      <c r="B70" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="15">
         <v>66</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="15">
         <v>202531778</v>
       </c>
-      <c r="E70" t="s">
+      <c r="E70" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="F70">
-        <v>100</v>
-      </c>
-      <c r="G70">
-        <v>0</v>
-      </c>
-      <c r="H70">
-        <v>100</v>
-      </c>
-      <c r="I70">
+      <c r="F70" s="15">
+        <v>100</v>
+      </c>
+      <c r="G70" s="15">
+        <v>0</v>
+      </c>
+      <c r="H70" s="15">
+        <v>100</v>
+      </c>
+      <c r="I70" s="15">
         <v>90</v>
       </c>
-      <c r="J70">
+      <c r="J70" s="37">
         <v>75</v>
       </c>
-      <c r="K70">
+      <c r="K70" s="37">
         <v>85</v>
       </c>
-      <c r="L70">
-        <v>100</v>
-      </c>
-      <c r="M70">
-        <v>100</v>
-      </c>
-      <c r="N70">
+      <c r="L70" s="15">
+        <v>100</v>
+      </c>
+      <c r="M70" s="15">
+        <v>100</v>
+      </c>
+      <c r="N70" s="37">
         <v>70</v>
       </c>
-      <c r="O70">
+      <c r="O70" s="15">
         <v>90</v>
       </c>
-      <c r="P70">
+      <c r="P70" s="37">
         <v>100</v>
       </c>
       <c r="Q70" s="14">
         <f>IF([1]punteo!L71="",0,[1]punteo!L71)</f>
         <v>100</v>
       </c>
-      <c r="R70" s="14">
+      <c r="R70" s="10">
         <f>IF([2]punteo!L71="",0,[2]punteo!L71)</f>
         <v>100</v>
       </c>
-      <c r="S70" s="14">
+      <c r="S70" s="10">
         <f>IF([3]punteo!L71="",0,[3]punteo!L71)</f>
         <v>100</v>
       </c>
-      <c r="T70" s="14"/>
-      <c r="U70" s="14">
-        <f>IF([4]punteo!L71="",0,[4]punteo!L71)</f>
-        <v>0</v>
-      </c>
-      <c r="V70" s="14"/>
+      <c r="T70" s="10"/>
+      <c r="U70" s="10"/>
+      <c r="V70">
+        <f t="shared" ref="V70:V77" si="2">IF(O70&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
       <c r="W70">
-        <f t="shared" ref="W70:W77" si="2">IF(O70&gt;0,1,0)</f>
+        <f t="shared" ref="W70:W77" si="3">IF(P70&gt;0,1,0)</f>
         <v>1</v>
       </c>
       <c r="X70">
-        <f t="shared" ref="X70:X77" si="3">IF(P70&gt;0,1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="Y70">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="C71">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A71" s="15"/>
+      <c r="B71" s="16"/>
+      <c r="C71" s="15">
         <v>67</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="15">
         <v>202531844</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E71" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="F71">
-        <v>100</v>
-      </c>
-      <c r="G71">
-        <v>0</v>
-      </c>
-      <c r="H71">
-        <v>100</v>
-      </c>
-      <c r="I71">
-        <v>100</v>
-      </c>
-      <c r="J71">
-        <v>100</v>
-      </c>
-      <c r="K71">
-        <v>100</v>
-      </c>
-      <c r="L71">
-        <v>100</v>
-      </c>
-      <c r="M71">
-        <v>100</v>
-      </c>
-      <c r="N71">
-        <v>100</v>
-      </c>
-      <c r="O71">
-        <v>0</v>
-      </c>
-      <c r="P71">
+      <c r="F71" s="15">
+        <v>100</v>
+      </c>
+      <c r="G71" s="15">
+        <v>0</v>
+      </c>
+      <c r="H71" s="15">
+        <v>100</v>
+      </c>
+      <c r="I71" s="15">
+        <v>100</v>
+      </c>
+      <c r="J71" s="37">
+        <v>100</v>
+      </c>
+      <c r="K71" s="37">
+        <v>100</v>
+      </c>
+      <c r="L71" s="15">
+        <v>100</v>
+      </c>
+      <c r="M71" s="15">
+        <v>100</v>
+      </c>
+      <c r="N71" s="37">
+        <v>100</v>
+      </c>
+      <c r="O71" s="15">
+        <v>0</v>
+      </c>
+      <c r="P71" s="37">
         <v>100</v>
       </c>
       <c r="Q71" s="14">
         <f>IF([1]punteo!L72="",0,[1]punteo!L72)</f>
         <v>0</v>
       </c>
-      <c r="R71" s="14">
+      <c r="R71" s="10">
         <f>IF([2]punteo!L72="",0,[2]punteo!L72)</f>
         <v>0</v>
       </c>
-      <c r="S71" s="14">
+      <c r="S71" s="10">
         <f>IF([3]punteo!L72="",0,[3]punteo!L72)</f>
         <v>0</v>
       </c>
-      <c r="T71" s="14"/>
-      <c r="U71" s="14">
-        <f>IF([4]punteo!L72="",0,[4]punteo!L72)</f>
-        <v>0</v>
-      </c>
-      <c r="V71" s="14"/>
+      <c r="T71" s="10"/>
+      <c r="U71" s="10"/>
+      <c r="V71">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="W71">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="X71">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="Y71">
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="C72">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A72" s="15"/>
+      <c r="B72" s="16"/>
+      <c r="C72" s="15">
         <v>68</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="15">
         <v>202531883</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E72" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="F72">
-        <v>100</v>
-      </c>
-      <c r="G72">
-        <v>0</v>
-      </c>
-      <c r="H72">
-        <v>100</v>
-      </c>
-      <c r="I72">
-        <v>100</v>
-      </c>
-      <c r="J72">
+      <c r="F72" s="15">
+        <v>100</v>
+      </c>
+      <c r="G72" s="15">
+        <v>0</v>
+      </c>
+      <c r="H72" s="15">
+        <v>100</v>
+      </c>
+      <c r="I72" s="15">
+        <v>100</v>
+      </c>
+      <c r="J72" s="37">
         <v>85</v>
       </c>
-      <c r="K72">
-        <v>100</v>
-      </c>
-      <c r="L72">
-        <v>100</v>
-      </c>
-      <c r="M72">
-        <v>100</v>
-      </c>
-      <c r="N72">
+      <c r="K72" s="37">
+        <v>100</v>
+      </c>
+      <c r="L72" s="15">
+        <v>100</v>
+      </c>
+      <c r="M72" s="15">
+        <v>100</v>
+      </c>
+      <c r="N72" s="37">
         <v>90</v>
       </c>
-      <c r="O72">
+      <c r="O72" s="15">
         <v>95</v>
       </c>
-      <c r="P72">
+      <c r="P72" s="37">
         <v>85</v>
       </c>
       <c r="Q72" s="14">
         <f>IF([1]punteo!L73="",0,[1]punteo!L73)</f>
         <v>95</v>
       </c>
-      <c r="R72" s="14">
+      <c r="R72" s="10">
         <f>IF([2]punteo!L73="",0,[2]punteo!L73)</f>
         <v>0</v>
       </c>
-      <c r="S72" s="14">
+      <c r="S72" s="10">
         <f>IF([3]punteo!L73="",0,[3]punteo!L73)</f>
         <v>100</v>
       </c>
-      <c r="T72" s="14"/>
-      <c r="U72" s="14">
-        <f>IF([4]punteo!L73="",0,[4]punteo!L73)</f>
-        <v>100</v>
-      </c>
-      <c r="V72" s="14"/>
+      <c r="T72" s="10"/>
+      <c r="U72" s="10"/>
+      <c r="V72">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
       <c r="W72">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="X72">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="Y72">
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="C73">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A73" s="15"/>
+      <c r="B73" s="16"/>
+      <c r="C73" s="15">
         <v>69</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="15">
         <v>202531947</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E73" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="F73">
-        <v>100</v>
-      </c>
-      <c r="G73">
-        <v>0</v>
-      </c>
-      <c r="H73">
-        <v>100</v>
-      </c>
-      <c r="I73">
-        <v>0</v>
-      </c>
-      <c r="J73">
+      <c r="F73" s="15">
+        <v>100</v>
+      </c>
+      <c r="G73" s="15">
+        <v>0</v>
+      </c>
+      <c r="H73" s="15">
+        <v>100</v>
+      </c>
+      <c r="I73" s="15">
+        <v>0</v>
+      </c>
+      <c r="J73" s="37">
         <v>85</v>
       </c>
-      <c r="K73">
+      <c r="K73" s="37">
         <v>75</v>
       </c>
-      <c r="L73">
-        <v>100</v>
-      </c>
-      <c r="M73">
-        <v>100</v>
-      </c>
-      <c r="N73">
+      <c r="L73" s="15">
+        <v>100</v>
+      </c>
+      <c r="M73" s="15">
+        <v>100</v>
+      </c>
+      <c r="N73" s="37">
         <v>50</v>
       </c>
-      <c r="O73">
+      <c r="O73" s="15">
         <v>90</v>
       </c>
-      <c r="P73">
+      <c r="P73" s="37">
         <v>70</v>
       </c>
       <c r="Q73" s="14">
         <f>IF([1]punteo!L74="",0,[1]punteo!L74)</f>
         <v>0</v>
       </c>
-      <c r="R73" s="14">
+      <c r="R73" s="10">
         <f>IF([2]punteo!L74="",0,[2]punteo!L74)</f>
         <v>0</v>
       </c>
-      <c r="S73" s="14">
+      <c r="S73" s="10">
         <f>IF([3]punteo!L74="",0,[3]punteo!L74)</f>
         <v>0</v>
       </c>
-      <c r="T73" s="14"/>
-      <c r="U73" s="14">
-        <f>IF([4]punteo!L74="",0,[4]punteo!L74)</f>
-        <v>0</v>
-      </c>
-      <c r="V73" s="14"/>
+      <c r="T73" s="10"/>
+      <c r="U73" s="10"/>
+      <c r="V73">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
       <c r="W73">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="X73">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="Y73">
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A74" s="6">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A74" s="38">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B74" s="13" t="s">
+      <c r="B74" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="15">
         <v>70</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="15">
         <v>202532062</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E74" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="F74">
-        <v>0</v>
-      </c>
-      <c r="G74">
-        <v>0</v>
-      </c>
-      <c r="H74">
-        <v>100</v>
-      </c>
-      <c r="I74">
-        <v>0</v>
-      </c>
-      <c r="J74">
+      <c r="F74" s="15">
+        <v>0</v>
+      </c>
+      <c r="G74" s="15">
+        <v>0</v>
+      </c>
+      <c r="H74" s="15">
+        <v>100</v>
+      </c>
+      <c r="I74" s="15">
+        <v>0</v>
+      </c>
+      <c r="J74" s="37">
         <v>85</v>
       </c>
-      <c r="K74">
-        <v>0</v>
-      </c>
-      <c r="L74">
-        <v>100</v>
-      </c>
-      <c r="M74">
-        <v>100</v>
-      </c>
-      <c r="N74">
+      <c r="K74" s="37">
+        <v>100</v>
+      </c>
+      <c r="L74" s="15">
+        <v>100</v>
+      </c>
+      <c r="M74" s="15">
+        <v>100</v>
+      </c>
+      <c r="N74" s="37">
         <v>50</v>
       </c>
-      <c r="O74">
-        <v>0</v>
-      </c>
-      <c r="P74">
+      <c r="O74" s="15">
+        <v>0</v>
+      </c>
+      <c r="P74" s="37">
         <v>20</v>
       </c>
       <c r="Q74" s="14">
         <f>IF([1]punteo!L75="",0,[1]punteo!L75)</f>
         <v>100</v>
       </c>
-      <c r="R74" s="14">
+      <c r="R74" s="10">
         <f>IF([2]punteo!L75="",0,[2]punteo!L75)</f>
         <v>100</v>
       </c>
-      <c r="S74" s="14">
+      <c r="S74" s="10">
         <f>IF([3]punteo!L75="",0,[3]punteo!L75)</f>
         <v>100</v>
       </c>
-      <c r="T74" s="14"/>
-      <c r="U74" s="14">
-        <f>IF([4]punteo!L75="",0,[4]punteo!L75)</f>
-        <v>0</v>
-      </c>
-      <c r="V74" s="14"/>
+      <c r="T74" s="10"/>
+      <c r="U74" s="10"/>
+      <c r="V74">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="W74">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="X74">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="Y74">
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="C75">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A75" s="15"/>
+      <c r="B75" s="16"/>
+      <c r="C75" s="15">
         <v>71</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="15">
         <v>202532079</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E75" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="F75">
-        <v>0</v>
-      </c>
-      <c r="G75">
-        <v>0</v>
-      </c>
-      <c r="H75">
-        <v>100</v>
-      </c>
-      <c r="I75">
-        <v>0</v>
-      </c>
-      <c r="J75">
-        <v>0</v>
-      </c>
-      <c r="K75">
+      <c r="F75" s="15">
+        <v>0</v>
+      </c>
+      <c r="G75" s="15">
+        <v>0</v>
+      </c>
+      <c r="H75" s="15">
+        <v>100</v>
+      </c>
+      <c r="I75" s="15">
+        <v>0</v>
+      </c>
+      <c r="J75" s="37">
+        <v>0</v>
+      </c>
+      <c r="K75" s="37">
         <v>50</v>
       </c>
-      <c r="L75">
-        <v>0</v>
-      </c>
-      <c r="M75">
-        <v>0</v>
-      </c>
-      <c r="N75">
-        <v>0</v>
-      </c>
-      <c r="O75">
-        <v>0</v>
-      </c>
-      <c r="P75">
+      <c r="L75" s="15">
+        <v>0</v>
+      </c>
+      <c r="M75" s="15">
+        <v>0</v>
+      </c>
+      <c r="N75" s="37">
+        <v>0</v>
+      </c>
+      <c r="O75" s="15">
+        <v>0</v>
+      </c>
+      <c r="P75" s="37">
         <v>0</v>
       </c>
       <c r="Q75" s="14">
         <f>IF([1]punteo!L76="",0,[1]punteo!L76)</f>
         <v>0</v>
       </c>
-      <c r="R75" s="14">
+      <c r="R75" s="10">
         <f>IF([2]punteo!L76="",0,[2]punteo!L76)</f>
         <v>0</v>
       </c>
-      <c r="S75" s="14">
+      <c r="S75" s="10">
         <f>IF([3]punteo!L76="",0,[3]punteo!L76)</f>
         <v>0</v>
       </c>
-      <c r="T75" s="14"/>
-      <c r="U75" s="14">
-        <f>IF([4]punteo!L76="",0,[4]punteo!L76)</f>
-        <v>0</v>
-      </c>
-      <c r="V75" s="14"/>
+      <c r="T75" s="10"/>
+      <c r="U75" s="10"/>
+      <c r="V75">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="W75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X75">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Y75">
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="B76" s="1" t="s">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A76" s="15"/>
+      <c r="B76" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="15">
         <v>72</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="15">
         <v>202530466</v>
       </c>
-      <c r="E76" t="s">
+      <c r="E76" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="F76">
-        <v>100</v>
-      </c>
-      <c r="G76">
-        <v>0</v>
-      </c>
-      <c r="H76">
-        <v>100</v>
-      </c>
-      <c r="I76">
-        <v>100</v>
-      </c>
-      <c r="J76">
-        <v>100</v>
-      </c>
-      <c r="K76">
-        <v>100</v>
-      </c>
-      <c r="L76">
-        <v>100</v>
-      </c>
-      <c r="M76">
-        <v>100</v>
-      </c>
-      <c r="N76">
-        <v>100</v>
-      </c>
-      <c r="O76">
-        <v>100</v>
-      </c>
-      <c r="P76">
+      <c r="F76" s="15">
+        <v>100</v>
+      </c>
+      <c r="G76" s="15">
+        <v>0</v>
+      </c>
+      <c r="H76" s="15">
+        <v>100</v>
+      </c>
+      <c r="I76" s="15">
+        <v>100</v>
+      </c>
+      <c r="J76" s="37">
+        <v>100</v>
+      </c>
+      <c r="K76" s="37">
+        <v>100</v>
+      </c>
+      <c r="L76" s="15">
+        <v>100</v>
+      </c>
+      <c r="M76" s="15">
+        <v>100</v>
+      </c>
+      <c r="N76" s="37">
+        <v>100</v>
+      </c>
+      <c r="O76" s="15">
+        <v>100</v>
+      </c>
+      <c r="P76" s="37">
         <v>100</v>
       </c>
       <c r="Q76" s="14">
         <f>IF([1]punteo!L77="",0,[1]punteo!L77)</f>
         <v>100</v>
       </c>
-      <c r="R76" s="14">
+      <c r="R76" s="10">
         <f>IF([2]punteo!L77="",0,[2]punteo!L77)</f>
         <v>100</v>
       </c>
-      <c r="S76" s="14">
+      <c r="S76" s="10">
         <f>IF([3]punteo!L77="",0,[3]punteo!L77)</f>
         <v>100</v>
       </c>
-      <c r="T76" s="14"/>
-      <c r="U76" s="14">
-        <f>IF([4]punteo!L77="",0,[4]punteo!L77)</f>
-        <v>0</v>
-      </c>
-      <c r="V76" s="14"/>
+      <c r="T76" s="10"/>
+      <c r="U76" s="10"/>
+      <c r="V76">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
       <c r="W76">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="X76">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="Y76">
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="B77" s="1" t="s">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A77" s="15"/>
+      <c r="B77" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="15">
         <v>73</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="15">
         <v>202030192</v>
       </c>
-      <c r="E77" t="s">
+      <c r="E77" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="F77">
-        <v>0</v>
-      </c>
-      <c r="G77">
-        <v>0</v>
-      </c>
-      <c r="H77">
+      <c r="F77" s="15">
+        <v>0</v>
+      </c>
+      <c r="G77" s="15">
+        <v>0</v>
+      </c>
+      <c r="H77" s="15">
         <v>50</v>
       </c>
-      <c r="I77">
+      <c r="I77" s="15">
         <v>75</v>
       </c>
-      <c r="J77">
-        <v>0</v>
-      </c>
-      <c r="K77">
-        <v>100</v>
-      </c>
-      <c r="L77">
-        <v>100</v>
-      </c>
-      <c r="M77">
-        <v>100</v>
-      </c>
-      <c r="N77">
-        <v>100</v>
-      </c>
-      <c r="O77">
+      <c r="J77" s="37">
+        <v>0</v>
+      </c>
+      <c r="K77" s="37">
+        <v>100</v>
+      </c>
+      <c r="L77" s="15">
+        <v>100</v>
+      </c>
+      <c r="M77" s="15">
+        <v>100</v>
+      </c>
+      <c r="N77" s="37">
+        <v>100</v>
+      </c>
+      <c r="O77" s="15">
         <v>85</v>
       </c>
-      <c r="P77">
+      <c r="P77" s="37">
         <v>0</v>
       </c>
       <c r="Q77" s="14">
         <f>IF([1]punteo!L78="",0,[1]punteo!L78)</f>
         <v>0</v>
       </c>
-      <c r="R77" s="14">
+      <c r="R77" s="10">
         <f>IF([2]punteo!L78="",0,[2]punteo!L78)</f>
         <v>0</v>
       </c>
-      <c r="S77" s="14">
+      <c r="S77" s="10">
         <f>IF([3]punteo!L78="",0,[3]punteo!L78)</f>
         <v>0</v>
       </c>
-      <c r="T77" s="14"/>
-      <c r="U77" s="14">
-        <f>IF([4]punteo!L78="",0,[4]punteo!L78)</f>
-        <v>0</v>
-      </c>
-      <c r="V77" s="14"/>
+      <c r="T77" s="10"/>
+      <c r="U77" s="10"/>
+      <c r="V77">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
       <c r="W77">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="X77">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Y77">
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="C78" s="8" t="s">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A78" s="15"/>
+      <c r="B78" s="16"/>
+      <c r="C78" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="10">
+      <c r="D78" s="40"/>
+      <c r="E78" s="40"/>
+      <c r="F78" s="41">
         <f t="shared" ref="F78:N78" si="4">COUNTIF(F5:F77,"&gt;0")</f>
         <v>49</v>
       </c>
-      <c r="G78" s="10">
+      <c r="G78" s="41">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="H78" s="10">
+      <c r="H78" s="41">
         <f t="shared" si="4"/>
         <v>59</v>
       </c>
-      <c r="I78" s="10">
+      <c r="I78" s="41">
         <f t="shared" si="4"/>
-        <v>46</v>
-      </c>
-      <c r="J78" s="10">
+        <v>47</v>
+      </c>
+      <c r="J78" s="42">
         <f t="shared" si="4"/>
-        <v>52</v>
-      </c>
-      <c r="K78" s="10">
+        <v>57</v>
+      </c>
+      <c r="K78" s="42">
         <f t="shared" si="4"/>
-        <v>52</v>
-      </c>
-      <c r="L78" s="10">
+        <v>62</v>
+      </c>
+      <c r="L78" s="41">
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="M78" s="10">
+      <c r="M78" s="41">
         <f t="shared" si="4"/>
         <v>61</v>
       </c>
-      <c r="N78" s="10">
+      <c r="N78" s="42">
         <f t="shared" si="4"/>
-        <v>57</v>
-      </c>
-      <c r="O78" s="10">
+        <v>58</v>
+      </c>
+      <c r="O78" s="41">
         <f>COUNTIF(O5:O77,"&gt;0")</f>
         <v>52</v>
       </c>
-      <c r="P78" s="11">
+      <c r="P78" s="43">
         <f>COUNTIF(P5:P77,"&gt;0")</f>
         <v>60</v>
       </c>
-      <c r="Q78" s="11">
+      <c r="Q78" s="43">
         <f>COUNTIF(Q5:Q77,"&gt;0")</f>
-        <v>49</v>
-      </c>
-      <c r="R78" s="11">
+        <v>50</v>
+      </c>
+      <c r="R78" s="17">
         <f t="shared" ref="R78:S78" si="5">COUNTIF(R5:R77,"&gt;0")</f>
         <v>41</v>
       </c>
-      <c r="S78" s="11">
+      <c r="S78" s="17">
         <f t="shared" si="5"/>
         <v>52</v>
       </c>
-      <c r="T78" s="10"/>
-      <c r="U78" s="9"/>
-      <c r="V78" s="9"/>
-      <c r="W78" s="9"/>
-      <c r="X78" s="9"/>
-      <c r="Y78" s="9"/>
-      <c r="Z78" s="12"/>
+      <c r="T78" s="41"/>
+      <c r="U78" s="7"/>
+      <c r="V78" s="7"/>
+      <c r="W78" s="7"/>
+      <c r="X78" s="7"/>
+      <c r="Y78" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="X2:Y2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/PRACTICAS DOCENCIA/LABORATORIO MB1/LISTADO COMPLETO MACROS/PUNTEOS FINALES.xlsx
+++ b/PRACTICAS DOCENCIA/LABORATORIO MB1/LISTADO COMPLETO MACROS/PUNTEOS FINALES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ubicacion C a D\Documentos\gitPrimer-Semetre-25\PRACTICAS DOCENCIA\LABORATORIO MB1\LISTADO COMPLETO MACROS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B1BF53-31BC-4FEA-AEFB-C35F3C2BEDFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A958DA8F-B4AA-4B2D-99EF-6F4F6CC4863B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{F4BDE4DC-E94C-4D9E-A851-8F281B73FE4C}"/>
   </bookViews>
@@ -598,7 +598,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -616,12 +616,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -634,12 +628,6 @@
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -657,12 +645,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -672,19 +654,26 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="20" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="20" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -713,7 +702,7 @@
       <sheetName val="punteo"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="6">
           <cell r="L6">
@@ -2155,12 +2144,9 @@
     <col min="4" max="4" width="12.6328125" customWidth="1"/>
     <col min="5" max="5" width="33.90625" customWidth="1"/>
     <col min="6" max="9" width="7.453125" customWidth="1"/>
-    <col min="10" max="11" width="9.6328125" style="13" customWidth="1"/>
-    <col min="12" max="13" width="9.6328125" customWidth="1"/>
-    <col min="14" max="14" width="9.6328125" style="13" customWidth="1"/>
-    <col min="15" max="15" width="9.6328125" customWidth="1"/>
-    <col min="16" max="17" width="9.6328125" style="13" customWidth="1"/>
-    <col min="18" max="20" width="9.6328125" customWidth="1"/>
+    <col min="10" max="13" width="9.6328125" customWidth="1"/>
+    <col min="14" max="14" width="9.6328125" style="31" customWidth="1"/>
+    <col min="15" max="20" width="9.6328125" customWidth="1"/>
     <col min="21" max="21" width="27.26953125" customWidth="1"/>
     <col min="22" max="23" width="31.81640625" customWidth="1"/>
     <col min="24" max="24" width="22.81640625" customWidth="1"/>
@@ -2168,55 +2154,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="1:25" ht="109" x14ac:dyDescent="0.35">
-      <c r="A2" s="15"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="20" t="s">
+    <row r="2" spans="1:25" ht="108" x14ac:dyDescent="0.35">
+      <c r="A2" s="11"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="I2" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="J2" s="23" t="s">
+      <c r="J2" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="K2" s="24" t="s">
+      <c r="K2" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="L2" s="21" t="s">
+      <c r="L2" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="N2" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="O2" s="21" t="s">
+      <c r="N2" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="O2" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="P2" s="24" t="s">
+      <c r="P2" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="Q2" s="24" t="s">
+      <c r="Q2" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="R2" s="21" t="s">
+      <c r="R2" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="S2" s="21" t="s">
+      <c r="S2" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="22" t="s">
+      <c r="T2" s="18" t="s">
         <v>106</v>
       </c>
       <c r="V2" s="5" t="s">
@@ -2225,62 +2211,62 @@
       <c r="W2" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="X2" s="11" t="s">
+      <c r="X2" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="Y2" s="11"/>
+      <c r="Y2" s="30"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A3" s="15"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="26" t="s">
+      <c r="A3" s="11"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="F3" s="27">
+      <c r="F3" s="21">
         <v>0.5</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3" s="22">
         <v>0.5</v>
       </c>
-      <c r="H3" s="28">
+      <c r="H3" s="22">
         <v>0.5</v>
       </c>
-      <c r="I3" s="29">
+      <c r="I3" s="23">
         <v>0.5</v>
       </c>
-      <c r="J3" s="30">
-        <v>1</v>
-      </c>
-      <c r="K3" s="31">
-        <v>1</v>
-      </c>
-      <c r="L3" s="28">
-        <v>1</v>
-      </c>
-      <c r="M3" s="28">
+      <c r="J3" s="21">
+        <v>1</v>
+      </c>
+      <c r="K3" s="22">
+        <v>1</v>
+      </c>
+      <c r="L3" s="22">
+        <v>1</v>
+      </c>
+      <c r="M3" s="22">
         <v>1.5</v>
       </c>
-      <c r="N3" s="31">
+      <c r="N3" s="33">
         <v>2</v>
       </c>
-      <c r="O3" s="28">
+      <c r="O3" s="22">
         <v>2</v>
       </c>
-      <c r="P3" s="31">
+      <c r="P3" s="22">
         <v>2</v>
       </c>
-      <c r="Q3" s="31">
-        <v>1</v>
-      </c>
-      <c r="R3" s="28">
+      <c r="Q3" s="22">
+        <v>1</v>
+      </c>
+      <c r="R3" s="22">
         <v>1.5</v>
       </c>
-      <c r="S3" s="28">
+      <c r="S3" s="22">
         <v>5</v>
       </c>
-      <c r="T3" s="29">
+      <c r="T3" s="23">
         <f>SUM(F3:S3)</f>
         <v>20</v>
       </c>
@@ -2298,60 +2284,60 @@
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A4" s="15"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="19" t="s">
+      <c r="A4" s="11"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="32" t="s">
+      <c r="F4" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="G4" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="H4" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="I4" s="34" t="s">
+      <c r="I4" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="J4" s="35" t="s">
+      <c r="J4" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="L4" s="33" t="s">
+      <c r="L4" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="M4" s="33" t="s">
+      <c r="M4" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="N4" s="36" t="s">
+      <c r="N4" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="O4" s="33" t="s">
+      <c r="O4" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="P4" s="36" t="s">
+      <c r="P4" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="Q4" s="36" t="s">
+      <c r="Q4" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="R4" s="33" t="s">
+      <c r="R4" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="S4" s="33" t="s">
+      <c r="S4" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="T4" s="34" t="s">
+      <c r="T4" s="26" t="s">
         <v>114</v>
       </c>
       <c r="U4" s="4"/>
@@ -2369,51 +2355,51 @@
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A5" s="15"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="15">
-        <v>1</v>
-      </c>
-      <c r="D5" s="15">
+      <c r="A5" s="11"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="11">
+        <v>1</v>
+      </c>
+      <c r="D5" s="11">
         <v>202030174</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="15">
-        <v>0</v>
-      </c>
-      <c r="G5" s="15">
-        <v>0</v>
-      </c>
-      <c r="H5" s="15">
+      <c r="F5" s="11">
+        <v>0</v>
+      </c>
+      <c r="G5" s="11">
+        <v>0</v>
+      </c>
+      <c r="H5" s="11">
         <v>50</v>
       </c>
-      <c r="I5" s="15">
-        <v>0</v>
-      </c>
-      <c r="J5" s="37">
-        <v>0</v>
-      </c>
-      <c r="K5" s="37">
-        <v>0</v>
-      </c>
-      <c r="L5" s="15">
-        <v>0</v>
-      </c>
-      <c r="M5" s="15">
-        <v>100</v>
-      </c>
-      <c r="N5" s="37">
-        <v>0</v>
-      </c>
-      <c r="O5" s="15">
-        <v>0</v>
-      </c>
-      <c r="P5" s="37">
-        <v>100</v>
-      </c>
-      <c r="Q5" s="14">
+      <c r="I5" s="11">
+        <v>0</v>
+      </c>
+      <c r="J5" s="11">
+        <v>0</v>
+      </c>
+      <c r="K5" s="11">
+        <v>0</v>
+      </c>
+      <c r="L5" s="11">
+        <v>0</v>
+      </c>
+      <c r="M5" s="11">
+        <v>100</v>
+      </c>
+      <c r="N5" s="35">
+        <v>0</v>
+      </c>
+      <c r="O5" s="11">
+        <v>0</v>
+      </c>
+      <c r="P5" s="11">
+        <v>100</v>
+      </c>
+      <c r="Q5" s="10">
         <f>IF([1]punteo!L6="",0,[1]punteo!L6)</f>
         <v>0</v>
       </c>
@@ -2440,51 +2426,51 @@
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A6" s="15"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="15">
+      <c r="A6" s="11"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="11">
         <v>2</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="11">
         <v>202032032</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="15">
-        <v>100</v>
-      </c>
-      <c r="G6" s="15">
-        <v>0</v>
-      </c>
-      <c r="H6" s="15">
+      <c r="F6" s="11">
+        <v>100</v>
+      </c>
+      <c r="G6" s="11">
+        <v>0</v>
+      </c>
+      <c r="H6" s="11">
         <v>50</v>
       </c>
-      <c r="I6" s="15">
-        <v>100</v>
-      </c>
-      <c r="J6" s="37">
-        <v>100</v>
-      </c>
-      <c r="K6" s="37">
-        <v>100</v>
-      </c>
-      <c r="L6" s="15">
-        <v>100</v>
-      </c>
-      <c r="M6" s="15">
-        <v>100</v>
-      </c>
-      <c r="N6" s="37">
+      <c r="I6" s="11">
+        <v>100</v>
+      </c>
+      <c r="J6" s="11">
+        <v>100</v>
+      </c>
+      <c r="K6" s="11">
+        <v>100</v>
+      </c>
+      <c r="L6" s="11">
+        <v>100</v>
+      </c>
+      <c r="M6" s="11">
+        <v>100</v>
+      </c>
+      <c r="N6" s="35">
         <v>80</v>
       </c>
-      <c r="O6" s="15">
-        <v>100</v>
-      </c>
-      <c r="P6" s="37">
-        <v>100</v>
-      </c>
-      <c r="Q6" s="14">
+      <c r="O6" s="11">
+        <v>100</v>
+      </c>
+      <c r="P6" s="11">
+        <v>100</v>
+      </c>
+      <c r="Q6" s="10">
         <f>IF([1]punteo!L7="",0,[1]punteo!L7)</f>
         <v>100</v>
       </c>
@@ -2511,51 +2497,51 @@
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A7" s="15"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="15">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="11">
         <v>3</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="11">
         <v>202231116</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="15">
-        <v>100</v>
-      </c>
-      <c r="G7" s="15">
-        <v>0</v>
-      </c>
-      <c r="H7" s="15">
-        <v>100</v>
-      </c>
-      <c r="I7" s="15">
-        <v>0</v>
-      </c>
-      <c r="J7" s="37">
+      <c r="F7" s="11">
+        <v>100</v>
+      </c>
+      <c r="G7" s="11">
+        <v>0</v>
+      </c>
+      <c r="H7" s="11">
+        <v>100</v>
+      </c>
+      <c r="I7" s="11">
+        <v>0</v>
+      </c>
+      <c r="J7" s="11">
         <v>85</v>
       </c>
-      <c r="K7" s="37">
-        <v>100</v>
-      </c>
-      <c r="L7" s="15">
-        <v>100</v>
-      </c>
-      <c r="M7" s="15">
-        <v>100</v>
-      </c>
-      <c r="N7" s="37">
+      <c r="K7" s="11">
+        <v>100</v>
+      </c>
+      <c r="L7" s="11">
+        <v>100</v>
+      </c>
+      <c r="M7" s="11">
+        <v>100</v>
+      </c>
+      <c r="N7" s="35">
         <v>70</v>
       </c>
-      <c r="O7" s="15">
-        <v>0</v>
-      </c>
-      <c r="P7" s="37">
+      <c r="O7" s="11">
+        <v>0</v>
+      </c>
+      <c r="P7" s="11">
         <v>85</v>
       </c>
-      <c r="Q7" s="14">
+      <c r="Q7" s="10">
         <f>IF([1]punteo!L8="",0,[1]punteo!L8)</f>
         <v>80</v>
       </c>
@@ -2582,51 +2568,51 @@
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A8" s="15"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="15">
+      <c r="A8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="11">
         <v>4</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="11">
         <v>202330276</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="15">
-        <v>0</v>
-      </c>
-      <c r="G8" s="15">
-        <v>0</v>
-      </c>
-      <c r="H8" s="15">
-        <v>0</v>
-      </c>
-      <c r="I8" s="15">
-        <v>0</v>
-      </c>
-      <c r="J8" s="37">
-        <v>0</v>
-      </c>
-      <c r="K8" s="37">
-        <v>0</v>
-      </c>
-      <c r="L8" s="15">
-        <v>0</v>
-      </c>
-      <c r="M8" s="15">
-        <v>0</v>
-      </c>
-      <c r="N8" s="37">
-        <v>0</v>
-      </c>
-      <c r="O8" s="15">
-        <v>0</v>
-      </c>
-      <c r="P8" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="14">
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>0</v>
+      </c>
+      <c r="H8" s="11">
+        <v>0</v>
+      </c>
+      <c r="I8" s="11">
+        <v>0</v>
+      </c>
+      <c r="J8" s="11">
+        <v>0</v>
+      </c>
+      <c r="K8" s="11">
+        <v>0</v>
+      </c>
+      <c r="L8" s="11">
+        <v>0</v>
+      </c>
+      <c r="M8" s="11">
+        <v>0</v>
+      </c>
+      <c r="N8" s="35">
+        <v>0</v>
+      </c>
+      <c r="O8" s="11">
+        <v>0</v>
+      </c>
+      <c r="P8" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="10">
         <f>IF([1]punteo!L9="",0,[1]punteo!L9)</f>
         <v>0</v>
       </c>
@@ -2653,51 +2639,51 @@
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A9" s="15"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="15">
+      <c r="A9" s="11"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="11">
         <v>5</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="11">
         <v>202331587</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="15">
-        <v>0</v>
-      </c>
-      <c r="G9" s="15">
-        <v>0</v>
-      </c>
-      <c r="H9" s="15">
-        <v>100</v>
-      </c>
-      <c r="I9" s="15">
+      <c r="F9" s="11">
+        <v>0</v>
+      </c>
+      <c r="G9" s="11">
+        <v>0</v>
+      </c>
+      <c r="H9" s="11">
+        <v>100</v>
+      </c>
+      <c r="I9" s="11">
         <v>90</v>
       </c>
-      <c r="J9" s="37">
-        <v>0</v>
-      </c>
-      <c r="K9" s="37">
+      <c r="J9" s="11">
+        <v>0</v>
+      </c>
+      <c r="K9" s="11">
         <v>50</v>
       </c>
-      <c r="L9" s="15">
+      <c r="L9" s="11">
         <v>90</v>
       </c>
-      <c r="M9" s="15">
+      <c r="M9" s="11">
         <v>80</v>
       </c>
-      <c r="N9" s="37">
+      <c r="N9" s="35">
         <v>75</v>
       </c>
-      <c r="O9" s="15">
+      <c r="O9" s="11">
         <v>85</v>
       </c>
-      <c r="P9" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="14">
+      <c r="P9" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="10">
         <f>IF([1]punteo!L10="",0,[1]punteo!L10)</f>
         <v>100</v>
       </c>
@@ -2724,51 +2710,51 @@
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A10" s="15"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="15">
+      <c r="A10" s="11"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="11">
         <v>6</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="11">
         <v>202332049</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="15">
-        <v>0</v>
-      </c>
-      <c r="G10" s="15">
-        <v>0</v>
-      </c>
-      <c r="H10" s="15">
-        <v>0</v>
-      </c>
-      <c r="I10" s="15">
-        <v>0</v>
-      </c>
-      <c r="J10" s="37">
-        <v>0</v>
-      </c>
-      <c r="K10" s="37">
-        <v>0</v>
-      </c>
-      <c r="L10" s="15">
-        <v>0</v>
-      </c>
-      <c r="M10" s="15">
-        <v>0</v>
-      </c>
-      <c r="N10" s="37">
-        <v>0</v>
-      </c>
-      <c r="O10" s="15">
-        <v>0</v>
-      </c>
-      <c r="P10" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="14">
+      <c r="F10" s="11">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
+        <v>0</v>
+      </c>
+      <c r="H10" s="11">
+        <v>0</v>
+      </c>
+      <c r="I10" s="11">
+        <v>0</v>
+      </c>
+      <c r="J10" s="11">
+        <v>0</v>
+      </c>
+      <c r="K10" s="11">
+        <v>0</v>
+      </c>
+      <c r="L10" s="11">
+        <v>0</v>
+      </c>
+      <c r="M10" s="11">
+        <v>0</v>
+      </c>
+      <c r="N10" s="35">
+        <v>0</v>
+      </c>
+      <c r="O10" s="11">
+        <v>0</v>
+      </c>
+      <c r="P10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="10">
         <f>IF([1]punteo!L11="",0,[1]punteo!L11)</f>
         <v>0</v>
       </c>
@@ -2795,51 +2781,51 @@
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A11" s="15"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="15">
+      <c r="A11" s="11"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="11">
         <v>7</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="11">
         <v>202402553</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="15">
-        <v>100</v>
-      </c>
-      <c r="G11" s="15">
-        <v>0</v>
-      </c>
-      <c r="H11" s="15">
-        <v>100</v>
-      </c>
-      <c r="I11" s="15">
+      <c r="F11" s="11">
+        <v>100</v>
+      </c>
+      <c r="G11" s="11">
+        <v>0</v>
+      </c>
+      <c r="H11" s="11">
+        <v>100</v>
+      </c>
+      <c r="I11" s="11">
         <v>90</v>
       </c>
-      <c r="J11" s="37">
+      <c r="J11" s="11">
         <v>60</v>
       </c>
-      <c r="K11" s="37">
-        <v>0</v>
-      </c>
-      <c r="L11" s="15">
-        <v>100</v>
-      </c>
-      <c r="M11" s="15">
-        <v>100</v>
-      </c>
-      <c r="N11" s="37">
+      <c r="K11" s="11">
+        <v>0</v>
+      </c>
+      <c r="L11" s="11">
+        <v>100</v>
+      </c>
+      <c r="M11" s="11">
+        <v>100</v>
+      </c>
+      <c r="N11" s="35">
         <v>50</v>
       </c>
-      <c r="O11" s="15">
-        <v>0</v>
-      </c>
-      <c r="P11" s="37">
+      <c r="O11" s="11">
+        <v>0</v>
+      </c>
+      <c r="P11" s="11">
         <v>65</v>
       </c>
-      <c r="Q11" s="14">
+      <c r="Q11" s="10">
         <f>IF([1]punteo!L12="",0,[1]punteo!L12)</f>
         <v>80</v>
       </c>
@@ -2866,51 +2852,51 @@
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A12" s="15"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="15">
+      <c r="A12" s="11"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="11">
         <v>8</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="11">
         <v>202430271</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="15">
-        <v>0</v>
-      </c>
-      <c r="G12" s="15">
-        <v>100</v>
-      </c>
-      <c r="H12" s="15">
-        <v>0</v>
-      </c>
-      <c r="I12" s="15">
-        <v>0</v>
-      </c>
-      <c r="J12" s="37">
-        <v>100</v>
-      </c>
-      <c r="K12" s="37">
-        <v>100</v>
-      </c>
-      <c r="L12" s="15">
-        <v>0</v>
-      </c>
-      <c r="M12" s="15">
-        <v>0</v>
-      </c>
-      <c r="N12" s="37">
-        <v>0</v>
-      </c>
-      <c r="O12" s="15">
-        <v>0</v>
-      </c>
-      <c r="P12" s="37">
+      <c r="F12" s="11">
+        <v>0</v>
+      </c>
+      <c r="G12" s="11">
+        <v>100</v>
+      </c>
+      <c r="H12" s="11">
+        <v>0</v>
+      </c>
+      <c r="I12" s="11">
+        <v>0</v>
+      </c>
+      <c r="J12" s="11">
+        <v>100</v>
+      </c>
+      <c r="K12" s="11">
+        <v>100</v>
+      </c>
+      <c r="L12" s="11">
+        <v>0</v>
+      </c>
+      <c r="M12" s="11">
+        <v>0</v>
+      </c>
+      <c r="N12" s="35">
+        <v>0</v>
+      </c>
+      <c r="O12" s="11">
+        <v>0</v>
+      </c>
+      <c r="P12" s="11">
         <v>70</v>
       </c>
-      <c r="Q12" s="14">
+      <c r="Q12" s="10">
         <f>IF([1]punteo!L13="",0,[1]punteo!L13)</f>
         <v>80</v>
       </c>
@@ -2937,51 +2923,51 @@
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A13" s="15"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="15">
+      <c r="A13" s="11"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="11">
         <v>9</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="11">
         <v>202430532</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="15">
-        <v>100</v>
-      </c>
-      <c r="G13" s="15">
-        <v>0</v>
-      </c>
-      <c r="H13" s="15">
-        <v>100</v>
-      </c>
-      <c r="I13" s="15">
-        <v>100</v>
-      </c>
-      <c r="J13" s="37">
-        <v>100</v>
-      </c>
-      <c r="K13" s="37">
-        <v>100</v>
-      </c>
-      <c r="L13" s="15">
-        <v>100</v>
-      </c>
-      <c r="M13" s="15">
-        <v>100</v>
-      </c>
-      <c r="N13" s="37">
-        <v>100</v>
-      </c>
-      <c r="O13" s="15">
+      <c r="F13" s="11">
+        <v>100</v>
+      </c>
+      <c r="G13" s="11">
+        <v>0</v>
+      </c>
+      <c r="H13" s="11">
+        <v>100</v>
+      </c>
+      <c r="I13" s="11">
+        <v>100</v>
+      </c>
+      <c r="J13" s="11">
+        <v>100</v>
+      </c>
+      <c r="K13" s="11">
+        <v>100</v>
+      </c>
+      <c r="L13" s="11">
+        <v>100</v>
+      </c>
+      <c r="M13" s="11">
+        <v>100</v>
+      </c>
+      <c r="N13" s="35">
+        <v>100</v>
+      </c>
+      <c r="O13" s="11">
         <v>65</v>
       </c>
-      <c r="P13" s="37">
+      <c r="P13" s="11">
         <v>80</v>
       </c>
-      <c r="Q13" s="14">
+      <c r="Q13" s="10">
         <f>IF([1]punteo!L14="",0,[1]punteo!L14)</f>
         <v>100</v>
       </c>
@@ -3008,51 +2994,51 @@
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A14" s="15"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="15">
+      <c r="A14" s="11"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="11">
         <v>10</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="11">
         <v>202430589</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="15">
-        <v>0</v>
-      </c>
-      <c r="G14" s="15">
-        <v>0</v>
-      </c>
-      <c r="H14" s="15">
-        <v>0</v>
-      </c>
-      <c r="I14" s="15">
-        <v>100</v>
-      </c>
-      <c r="J14" s="37">
+      <c r="F14" s="11">
+        <v>0</v>
+      </c>
+      <c r="G14" s="11">
+        <v>0</v>
+      </c>
+      <c r="H14" s="11">
+        <v>0</v>
+      </c>
+      <c r="I14" s="11">
+        <v>100</v>
+      </c>
+      <c r="J14" s="11">
         <v>75</v>
       </c>
-      <c r="K14" s="37">
+      <c r="K14" s="11">
         <v>90</v>
       </c>
-      <c r="L14" s="15">
-        <v>100</v>
-      </c>
-      <c r="M14" s="15">
+      <c r="L14" s="11">
+        <v>100</v>
+      </c>
+      <c r="M14" s="11">
         <v>80</v>
       </c>
-      <c r="N14" s="37">
+      <c r="N14" s="35">
         <v>70</v>
       </c>
-      <c r="O14" s="15">
-        <v>0</v>
-      </c>
-      <c r="P14" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="14">
+      <c r="O14" s="11">
+        <v>0</v>
+      </c>
+      <c r="P14" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="10">
         <f>IF([1]punteo!L15="",0,[1]punteo!L15)</f>
         <v>0</v>
       </c>
@@ -3079,51 +3065,51 @@
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A15" s="15"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="15">
+      <c r="A15" s="11"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="11">
         <v>11</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="11">
         <v>202430602</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="15">
-        <v>0</v>
-      </c>
-      <c r="G15" s="15">
-        <v>0</v>
-      </c>
-      <c r="H15" s="15">
-        <v>100</v>
-      </c>
-      <c r="I15" s="15">
-        <v>0</v>
-      </c>
-      <c r="J15" s="37">
+      <c r="F15" s="11">
+        <v>0</v>
+      </c>
+      <c r="G15" s="11">
+        <v>0</v>
+      </c>
+      <c r="H15" s="11">
+        <v>100</v>
+      </c>
+      <c r="I15" s="11">
+        <v>0</v>
+      </c>
+      <c r="J15" s="11">
         <v>60</v>
       </c>
-      <c r="K15" s="37">
-        <v>0</v>
-      </c>
-      <c r="L15" s="15">
+      <c r="K15" s="11">
+        <v>0</v>
+      </c>
+      <c r="L15" s="11">
         <v>90</v>
       </c>
-      <c r="M15" s="15">
-        <v>100</v>
-      </c>
-      <c r="N15" s="37">
-        <v>0</v>
-      </c>
-      <c r="O15" s="15">
-        <v>0</v>
-      </c>
-      <c r="P15" s="37">
+      <c r="M15" s="11">
+        <v>100</v>
+      </c>
+      <c r="N15" s="35">
+        <v>0</v>
+      </c>
+      <c r="O15" s="11">
+        <v>0</v>
+      </c>
+      <c r="P15" s="11">
         <v>30</v>
       </c>
-      <c r="Q15" s="14">
+      <c r="Q15" s="10">
         <f>IF([1]punteo!L16="",0,[1]punteo!L16)</f>
         <v>0</v>
       </c>
@@ -3150,51 +3136,51 @@
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A16" s="15"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="15">
+      <c r="A16" s="11"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="11">
         <v>12</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="11">
         <v>202430633</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E16" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F16" s="15">
-        <v>100</v>
-      </c>
-      <c r="G16" s="15">
-        <v>0</v>
-      </c>
-      <c r="H16" s="15">
-        <v>100</v>
-      </c>
-      <c r="I16" s="15">
-        <v>100</v>
-      </c>
-      <c r="J16" s="37">
-        <v>100</v>
-      </c>
-      <c r="K16" s="37">
-        <v>100</v>
-      </c>
-      <c r="L16" s="15">
-        <v>100</v>
-      </c>
-      <c r="M16" s="15">
-        <v>100</v>
-      </c>
-      <c r="N16" s="37">
+      <c r="F16" s="11">
+        <v>100</v>
+      </c>
+      <c r="G16" s="11">
+        <v>0</v>
+      </c>
+      <c r="H16" s="11">
+        <v>100</v>
+      </c>
+      <c r="I16" s="11">
+        <v>100</v>
+      </c>
+      <c r="J16" s="11">
+        <v>100</v>
+      </c>
+      <c r="K16" s="11">
+        <v>100</v>
+      </c>
+      <c r="L16" s="11">
+        <v>100</v>
+      </c>
+      <c r="M16" s="11">
+        <v>100</v>
+      </c>
+      <c r="N16" s="35">
         <v>50</v>
       </c>
-      <c r="O16" s="15">
-        <v>100</v>
-      </c>
-      <c r="P16" s="37">
+      <c r="O16" s="11">
+        <v>100</v>
+      </c>
+      <c r="P16" s="11">
         <v>50</v>
       </c>
-      <c r="Q16" s="14">
+      <c r="Q16" s="10">
         <f>IF([1]punteo!L17="",0,[1]punteo!L17)</f>
         <v>0</v>
       </c>
@@ -3221,55 +3207,55 @@
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A17" s="38">
+      <c r="A17" s="27">
         <v>0.27777777777777779</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="11">
         <v>13</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="11">
         <v>202430645</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F17" s="15">
-        <v>100</v>
-      </c>
-      <c r="G17" s="15">
-        <v>0</v>
-      </c>
-      <c r="H17" s="15">
+      <c r="F17" s="11">
+        <v>100</v>
+      </c>
+      <c r="G17" s="11">
+        <v>0</v>
+      </c>
+      <c r="H17" s="11">
         <v>50</v>
       </c>
-      <c r="I17" s="15">
+      <c r="I17" s="11">
         <v>90</v>
       </c>
-      <c r="J17" s="37">
-        <v>100</v>
-      </c>
-      <c r="K17" s="37">
+      <c r="J17" s="11">
+        <v>100</v>
+      </c>
+      <c r="K17" s="11">
         <v>85</v>
       </c>
-      <c r="L17" s="15">
-        <v>100</v>
-      </c>
-      <c r="M17" s="15">
-        <v>100</v>
-      </c>
-      <c r="N17" s="37">
+      <c r="L17" s="11">
+        <v>100</v>
+      </c>
+      <c r="M17" s="11">
+        <v>100</v>
+      </c>
+      <c r="N17" s="35">
         <v>70</v>
       </c>
-      <c r="O17" s="15">
+      <c r="O17" s="11">
         <v>75</v>
       </c>
-      <c r="P17" s="37">
+      <c r="P17" s="11">
         <v>70</v>
       </c>
-      <c r="Q17" s="14">
+      <c r="Q17" s="10">
         <f>IF([1]punteo!L18="",0,[1]punteo!L18)</f>
         <v>100</v>
       </c>
@@ -3296,51 +3282,51 @@
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A18" s="15"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="15">
+      <c r="A18" s="11"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="11">
         <v>14</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="11">
         <v>202430733</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F18" s="15">
-        <v>100</v>
-      </c>
-      <c r="G18" s="15">
-        <v>0</v>
-      </c>
-      <c r="H18" s="15">
+      <c r="F18" s="11">
+        <v>100</v>
+      </c>
+      <c r="G18" s="11">
+        <v>0</v>
+      </c>
+      <c r="H18" s="11">
         <v>50</v>
       </c>
-      <c r="I18" s="15">
-        <v>100</v>
-      </c>
-      <c r="J18" s="37">
+      <c r="I18" s="11">
+        <v>100</v>
+      </c>
+      <c r="J18" s="11">
         <v>85</v>
       </c>
-      <c r="K18" s="37">
-        <v>100</v>
-      </c>
-      <c r="L18" s="15">
-        <v>100</v>
-      </c>
-      <c r="M18" s="15">
-        <v>100</v>
-      </c>
-      <c r="N18" s="37">
+      <c r="K18" s="11">
+        <v>100</v>
+      </c>
+      <c r="L18" s="11">
+        <v>100</v>
+      </c>
+      <c r="M18" s="11">
+        <v>100</v>
+      </c>
+      <c r="N18" s="35">
         <v>50</v>
       </c>
-      <c r="O18" s="15">
-        <v>100</v>
-      </c>
-      <c r="P18" s="37">
-        <v>100</v>
-      </c>
-      <c r="Q18" s="14">
+      <c r="O18" s="11">
+        <v>100</v>
+      </c>
+      <c r="P18" s="11">
+        <v>100</v>
+      </c>
+      <c r="Q18" s="10">
         <f>IF([1]punteo!L19="",0,[1]punteo!L19)</f>
         <v>100</v>
       </c>
@@ -3367,51 +3353,51 @@
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A19" s="15"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="15">
+      <c r="A19" s="11"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="11">
         <v>15</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="11">
         <v>202430804</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F19" s="15">
-        <v>100</v>
-      </c>
-      <c r="G19" s="15">
-        <v>0</v>
-      </c>
-      <c r="H19" s="15">
-        <v>0</v>
-      </c>
-      <c r="I19" s="15">
-        <v>0</v>
-      </c>
-      <c r="J19" s="37">
-        <v>100</v>
-      </c>
-      <c r="K19" s="37">
-        <v>100</v>
-      </c>
-      <c r="L19" s="15">
-        <v>100</v>
-      </c>
-      <c r="M19" s="15">
-        <v>100</v>
-      </c>
-      <c r="N19" s="37">
+      <c r="F19" s="11">
+        <v>100</v>
+      </c>
+      <c r="G19" s="11">
+        <v>0</v>
+      </c>
+      <c r="H19" s="11">
+        <v>0</v>
+      </c>
+      <c r="I19" s="11">
+        <v>0</v>
+      </c>
+      <c r="J19" s="11">
+        <v>100</v>
+      </c>
+      <c r="K19" s="11">
+        <v>100</v>
+      </c>
+      <c r="L19" s="11">
+        <v>100</v>
+      </c>
+      <c r="M19" s="11">
+        <v>100</v>
+      </c>
+      <c r="N19" s="35">
         <v>80</v>
       </c>
-      <c r="O19" s="15">
-        <v>100</v>
-      </c>
-      <c r="P19" s="37">
-        <v>100</v>
-      </c>
-      <c r="Q19" s="14">
+      <c r="O19" s="11">
+        <v>100</v>
+      </c>
+      <c r="P19" s="11">
+        <v>100</v>
+      </c>
+      <c r="Q19" s="10">
         <f>IF([1]punteo!L20="",0,[1]punteo!L20)</f>
         <v>0</v>
       </c>
@@ -3438,55 +3424,55 @@
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A20" s="38" t="s">
+      <c r="A20" s="27" t="s">
         <v>88</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="11">
         <v>16</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="11">
         <v>202430829</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="15">
-        <v>100</v>
-      </c>
-      <c r="G20" s="15">
-        <v>100</v>
-      </c>
-      <c r="H20" s="15">
-        <v>100</v>
-      </c>
-      <c r="I20" s="15">
+      <c r="F20" s="11">
+        <v>100</v>
+      </c>
+      <c r="G20" s="11">
+        <v>100</v>
+      </c>
+      <c r="H20" s="11">
+        <v>100</v>
+      </c>
+      <c r="I20" s="11">
         <v>90</v>
       </c>
-      <c r="J20" s="37">
+      <c r="J20" s="11">
         <v>85</v>
       </c>
-      <c r="K20" s="37">
-        <v>100</v>
-      </c>
-      <c r="L20" s="15">
-        <v>100</v>
-      </c>
-      <c r="M20" s="15">
-        <v>100</v>
-      </c>
-      <c r="N20" s="37">
+      <c r="K20" s="11">
+        <v>100</v>
+      </c>
+      <c r="L20" s="11">
+        <v>100</v>
+      </c>
+      <c r="M20" s="11">
+        <v>100</v>
+      </c>
+      <c r="N20" s="35">
         <v>70</v>
       </c>
-      <c r="O20" s="15">
+      <c r="O20" s="11">
         <v>85</v>
       </c>
-      <c r="P20" s="37">
+      <c r="P20" s="11">
         <v>85</v>
       </c>
-      <c r="Q20" s="14">
+      <c r="Q20" s="10">
         <f>IF([1]punteo!L21="",0,[1]punteo!L21)</f>
         <v>80</v>
       </c>
@@ -3513,51 +3499,51 @@
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A21" s="15"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="15">
+      <c r="A21" s="11"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="11">
         <v>17</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="11">
         <v>202431169</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F21" s="15">
-        <v>100</v>
-      </c>
-      <c r="G21" s="15">
-        <v>0</v>
-      </c>
-      <c r="H21" s="15">
+      <c r="F21" s="11">
+        <v>100</v>
+      </c>
+      <c r="G21" s="11">
+        <v>0</v>
+      </c>
+      <c r="H21" s="11">
         <v>50</v>
       </c>
-      <c r="I21" s="15">
-        <v>100</v>
-      </c>
-      <c r="J21" s="37">
+      <c r="I21" s="11">
+        <v>100</v>
+      </c>
+      <c r="J21" s="11">
         <v>85</v>
       </c>
-      <c r="K21" s="37">
-        <v>100</v>
-      </c>
-      <c r="L21" s="15">
-        <v>100</v>
-      </c>
-      <c r="M21" s="15">
-        <v>100</v>
-      </c>
-      <c r="N21" s="37">
+      <c r="K21" s="11">
+        <v>100</v>
+      </c>
+      <c r="L21" s="11">
+        <v>100</v>
+      </c>
+      <c r="M21" s="11">
+        <v>100</v>
+      </c>
+      <c r="N21" s="35">
         <v>50</v>
       </c>
-      <c r="O21" s="15">
-        <v>100</v>
-      </c>
-      <c r="P21" s="37">
-        <v>100</v>
-      </c>
-      <c r="Q21" s="14">
+      <c r="O21" s="11">
+        <v>100</v>
+      </c>
+      <c r="P21" s="11">
+        <v>100</v>
+      </c>
+      <c r="Q21" s="10">
         <f>IF([1]punteo!L22="",0,[1]punteo!L22)</f>
         <v>100</v>
       </c>
@@ -3584,55 +3570,55 @@
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A22" s="38">
+      <c r="A22" s="27">
         <v>0.27777777777777779</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="11">
         <v>18</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="11">
         <v>202431502</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E22" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="F22" s="15">
-        <v>100</v>
-      </c>
-      <c r="G22" s="15">
-        <v>100</v>
-      </c>
-      <c r="H22" s="15">
-        <v>100</v>
-      </c>
-      <c r="I22" s="15">
-        <v>100</v>
-      </c>
-      <c r="J22" s="37">
-        <v>100</v>
-      </c>
-      <c r="K22" s="37">
-        <v>100</v>
-      </c>
-      <c r="L22" s="15">
-        <v>100</v>
-      </c>
-      <c r="M22" s="15">
-        <v>100</v>
-      </c>
-      <c r="N22" s="37">
+      <c r="F22" s="11">
+        <v>100</v>
+      </c>
+      <c r="G22" s="11">
+        <v>100</v>
+      </c>
+      <c r="H22" s="11">
+        <v>100</v>
+      </c>
+      <c r="I22" s="11">
+        <v>100</v>
+      </c>
+      <c r="J22" s="11">
+        <v>100</v>
+      </c>
+      <c r="K22" s="11">
+        <v>100</v>
+      </c>
+      <c r="L22" s="11">
+        <v>100</v>
+      </c>
+      <c r="M22" s="11">
+        <v>100</v>
+      </c>
+      <c r="N22" s="35">
         <v>50</v>
       </c>
-      <c r="O22" s="15">
+      <c r="O22" s="11">
         <v>90</v>
       </c>
-      <c r="P22" s="37">
+      <c r="P22" s="11">
         <v>45</v>
       </c>
-      <c r="Q22" s="14">
+      <c r="Q22" s="10">
         <f>IF([1]punteo!L23="",0,[1]punteo!L23)</f>
         <v>80</v>
       </c>
@@ -3659,51 +3645,51 @@
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A23" s="15"/>
+      <c r="A23" s="11"/>
       <c r="B23" s="9"/>
-      <c r="C23" s="15">
+      <c r="C23" s="11">
         <v>19</v>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="11">
         <v>202431726</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E23" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="15">
-        <v>100</v>
-      </c>
-      <c r="G23" s="15">
-        <v>0</v>
-      </c>
-      <c r="H23" s="15">
-        <v>100</v>
-      </c>
-      <c r="I23" s="15">
-        <v>100</v>
-      </c>
-      <c r="J23" s="37">
+      <c r="F23" s="11">
+        <v>100</v>
+      </c>
+      <c r="G23" s="11">
+        <v>0</v>
+      </c>
+      <c r="H23" s="11">
+        <v>100</v>
+      </c>
+      <c r="I23" s="11">
+        <v>100</v>
+      </c>
+      <c r="J23" s="11">
         <v>75</v>
       </c>
-      <c r="K23" s="37">
-        <v>100</v>
-      </c>
-      <c r="L23" s="15">
-        <v>100</v>
-      </c>
-      <c r="M23" s="15">
-        <v>100</v>
-      </c>
-      <c r="N23" s="37">
+      <c r="K23" s="11">
+        <v>100</v>
+      </c>
+      <c r="L23" s="11">
+        <v>100</v>
+      </c>
+      <c r="M23" s="11">
+        <v>100</v>
+      </c>
+      <c r="N23" s="35">
         <v>90</v>
       </c>
-      <c r="O23" s="15">
+      <c r="O23" s="11">
         <v>95</v>
       </c>
-      <c r="P23" s="37">
+      <c r="P23" s="11">
         <v>90</v>
       </c>
-      <c r="Q23" s="14">
+      <c r="Q23" s="10">
         <f>IF([1]punteo!L24="",0,[1]punteo!L24)</f>
         <v>0</v>
       </c>
@@ -3730,51 +3716,51 @@
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A24" s="15"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="15">
+      <c r="A24" s="11"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="11">
         <v>20</v>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="11">
         <v>202431817</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="F24" s="15">
-        <v>0</v>
-      </c>
-      <c r="G24" s="15">
-        <v>0</v>
-      </c>
-      <c r="H24" s="15">
-        <v>100</v>
-      </c>
-      <c r="I24" s="15">
-        <v>100</v>
-      </c>
-      <c r="J24" s="37">
-        <v>0</v>
-      </c>
-      <c r="K24" s="37">
-        <v>0</v>
-      </c>
-      <c r="L24" s="15">
-        <v>100</v>
-      </c>
-      <c r="M24" s="15">
-        <v>0</v>
-      </c>
-      <c r="N24" s="37">
-        <v>0</v>
-      </c>
-      <c r="O24" s="15">
+      <c r="F24" s="11">
+        <v>0</v>
+      </c>
+      <c r="G24" s="11">
+        <v>0</v>
+      </c>
+      <c r="H24" s="11">
+        <v>100</v>
+      </c>
+      <c r="I24" s="11">
+        <v>100</v>
+      </c>
+      <c r="J24" s="11">
+        <v>0</v>
+      </c>
+      <c r="K24" s="11">
+        <v>0</v>
+      </c>
+      <c r="L24" s="11">
+        <v>100</v>
+      </c>
+      <c r="M24" s="11">
+        <v>0</v>
+      </c>
+      <c r="N24" s="35">
+        <v>0</v>
+      </c>
+      <c r="O24" s="11">
         <v>15</v>
       </c>
-      <c r="P24" s="37">
+      <c r="P24" s="11">
         <v>90</v>
       </c>
-      <c r="Q24" s="14">
+      <c r="Q24" s="10">
         <f>IF([1]punteo!L25="",0,[1]punteo!L25)</f>
         <v>100</v>
       </c>
@@ -3801,51 +3787,51 @@
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A25" s="15"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="15">
+      <c r="A25" s="11"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="11">
         <v>21</v>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="11">
         <v>202431819</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F25" s="15">
-        <v>0</v>
-      </c>
-      <c r="G25" s="15">
-        <v>100</v>
-      </c>
-      <c r="H25" s="15">
-        <v>0</v>
-      </c>
-      <c r="I25" s="15">
-        <v>0</v>
-      </c>
-      <c r="J25" s="37">
-        <v>0</v>
-      </c>
-      <c r="K25" s="37">
-        <v>100</v>
-      </c>
-      <c r="L25" s="15">
-        <v>0</v>
-      </c>
-      <c r="M25" s="15">
-        <v>100</v>
-      </c>
-      <c r="N25" s="37">
-        <v>0</v>
-      </c>
-      <c r="O25" s="15">
+      <c r="F25" s="11">
+        <v>0</v>
+      </c>
+      <c r="G25" s="11">
+        <v>100</v>
+      </c>
+      <c r="H25" s="11">
+        <v>0</v>
+      </c>
+      <c r="I25" s="11">
+        <v>0</v>
+      </c>
+      <c r="J25" s="11">
+        <v>0</v>
+      </c>
+      <c r="K25" s="11">
+        <v>100</v>
+      </c>
+      <c r="L25" s="11">
+        <v>0</v>
+      </c>
+      <c r="M25" s="11">
+        <v>100</v>
+      </c>
+      <c r="N25" s="35">
+        <v>0</v>
+      </c>
+      <c r="O25" s="11">
         <v>85</v>
       </c>
-      <c r="P25" s="37">
+      <c r="P25" s="11">
         <v>70</v>
       </c>
-      <c r="Q25" s="14">
+      <c r="Q25" s="10">
         <f>IF([1]punteo!L26="",0,[1]punteo!L26)</f>
         <v>80</v>
       </c>
@@ -3872,55 +3858,55 @@
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="11" t="s">
         <v>86</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="11">
         <v>22</v>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="11">
         <v>202431863</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="E26" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="F26" s="15">
-        <v>100</v>
-      </c>
-      <c r="G26" s="15">
-        <v>0</v>
-      </c>
-      <c r="H26" s="15">
-        <v>0</v>
-      </c>
-      <c r="I26" s="15">
-        <v>100</v>
-      </c>
-      <c r="J26" s="37">
+      <c r="F26" s="11">
+        <v>100</v>
+      </c>
+      <c r="G26" s="11">
+        <v>0</v>
+      </c>
+      <c r="H26" s="11">
+        <v>0</v>
+      </c>
+      <c r="I26" s="11">
+        <v>100</v>
+      </c>
+      <c r="J26" s="11">
         <v>50</v>
       </c>
-      <c r="K26" s="37">
+      <c r="K26" s="11">
         <v>50</v>
       </c>
-      <c r="L26" s="15">
+      <c r="L26" s="11">
         <v>50</v>
       </c>
-      <c r="M26" s="15">
-        <v>100</v>
-      </c>
-      <c r="N26" s="37">
+      <c r="M26" s="11">
+        <v>100</v>
+      </c>
+      <c r="N26" s="35">
         <v>25</v>
       </c>
-      <c r="O26" s="15">
+      <c r="O26" s="11">
         <v>25</v>
       </c>
-      <c r="P26" s="37">
-        <v>100</v>
-      </c>
-      <c r="Q26" s="14">
+      <c r="P26" s="11">
+        <v>100</v>
+      </c>
+      <c r="Q26" s="10">
         <f>IF([1]punteo!L27="",0,[1]punteo!L27)</f>
         <v>80</v>
       </c>
@@ -3947,51 +3933,51 @@
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A27" s="15"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="15">
+      <c r="A27" s="11"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="11">
         <v>23</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="11">
         <v>202432080</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="E27" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F27" s="15">
-        <v>100</v>
-      </c>
-      <c r="G27" s="15">
-        <v>0</v>
-      </c>
-      <c r="H27" s="15">
-        <v>0</v>
-      </c>
-      <c r="I27" s="15">
-        <v>0</v>
-      </c>
-      <c r="J27" s="37">
-        <v>0</v>
-      </c>
-      <c r="K27" s="37">
-        <v>100</v>
-      </c>
-      <c r="L27" s="15">
-        <v>100</v>
-      </c>
-      <c r="M27" s="15">
-        <v>100</v>
-      </c>
-      <c r="N27" s="37">
+      <c r="F27" s="11">
+        <v>100</v>
+      </c>
+      <c r="G27" s="11">
+        <v>0</v>
+      </c>
+      <c r="H27" s="11">
+        <v>0</v>
+      </c>
+      <c r="I27" s="11">
+        <v>0</v>
+      </c>
+      <c r="J27" s="11">
+        <v>0</v>
+      </c>
+      <c r="K27" s="11">
+        <v>100</v>
+      </c>
+      <c r="L27" s="11">
+        <v>100</v>
+      </c>
+      <c r="M27" s="11">
+        <v>100</v>
+      </c>
+      <c r="N27" s="35">
         <v>70</v>
       </c>
-      <c r="O27" s="15">
-        <v>100</v>
-      </c>
-      <c r="P27" s="37">
-        <v>100</v>
-      </c>
-      <c r="Q27" s="14">
+      <c r="O27" s="11">
+        <v>100</v>
+      </c>
+      <c r="P27" s="11">
+        <v>100</v>
+      </c>
+      <c r="Q27" s="10">
         <f>IF([1]punteo!L28="",0,[1]punteo!L28)</f>
         <v>0</v>
       </c>
@@ -4018,51 +4004,51 @@
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A28" s="15"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="15">
+      <c r="A28" s="11"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="11">
         <v>24</v>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="11">
         <v>202432085</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="F28" s="15">
-        <v>100</v>
-      </c>
-      <c r="G28" s="15">
-        <v>0</v>
-      </c>
-      <c r="H28" s="15">
-        <v>100</v>
-      </c>
-      <c r="I28" s="15">
-        <v>100</v>
-      </c>
-      <c r="J28" s="37">
+      <c r="F28" s="11">
+        <v>100</v>
+      </c>
+      <c r="G28" s="11">
+        <v>0</v>
+      </c>
+      <c r="H28" s="11">
+        <v>100</v>
+      </c>
+      <c r="I28" s="11">
+        <v>100</v>
+      </c>
+      <c r="J28" s="11">
         <v>75</v>
       </c>
-      <c r="K28" s="37">
-        <v>100</v>
-      </c>
-      <c r="L28" s="15">
+      <c r="K28" s="11">
+        <v>100</v>
+      </c>
+      <c r="L28" s="11">
         <v>90</v>
       </c>
-      <c r="M28" s="15">
-        <v>100</v>
-      </c>
-      <c r="N28" s="37">
+      <c r="M28" s="11">
+        <v>100</v>
+      </c>
+      <c r="N28" s="35">
         <v>70</v>
       </c>
-      <c r="O28" s="15">
+      <c r="O28" s="11">
         <v>95</v>
       </c>
-      <c r="P28" s="37">
+      <c r="P28" s="11">
         <v>90</v>
       </c>
-      <c r="Q28" s="14">
+      <c r="Q28" s="10">
         <f>IF([1]punteo!L29="",0,[1]punteo!L29)</f>
         <v>0</v>
       </c>
@@ -4089,55 +4075,55 @@
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A29" s="38" t="s">
+      <c r="A29" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="11">
         <v>25</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="11">
         <v>202432137</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E29" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="F29" s="15">
-        <v>100</v>
-      </c>
-      <c r="G29" s="15">
-        <v>0</v>
-      </c>
-      <c r="H29" s="15">
-        <v>0</v>
-      </c>
-      <c r="I29" s="15">
-        <v>100</v>
-      </c>
-      <c r="J29" s="37">
+      <c r="F29" s="11">
+        <v>100</v>
+      </c>
+      <c r="G29" s="11">
+        <v>0</v>
+      </c>
+      <c r="H29" s="11">
+        <v>0</v>
+      </c>
+      <c r="I29" s="11">
+        <v>100</v>
+      </c>
+      <c r="J29" s="11">
         <v>50</v>
       </c>
-      <c r="K29" s="37">
+      <c r="K29" s="11">
         <v>50</v>
       </c>
-      <c r="L29" s="15">
+      <c r="L29" s="11">
         <v>50</v>
       </c>
-      <c r="M29" s="15">
-        <v>0</v>
-      </c>
-      <c r="N29" s="37">
+      <c r="M29" s="11">
+        <v>0</v>
+      </c>
+      <c r="N29" s="35">
         <v>25</v>
       </c>
-      <c r="O29" s="15">
+      <c r="O29" s="11">
         <v>25</v>
       </c>
-      <c r="P29" s="37">
-        <v>100</v>
-      </c>
-      <c r="Q29" s="14">
+      <c r="P29" s="11">
+        <v>100</v>
+      </c>
+      <c r="Q29" s="10">
         <f>IF([1]punteo!L30="",0,[1]punteo!L30)</f>
         <v>80</v>
       </c>
@@ -4164,51 +4150,51 @@
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A30" s="15"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="15">
+      <c r="A30" s="11"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="11">
         <v>26</v>
       </c>
-      <c r="D30" s="15">
+      <c r="D30" s="11">
         <v>202530125</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E30" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="F30" s="15">
-        <v>0</v>
-      </c>
-      <c r="G30" s="15">
-        <v>0</v>
-      </c>
-      <c r="H30" s="15">
-        <v>100</v>
-      </c>
-      <c r="I30" s="15">
-        <v>100</v>
-      </c>
-      <c r="J30" s="37">
-        <v>100</v>
-      </c>
-      <c r="K30" s="37">
+      <c r="F30" s="11">
+        <v>0</v>
+      </c>
+      <c r="G30" s="11">
+        <v>0</v>
+      </c>
+      <c r="H30" s="11">
+        <v>100</v>
+      </c>
+      <c r="I30" s="11">
+        <v>100</v>
+      </c>
+      <c r="J30" s="11">
+        <v>100</v>
+      </c>
+      <c r="K30" s="11">
         <v>75</v>
       </c>
-      <c r="L30" s="15">
+      <c r="L30" s="11">
         <v>90</v>
       </c>
-      <c r="M30" s="15">
-        <v>100</v>
-      </c>
-      <c r="N30" s="37">
+      <c r="M30" s="11">
+        <v>100</v>
+      </c>
+      <c r="N30" s="35">
         <v>80</v>
       </c>
-      <c r="O30" s="15">
+      <c r="O30" s="11">
         <v>90</v>
       </c>
-      <c r="P30" s="37">
+      <c r="P30" s="11">
         <v>60</v>
       </c>
-      <c r="Q30" s="14">
+      <c r="Q30" s="10">
         <f>IF([1]punteo!L31="",0,[1]punteo!L31)</f>
         <v>0</v>
       </c>
@@ -4235,55 +4221,55 @@
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="27" t="s">
         <v>88</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="11">
         <v>27</v>
       </c>
-      <c r="D31" s="15">
+      <c r="D31" s="11">
         <v>202530235</v>
       </c>
-      <c r="E31" s="15" t="s">
+      <c r="E31" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="F31" s="15">
-        <v>100</v>
-      </c>
-      <c r="G31" s="15">
-        <v>0</v>
-      </c>
-      <c r="H31" s="15">
-        <v>100</v>
-      </c>
-      <c r="I31" s="15">
-        <v>100</v>
-      </c>
-      <c r="J31" s="37">
-        <v>100</v>
-      </c>
-      <c r="K31" s="37">
-        <v>100</v>
-      </c>
-      <c r="L31" s="15">
-        <v>100</v>
-      </c>
-      <c r="M31" s="15">
-        <v>100</v>
-      </c>
-      <c r="N31" s="37">
-        <v>100</v>
-      </c>
-      <c r="O31" s="15">
-        <v>0</v>
-      </c>
-      <c r="P31" s="37">
-        <v>100</v>
-      </c>
-      <c r="Q31" s="14">
+      <c r="F31" s="11">
+        <v>100</v>
+      </c>
+      <c r="G31" s="11">
+        <v>0</v>
+      </c>
+      <c r="H31" s="11">
+        <v>100</v>
+      </c>
+      <c r="I31" s="11">
+        <v>100</v>
+      </c>
+      <c r="J31" s="11">
+        <v>100</v>
+      </c>
+      <c r="K31" s="11">
+        <v>100</v>
+      </c>
+      <c r="L31" s="11">
+        <v>100</v>
+      </c>
+      <c r="M31" s="11">
+        <v>100</v>
+      </c>
+      <c r="N31" s="35">
+        <v>100</v>
+      </c>
+      <c r="O31" s="11">
+        <v>0</v>
+      </c>
+      <c r="P31" s="11">
+        <v>100</v>
+      </c>
+      <c r="Q31" s="10">
         <f>IF([1]punteo!L32="",0,[1]punteo!L32)</f>
         <v>80</v>
       </c>
@@ -4310,55 +4296,55 @@
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A32" s="38">
+      <c r="A32" s="27">
         <v>0.27777777777777779</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C32" s="15">
+      <c r="C32" s="11">
         <v>28</v>
       </c>
-      <c r="D32" s="15">
+      <c r="D32" s="11">
         <v>202530265</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="E32" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F32" s="15">
-        <v>100</v>
-      </c>
-      <c r="G32" s="15">
-        <v>100</v>
-      </c>
-      <c r="H32" s="15">
-        <v>100</v>
-      </c>
-      <c r="I32" s="15">
-        <v>100</v>
-      </c>
-      <c r="J32" s="37">
-        <v>100</v>
-      </c>
-      <c r="K32" s="37">
+      <c r="F32" s="11">
+        <v>100</v>
+      </c>
+      <c r="G32" s="11">
+        <v>100</v>
+      </c>
+      <c r="H32" s="11">
+        <v>100</v>
+      </c>
+      <c r="I32" s="11">
+        <v>100</v>
+      </c>
+      <c r="J32" s="11">
+        <v>100</v>
+      </c>
+      <c r="K32" s="11">
         <v>90</v>
       </c>
-      <c r="L32" s="15">
-        <v>100</v>
-      </c>
-      <c r="M32" s="15">
-        <v>100</v>
-      </c>
-      <c r="N32" s="37">
+      <c r="L32" s="11">
+        <v>100</v>
+      </c>
+      <c r="M32" s="11">
+        <v>100</v>
+      </c>
+      <c r="N32" s="35">
         <v>70</v>
       </c>
-      <c r="O32" s="15">
-        <v>100</v>
-      </c>
-      <c r="P32" s="37">
-        <v>100</v>
-      </c>
-      <c r="Q32" s="14">
+      <c r="O32" s="11">
+        <v>100</v>
+      </c>
+      <c r="P32" s="11">
+        <v>100</v>
+      </c>
+      <c r="Q32" s="10">
         <f>IF([1]punteo!L33="",0,[1]punteo!L33)</f>
         <v>90</v>
       </c>
@@ -4385,51 +4371,51 @@
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A33" s="15"/>
-      <c r="B33" s="16"/>
-      <c r="C33" s="15">
+      <c r="A33" s="11"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="11">
         <v>29</v>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="11">
         <v>202530315</v>
       </c>
-      <c r="E33" s="15" t="s">
+      <c r="E33" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="F33" s="15">
-        <v>100</v>
-      </c>
-      <c r="G33" s="15">
-        <v>0</v>
-      </c>
-      <c r="H33" s="15">
-        <v>100</v>
-      </c>
-      <c r="I33" s="15">
-        <v>100</v>
-      </c>
-      <c r="J33" s="37">
-        <v>100</v>
-      </c>
-      <c r="K33" s="37">
-        <v>100</v>
-      </c>
-      <c r="L33" s="15">
-        <v>100</v>
-      </c>
-      <c r="M33" s="15">
-        <v>100</v>
-      </c>
-      <c r="N33" s="37">
+      <c r="F33" s="11">
+        <v>100</v>
+      </c>
+      <c r="G33" s="11">
+        <v>0</v>
+      </c>
+      <c r="H33" s="11">
+        <v>100</v>
+      </c>
+      <c r="I33" s="11">
+        <v>100</v>
+      </c>
+      <c r="J33" s="11">
+        <v>100</v>
+      </c>
+      <c r="K33" s="11">
+        <v>100</v>
+      </c>
+      <c r="L33" s="11">
+        <v>100</v>
+      </c>
+      <c r="M33" s="11">
+        <v>100</v>
+      </c>
+      <c r="N33" s="35">
         <v>50</v>
       </c>
-      <c r="O33" s="15">
-        <v>100</v>
-      </c>
-      <c r="P33" s="37">
+      <c r="O33" s="11">
+        <v>100</v>
+      </c>
+      <c r="P33" s="11">
         <v>50</v>
       </c>
-      <c r="Q33" s="14">
+      <c r="Q33" s="10">
         <f>IF([1]punteo!L34="",0,[1]punteo!L34)</f>
         <v>80</v>
       </c>
@@ -4456,51 +4442,51 @@
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A34" s="15"/>
-      <c r="B34" s="16"/>
-      <c r="C34" s="15">
+      <c r="A34" s="11"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="11">
         <v>30</v>
       </c>
-      <c r="D34" s="15">
+      <c r="D34" s="11">
         <v>202530329</v>
       </c>
-      <c r="E34" s="15" t="s">
+      <c r="E34" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="F34" s="15">
-        <v>100</v>
-      </c>
-      <c r="G34" s="15">
-        <v>0</v>
-      </c>
-      <c r="H34" s="15">
-        <v>100</v>
-      </c>
-      <c r="I34" s="15">
-        <v>0</v>
-      </c>
-      <c r="J34" s="37">
-        <v>100</v>
-      </c>
-      <c r="K34" s="37">
+      <c r="F34" s="11">
+        <v>100</v>
+      </c>
+      <c r="G34" s="11">
+        <v>0</v>
+      </c>
+      <c r="H34" s="11">
+        <v>100</v>
+      </c>
+      <c r="I34" s="11">
+        <v>0</v>
+      </c>
+      <c r="J34" s="11">
+        <v>100</v>
+      </c>
+      <c r="K34" s="11">
         <v>95</v>
       </c>
-      <c r="L34" s="15">
-        <v>100</v>
-      </c>
-      <c r="M34" s="15">
-        <v>100</v>
-      </c>
-      <c r="N34" s="37">
+      <c r="L34" s="11">
+        <v>100</v>
+      </c>
+      <c r="M34" s="11">
+        <v>100</v>
+      </c>
+      <c r="N34" s="35">
         <v>70</v>
       </c>
-      <c r="O34" s="15">
+      <c r="O34" s="11">
         <v>85</v>
       </c>
-      <c r="P34" s="37">
+      <c r="P34" s="11">
         <v>65</v>
       </c>
-      <c r="Q34" s="14">
+      <c r="Q34" s="10">
         <f>IF([1]punteo!L35="",0,[1]punteo!L35)</f>
         <v>80</v>
       </c>
@@ -4527,55 +4513,55 @@
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A35" s="38">
+      <c r="A35" s="27">
         <v>0.27777777777777779</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="C35" s="15">
+      <c r="C35" s="11">
         <v>31</v>
       </c>
-      <c r="D35" s="15">
+      <c r="D35" s="11">
         <v>202530349</v>
       </c>
-      <c r="E35" s="15" t="s">
+      <c r="E35" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F35" s="15">
-        <v>0</v>
-      </c>
-      <c r="G35" s="15">
-        <v>0</v>
-      </c>
-      <c r="H35" s="15">
-        <v>100</v>
-      </c>
-      <c r="I35" s="15">
-        <v>100</v>
-      </c>
-      <c r="J35" s="37">
-        <v>100</v>
-      </c>
-      <c r="K35" s="37">
+      <c r="F35" s="11">
+        <v>0</v>
+      </c>
+      <c r="G35" s="11">
+        <v>0</v>
+      </c>
+      <c r="H35" s="11">
+        <v>100</v>
+      </c>
+      <c r="I35" s="11">
+        <v>100</v>
+      </c>
+      <c r="J35" s="11">
+        <v>100</v>
+      </c>
+      <c r="K35" s="11">
         <v>75</v>
       </c>
-      <c r="L35" s="15">
-        <v>100</v>
-      </c>
-      <c r="M35" s="15">
-        <v>100</v>
-      </c>
-      <c r="N35" s="37">
+      <c r="L35" s="11">
+        <v>100</v>
+      </c>
+      <c r="M35" s="11">
+        <v>100</v>
+      </c>
+      <c r="N35" s="35">
         <v>80</v>
       </c>
-      <c r="O35" s="15">
+      <c r="O35" s="11">
         <v>90</v>
       </c>
-      <c r="P35" s="37">
+      <c r="P35" s="11">
         <v>60</v>
       </c>
-      <c r="Q35" s="14">
+      <c r="Q35" s="10">
         <f>IF([1]punteo!L36="",0,[1]punteo!L36)</f>
         <v>100</v>
       </c>
@@ -4602,51 +4588,51 @@
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A36" s="15"/>
-      <c r="B36" s="16"/>
-      <c r="C36" s="15">
+      <c r="A36" s="11"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="11">
         <v>32</v>
       </c>
-      <c r="D36" s="15">
+      <c r="D36" s="11">
         <v>202530357</v>
       </c>
-      <c r="E36" s="15" t="s">
+      <c r="E36" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="F36" s="15">
-        <v>100</v>
-      </c>
-      <c r="G36" s="15">
-        <v>0</v>
-      </c>
-      <c r="H36" s="15">
-        <v>100</v>
-      </c>
-      <c r="I36" s="15">
-        <v>100</v>
-      </c>
-      <c r="J36" s="37">
-        <v>100</v>
-      </c>
-      <c r="K36" s="37">
-        <v>100</v>
-      </c>
-      <c r="L36" s="15">
-        <v>100</v>
-      </c>
-      <c r="M36" s="15">
-        <v>100</v>
-      </c>
-      <c r="N36" s="37">
+      <c r="F36" s="11">
+        <v>100</v>
+      </c>
+      <c r="G36" s="11">
+        <v>0</v>
+      </c>
+      <c r="H36" s="11">
+        <v>100</v>
+      </c>
+      <c r="I36" s="11">
+        <v>100</v>
+      </c>
+      <c r="J36" s="11">
+        <v>100</v>
+      </c>
+      <c r="K36" s="11">
+        <v>100</v>
+      </c>
+      <c r="L36" s="11">
+        <v>100</v>
+      </c>
+      <c r="M36" s="11">
+        <v>100</v>
+      </c>
+      <c r="N36" s="35">
         <v>80</v>
       </c>
-      <c r="O36" s="15">
+      <c r="O36" s="11">
         <v>65</v>
       </c>
-      <c r="P36" s="37">
+      <c r="P36" s="11">
         <v>80</v>
       </c>
-      <c r="Q36" s="14">
+      <c r="Q36" s="10">
         <f>IF([1]punteo!L37="",0,[1]punteo!L37)</f>
         <v>100</v>
       </c>
@@ -4673,51 +4659,51 @@
       </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A37" s="15"/>
-      <c r="B37" s="16"/>
-      <c r="C37" s="15">
+      <c r="A37" s="11"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="11">
         <v>33</v>
       </c>
-      <c r="D37" s="15">
+      <c r="D37" s="11">
         <v>202530381</v>
       </c>
-      <c r="E37" s="15" t="s">
+      <c r="E37" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="F37" s="15">
-        <v>100</v>
-      </c>
-      <c r="G37" s="15">
-        <v>100</v>
-      </c>
-      <c r="H37" s="15">
-        <v>100</v>
-      </c>
-      <c r="I37" s="15">
-        <v>100</v>
-      </c>
-      <c r="J37" s="37">
-        <v>100</v>
-      </c>
-      <c r="K37" s="37">
-        <v>100</v>
-      </c>
-      <c r="L37" s="15">
-        <v>100</v>
-      </c>
-      <c r="M37" s="15">
-        <v>100</v>
-      </c>
-      <c r="N37" s="37">
+      <c r="F37" s="11">
+        <v>100</v>
+      </c>
+      <c r="G37" s="11">
+        <v>100</v>
+      </c>
+      <c r="H37" s="11">
+        <v>100</v>
+      </c>
+      <c r="I37" s="11">
+        <v>100</v>
+      </c>
+      <c r="J37" s="11">
+        <v>100</v>
+      </c>
+      <c r="K37" s="11">
+        <v>100</v>
+      </c>
+      <c r="L37" s="11">
+        <v>100</v>
+      </c>
+      <c r="M37" s="11">
+        <v>100</v>
+      </c>
+      <c r="N37" s="35">
         <v>50</v>
       </c>
-      <c r="O37" s="15">
+      <c r="O37" s="11">
         <v>90</v>
       </c>
-      <c r="P37" s="37">
+      <c r="P37" s="11">
         <v>45</v>
       </c>
-      <c r="Q37" s="14">
+      <c r="Q37" s="10">
         <f>IF([1]punteo!L38="",0,[1]punteo!L38)</f>
         <v>80</v>
       </c>
@@ -4744,55 +4730,55 @@
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A38" s="38">
+      <c r="A38" s="27">
         <v>0.27777777777777779</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C38" s="15">
+      <c r="C38" s="11">
         <v>34</v>
       </c>
-      <c r="D38" s="15">
+      <c r="D38" s="11">
         <v>202530434</v>
       </c>
-      <c r="E38" s="15" t="s">
+      <c r="E38" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="F38" s="15">
-        <v>100</v>
-      </c>
-      <c r="G38" s="15">
-        <v>0</v>
-      </c>
-      <c r="H38" s="15">
-        <v>100</v>
-      </c>
-      <c r="I38" s="15">
+      <c r="F38" s="11">
+        <v>100</v>
+      </c>
+      <c r="G38" s="11">
+        <v>0</v>
+      </c>
+      <c r="H38" s="11">
+        <v>100</v>
+      </c>
+      <c r="I38" s="11">
         <v>90</v>
       </c>
-      <c r="J38" s="37">
+      <c r="J38" s="11">
         <v>75</v>
       </c>
-      <c r="K38" s="37">
+      <c r="K38" s="11">
         <v>55</v>
       </c>
-      <c r="L38" s="15">
-        <v>100</v>
-      </c>
-      <c r="M38" s="15">
-        <v>100</v>
-      </c>
-      <c r="N38" s="37">
+      <c r="L38" s="11">
+        <v>100</v>
+      </c>
+      <c r="M38" s="11">
+        <v>100</v>
+      </c>
+      <c r="N38" s="35">
         <v>90</v>
       </c>
-      <c r="O38" s="15">
+      <c r="O38" s="11">
         <v>75</v>
       </c>
-      <c r="P38" s="37">
-        <v>100</v>
-      </c>
-      <c r="Q38" s="14">
+      <c r="P38" s="11">
+        <v>100</v>
+      </c>
+      <c r="Q38" s="10">
         <f>IF([1]punteo!L39="",0,[1]punteo!L39)</f>
         <v>95</v>
       </c>
@@ -4819,55 +4805,55 @@
       </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A39" s="38">
+      <c r="A39" s="27">
         <v>0.27777777777777779</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="11">
         <v>35</v>
       </c>
-      <c r="D39" s="15">
+      <c r="D39" s="11">
         <v>202530446</v>
       </c>
-      <c r="E39" s="15" t="s">
+      <c r="E39" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="F39" s="15">
-        <v>100</v>
-      </c>
-      <c r="G39" s="15">
-        <v>0</v>
-      </c>
-      <c r="H39" s="15">
-        <v>100</v>
-      </c>
-      <c r="I39" s="15">
-        <v>0</v>
-      </c>
-      <c r="J39" s="37">
-        <v>100</v>
-      </c>
-      <c r="K39" s="37">
-        <v>100</v>
-      </c>
-      <c r="L39" s="15">
-        <v>100</v>
-      </c>
-      <c r="M39" s="15">
-        <v>100</v>
-      </c>
-      <c r="N39" s="37">
+      <c r="F39" s="11">
+        <v>100</v>
+      </c>
+      <c r="G39" s="11">
+        <v>0</v>
+      </c>
+      <c r="H39" s="11">
+        <v>100</v>
+      </c>
+      <c r="I39" s="11">
+        <v>0</v>
+      </c>
+      <c r="J39" s="11">
+        <v>100</v>
+      </c>
+      <c r="K39" s="11">
+        <v>100</v>
+      </c>
+      <c r="L39" s="11">
+        <v>100</v>
+      </c>
+      <c r="M39" s="11">
+        <v>100</v>
+      </c>
+      <c r="N39" s="35">
         <v>50</v>
       </c>
-      <c r="O39" s="15">
+      <c r="O39" s="11">
         <v>85</v>
       </c>
-      <c r="P39" s="37">
+      <c r="P39" s="11">
         <v>80</v>
       </c>
-      <c r="Q39" s="14">
+      <c r="Q39" s="10">
         <f>IF([1]punteo!L40="",0,[1]punteo!L40)</f>
         <v>100</v>
       </c>
@@ -4894,51 +4880,51 @@
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A40" s="15"/>
-      <c r="B40" s="16"/>
-      <c r="C40" s="15">
+      <c r="A40" s="11"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="11">
         <v>36</v>
       </c>
-      <c r="D40" s="15">
+      <c r="D40" s="11">
         <v>202530522</v>
       </c>
-      <c r="E40" s="15" t="s">
+      <c r="E40" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F40" s="15">
-        <v>100</v>
-      </c>
-      <c r="G40" s="15">
-        <v>0</v>
-      </c>
-      <c r="H40" s="15">
-        <v>100</v>
-      </c>
-      <c r="I40" s="15">
-        <v>0</v>
-      </c>
-      <c r="J40" s="37">
-        <v>100</v>
-      </c>
-      <c r="K40" s="37">
-        <v>100</v>
-      </c>
-      <c r="L40" s="15">
-        <v>100</v>
-      </c>
-      <c r="M40" s="15">
-        <v>100</v>
-      </c>
-      <c r="N40" s="37">
+      <c r="F40" s="11">
+        <v>100</v>
+      </c>
+      <c r="G40" s="11">
+        <v>0</v>
+      </c>
+      <c r="H40" s="11">
+        <v>100</v>
+      </c>
+      <c r="I40" s="11">
+        <v>0</v>
+      </c>
+      <c r="J40" s="11">
+        <v>100</v>
+      </c>
+      <c r="K40" s="11">
+        <v>100</v>
+      </c>
+      <c r="L40" s="11">
+        <v>100</v>
+      </c>
+      <c r="M40" s="11">
+        <v>100</v>
+      </c>
+      <c r="N40" s="35">
         <v>50</v>
       </c>
-      <c r="O40" s="15">
+      <c r="O40" s="11">
         <v>80</v>
       </c>
-      <c r="P40" s="37">
+      <c r="P40" s="11">
         <v>80</v>
       </c>
-      <c r="Q40" s="14">
+      <c r="Q40" s="10">
         <f>IF([1]punteo!L41="",0,[1]punteo!L41)</f>
         <v>0</v>
       </c>
@@ -4965,51 +4951,51 @@
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A41" s="15"/>
-      <c r="B41" s="16"/>
-      <c r="C41" s="15">
+      <c r="A41" s="11"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="11">
         <v>37</v>
       </c>
-      <c r="D41" s="15">
+      <c r="D41" s="11">
         <v>202530613</v>
       </c>
-      <c r="E41" s="15" t="s">
+      <c r="E41" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F41" s="15">
-        <v>0</v>
-      </c>
-      <c r="G41" s="15">
-        <v>100</v>
-      </c>
-      <c r="H41" s="15">
-        <v>0</v>
-      </c>
-      <c r="I41" s="15">
-        <v>0</v>
-      </c>
-      <c r="J41" s="37">
-        <v>0</v>
-      </c>
-      <c r="K41" s="37">
-        <v>0</v>
-      </c>
-      <c r="L41" s="15">
-        <v>0</v>
-      </c>
-      <c r="M41" s="15">
-        <v>0</v>
-      </c>
-      <c r="N41" s="37">
-        <v>0</v>
-      </c>
-      <c r="O41" s="15">
-        <v>0</v>
-      </c>
-      <c r="P41" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="14">
+      <c r="F41" s="11">
+        <v>0</v>
+      </c>
+      <c r="G41" s="11">
+        <v>100</v>
+      </c>
+      <c r="H41" s="11">
+        <v>0</v>
+      </c>
+      <c r="I41" s="11">
+        <v>0</v>
+      </c>
+      <c r="J41" s="11">
+        <v>0</v>
+      </c>
+      <c r="K41" s="11">
+        <v>0</v>
+      </c>
+      <c r="L41" s="11">
+        <v>0</v>
+      </c>
+      <c r="M41" s="11">
+        <v>0</v>
+      </c>
+      <c r="N41" s="35">
+        <v>0</v>
+      </c>
+      <c r="O41" s="11">
+        <v>0</v>
+      </c>
+      <c r="P41" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="10">
         <f>IF([1]punteo!L42="",0,[1]punteo!L42)</f>
         <v>0</v>
       </c>
@@ -5036,51 +5022,51 @@
       </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A42" s="15"/>
-      <c r="B42" s="16"/>
-      <c r="C42" s="15">
+      <c r="A42" s="11"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="11">
         <v>38</v>
       </c>
-      <c r="D42" s="15">
+      <c r="D42" s="11">
         <v>202530621</v>
       </c>
-      <c r="E42" s="15" t="s">
+      <c r="E42" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F42" s="15">
-        <v>100</v>
-      </c>
-      <c r="G42" s="15">
-        <v>0</v>
-      </c>
-      <c r="H42" s="15">
-        <v>100</v>
-      </c>
-      <c r="I42" s="15">
+      <c r="F42" s="11">
+        <v>100</v>
+      </c>
+      <c r="G42" s="11">
+        <v>0</v>
+      </c>
+      <c r="H42" s="11">
+        <v>100</v>
+      </c>
+      <c r="I42" s="11">
         <v>90</v>
       </c>
-      <c r="J42" s="37">
+      <c r="J42" s="11">
         <v>70</v>
       </c>
-      <c r="K42" s="37">
-        <v>100</v>
-      </c>
-      <c r="L42" s="15">
-        <v>100</v>
-      </c>
-      <c r="M42" s="15">
-        <v>100</v>
-      </c>
-      <c r="N42" s="37">
+      <c r="K42" s="11">
+        <v>100</v>
+      </c>
+      <c r="L42" s="11">
+        <v>100</v>
+      </c>
+      <c r="M42" s="11">
+        <v>100</v>
+      </c>
+      <c r="N42" s="35">
         <v>70</v>
       </c>
-      <c r="O42" s="15">
+      <c r="O42" s="11">
         <v>60</v>
       </c>
-      <c r="P42" s="37">
+      <c r="P42" s="11">
         <v>65</v>
       </c>
-      <c r="Q42" s="14">
+      <c r="Q42" s="10">
         <f>IF([1]punteo!L43="",0,[1]punteo!L43)</f>
         <v>80</v>
       </c>
@@ -5106,126 +5092,126 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="39">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A43" s="27">
         <v>0.27777777777777779</v>
       </c>
-      <c r="B43" s="12" t="s">
+      <c r="B43" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C43" s="37">
+      <c r="C43" s="11">
         <v>39</v>
       </c>
-      <c r="D43" s="37">
+      <c r="D43" s="11">
         <v>202530673</v>
       </c>
-      <c r="E43" s="37" t="s">
+      <c r="E43" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="F43" s="37">
-        <v>0</v>
-      </c>
-      <c r="G43" s="37">
-        <v>0</v>
-      </c>
-      <c r="H43" s="37">
-        <v>0</v>
-      </c>
-      <c r="I43" s="37">
-        <v>100</v>
-      </c>
-      <c r="J43" s="37">
-        <v>0</v>
-      </c>
-      <c r="K43" s="37">
-        <v>100</v>
-      </c>
-      <c r="L43" s="37">
-        <v>100</v>
-      </c>
-      <c r="M43" s="37">
-        <v>100</v>
-      </c>
-      <c r="N43" s="37">
+      <c r="F43" s="11">
+        <v>0</v>
+      </c>
+      <c r="G43" s="11">
+        <v>0</v>
+      </c>
+      <c r="H43" s="11">
+        <v>0</v>
+      </c>
+      <c r="I43" s="11">
+        <v>100</v>
+      </c>
+      <c r="J43" s="11">
+        <v>0</v>
+      </c>
+      <c r="K43" s="11">
+        <v>100</v>
+      </c>
+      <c r="L43" s="11">
+        <v>100</v>
+      </c>
+      <c r="M43" s="11">
+        <v>100</v>
+      </c>
+      <c r="N43" s="35">
         <v>70</v>
       </c>
-      <c r="O43" s="37">
+      <c r="O43" s="11">
         <v>95</v>
       </c>
-      <c r="P43" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="14">
+      <c r="P43" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="10">
         <v>50</v>
       </c>
-      <c r="R43" s="14">
+      <c r="R43" s="10">
         <f>IF([2]punteo!L44="",0,[2]punteo!L44)</f>
         <v>0</v>
       </c>
-      <c r="S43" s="14">
+      <c r="S43" s="10">
         <f>IF([3]punteo!L44="",0,[3]punteo!L44)</f>
         <v>100</v>
       </c>
-      <c r="T43" s="14"/>
-      <c r="U43" s="14"/>
-      <c r="V43" s="13">
+      <c r="T43" s="10"/>
+      <c r="U43" s="10"/>
+      <c r="V43">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="W43" s="13">
+      <c r="W43">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="X43" s="13">
+      <c r="X43">
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A44" s="15"/>
-      <c r="B44" s="16"/>
-      <c r="C44" s="15">
+      <c r="A44" s="11"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="11">
         <v>40</v>
       </c>
-      <c r="D44" s="15">
+      <c r="D44" s="11">
         <v>202530674</v>
       </c>
-      <c r="E44" s="15" t="s">
+      <c r="E44" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F44" s="15">
-        <v>0</v>
-      </c>
-      <c r="G44" s="15">
-        <v>0</v>
-      </c>
-      <c r="H44" s="15">
+      <c r="F44" s="11">
+        <v>0</v>
+      </c>
+      <c r="G44" s="11">
+        <v>0</v>
+      </c>
+      <c r="H44" s="11">
         <v>50</v>
       </c>
-      <c r="I44" s="15">
-        <v>0</v>
-      </c>
-      <c r="J44" s="37">
-        <v>100</v>
-      </c>
-      <c r="K44" s="37">
-        <v>100</v>
-      </c>
-      <c r="L44" s="15">
+      <c r="I44" s="11">
+        <v>0</v>
+      </c>
+      <c r="J44" s="11">
+        <v>100</v>
+      </c>
+      <c r="K44" s="11">
+        <v>100</v>
+      </c>
+      <c r="L44" s="11">
         <v>90</v>
       </c>
-      <c r="M44" s="15">
-        <v>100</v>
-      </c>
-      <c r="N44" s="37">
+      <c r="M44" s="11">
+        <v>100</v>
+      </c>
+      <c r="N44" s="35">
         <v>50</v>
       </c>
-      <c r="O44" s="15">
+      <c r="O44" s="11">
         <v>85</v>
       </c>
-      <c r="P44" s="37">
+      <c r="P44" s="11">
         <v>70</v>
       </c>
-      <c r="Q44" s="14">
+      <c r="Q44" s="10">
         <f>IF([1]punteo!L45="",0,[1]punteo!L45)</f>
         <v>0</v>
       </c>
@@ -5252,51 +5238,51 @@
       </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A45" s="15"/>
-      <c r="B45" s="16"/>
-      <c r="C45" s="15">
+      <c r="A45" s="11"/>
+      <c r="B45" s="12"/>
+      <c r="C45" s="11">
         <v>41</v>
       </c>
-      <c r="D45" s="15">
+      <c r="D45" s="11">
         <v>202530677</v>
       </c>
-      <c r="E45" s="15" t="s">
+      <c r="E45" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F45" s="15">
-        <v>100</v>
-      </c>
-      <c r="G45" s="15">
-        <v>0</v>
-      </c>
-      <c r="H45" s="15">
-        <v>100</v>
-      </c>
-      <c r="I45" s="15">
-        <v>0</v>
-      </c>
-      <c r="J45" s="37">
-        <v>100</v>
-      </c>
-      <c r="K45" s="37">
-        <v>0</v>
-      </c>
-      <c r="L45" s="15">
-        <v>100</v>
-      </c>
-      <c r="M45" s="15">
-        <v>0</v>
-      </c>
-      <c r="N45" s="37">
-        <v>0</v>
-      </c>
-      <c r="O45" s="15">
-        <v>0</v>
-      </c>
-      <c r="P45" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="14">
+      <c r="F45" s="11">
+        <v>100</v>
+      </c>
+      <c r="G45" s="11">
+        <v>0</v>
+      </c>
+      <c r="H45" s="11">
+        <v>100</v>
+      </c>
+      <c r="I45" s="11">
+        <v>0</v>
+      </c>
+      <c r="J45" s="11">
+        <v>100</v>
+      </c>
+      <c r="K45" s="11">
+        <v>0</v>
+      </c>
+      <c r="L45" s="11">
+        <v>100</v>
+      </c>
+      <c r="M45" s="11">
+        <v>0</v>
+      </c>
+      <c r="N45" s="35">
+        <v>0</v>
+      </c>
+      <c r="O45" s="11">
+        <v>0</v>
+      </c>
+      <c r="P45" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="10">
         <f>IF([1]punteo!L46="",0,[1]punteo!L46)</f>
         <v>0</v>
       </c>
@@ -5323,55 +5309,55 @@
       </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A46" s="38">
+      <c r="A46" s="27">
         <v>0.27777777777777779</v>
       </c>
       <c r="B46" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C46" s="15">
+      <c r="C46" s="11">
         <v>42</v>
       </c>
-      <c r="D46" s="15">
+      <c r="D46" s="11">
         <v>202530728</v>
       </c>
-      <c r="E46" s="15" t="s">
+      <c r="E46" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="F46" s="15">
-        <v>100</v>
-      </c>
-      <c r="G46" s="15">
-        <v>0</v>
-      </c>
-      <c r="H46" s="15">
-        <v>100</v>
-      </c>
-      <c r="I46" s="15">
-        <v>0</v>
-      </c>
-      <c r="J46" s="37">
-        <v>100</v>
-      </c>
-      <c r="K46" s="37">
-        <v>100</v>
-      </c>
-      <c r="L46" s="15">
-        <v>0</v>
-      </c>
-      <c r="M46" s="15">
-        <v>100</v>
-      </c>
-      <c r="N46" s="37">
+      <c r="F46" s="11">
+        <v>100</v>
+      </c>
+      <c r="G46" s="11">
+        <v>0</v>
+      </c>
+      <c r="H46" s="11">
+        <v>100</v>
+      </c>
+      <c r="I46" s="11">
+        <v>0</v>
+      </c>
+      <c r="J46" s="11">
+        <v>100</v>
+      </c>
+      <c r="K46" s="11">
+        <v>100</v>
+      </c>
+      <c r="L46" s="11">
+        <v>0</v>
+      </c>
+      <c r="M46" s="11">
+        <v>100</v>
+      </c>
+      <c r="N46" s="35">
         <v>70</v>
       </c>
-      <c r="O46" s="15">
+      <c r="O46" s="11">
         <v>85</v>
       </c>
-      <c r="P46" s="37">
+      <c r="P46" s="11">
         <v>50</v>
       </c>
-      <c r="Q46" s="14">
+      <c r="Q46" s="10">
         <f>IF([1]punteo!L47="",0,[1]punteo!L47)</f>
         <v>80</v>
       </c>
@@ -5398,55 +5384,55 @@
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A47" s="38">
+      <c r="A47" s="27">
         <v>0.27777777777777779</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C47" s="15">
+      <c r="C47" s="11">
         <v>43</v>
       </c>
-      <c r="D47" s="15">
+      <c r="D47" s="11">
         <v>202530843</v>
       </c>
-      <c r="E47" s="15" t="s">
+      <c r="E47" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="F47" s="15">
-        <v>0</v>
-      </c>
-      <c r="G47" s="15">
-        <v>0</v>
-      </c>
-      <c r="H47" s="15">
-        <v>0</v>
-      </c>
-      <c r="I47" s="15">
-        <v>0</v>
-      </c>
-      <c r="J47" s="37">
-        <v>100</v>
-      </c>
-      <c r="K47" s="37">
-        <v>100</v>
-      </c>
-      <c r="L47" s="15">
-        <v>0</v>
-      </c>
-      <c r="M47" s="15">
-        <v>100</v>
-      </c>
-      <c r="N47" s="37">
+      <c r="F47" s="11">
+        <v>0</v>
+      </c>
+      <c r="G47" s="11">
+        <v>0</v>
+      </c>
+      <c r="H47" s="11">
+        <v>0</v>
+      </c>
+      <c r="I47" s="11">
+        <v>0</v>
+      </c>
+      <c r="J47" s="11">
+        <v>100</v>
+      </c>
+      <c r="K47" s="11">
+        <v>100</v>
+      </c>
+      <c r="L47" s="11">
+        <v>0</v>
+      </c>
+      <c r="M47" s="11">
+        <v>100</v>
+      </c>
+      <c r="N47" s="35">
         <v>70</v>
       </c>
-      <c r="O47" s="15">
+      <c r="O47" s="11">
         <v>85</v>
       </c>
-      <c r="P47" s="37">
+      <c r="P47" s="11">
         <v>85</v>
       </c>
-      <c r="Q47" s="14">
+      <c r="Q47" s="10">
         <f>IF([1]punteo!L48="",0,[1]punteo!L48)</f>
         <v>80</v>
       </c>
@@ -5473,51 +5459,51 @@
       </c>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A48" s="15"/>
-      <c r="B48" s="16"/>
-      <c r="C48" s="15">
+      <c r="A48" s="11"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="11">
         <v>44</v>
       </c>
-      <c r="D48" s="15">
+      <c r="D48" s="11">
         <v>202530866</v>
       </c>
-      <c r="E48" s="15" t="s">
+      <c r="E48" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="F48" s="15">
-        <v>100</v>
-      </c>
-      <c r="G48" s="15">
-        <v>0</v>
-      </c>
-      <c r="H48" s="15">
-        <v>100</v>
-      </c>
-      <c r="I48" s="15">
+      <c r="F48" s="11">
+        <v>100</v>
+      </c>
+      <c r="G48" s="11">
+        <v>0</v>
+      </c>
+      <c r="H48" s="11">
+        <v>100</v>
+      </c>
+      <c r="I48" s="11">
         <v>90</v>
       </c>
-      <c r="J48" s="37">
-        <v>100</v>
-      </c>
-      <c r="K48" s="37">
-        <v>100</v>
-      </c>
-      <c r="L48" s="15">
+      <c r="J48" s="11">
+        <v>100</v>
+      </c>
+      <c r="K48" s="11">
+        <v>100</v>
+      </c>
+      <c r="L48" s="11">
         <v>90</v>
       </c>
-      <c r="M48" s="15">
-        <v>100</v>
-      </c>
-      <c r="N48" s="37">
+      <c r="M48" s="11">
+        <v>100</v>
+      </c>
+      <c r="N48" s="35">
         <v>50</v>
       </c>
-      <c r="O48" s="15">
+      <c r="O48" s="11">
         <v>85</v>
       </c>
-      <c r="P48" s="37">
+      <c r="P48" s="11">
         <v>55</v>
       </c>
-      <c r="Q48" s="14">
+      <c r="Q48" s="10">
         <f>IF([1]punteo!L49="",0,[1]punteo!L49)</f>
         <v>100</v>
       </c>
@@ -5544,55 +5530,55 @@
       </c>
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A49" s="38">
+      <c r="A49" s="27">
         <v>0.27777777777777779</v>
       </c>
       <c r="B49" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C49" s="15">
+      <c r="C49" s="11">
         <v>45</v>
       </c>
-      <c r="D49" s="15">
+      <c r="D49" s="11">
         <v>202530917</v>
       </c>
-      <c r="E49" s="15" t="s">
+      <c r="E49" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="F49" s="15">
-        <v>0</v>
-      </c>
-      <c r="G49" s="15">
-        <v>0</v>
-      </c>
-      <c r="H49" s="15">
+      <c r="F49" s="11">
+        <v>0</v>
+      </c>
+      <c r="G49" s="11">
+        <v>0</v>
+      </c>
+      <c r="H49" s="11">
         <v>50</v>
       </c>
-      <c r="I49" s="15">
-        <v>100</v>
-      </c>
-      <c r="J49" s="37">
+      <c r="I49" s="11">
+        <v>100</v>
+      </c>
+      <c r="J49" s="11">
         <v>75</v>
       </c>
-      <c r="K49" s="37">
-        <v>100</v>
-      </c>
-      <c r="L49" s="15">
-        <v>100</v>
-      </c>
-      <c r="M49" s="15">
-        <v>100</v>
-      </c>
-      <c r="N49" s="37">
+      <c r="K49" s="11">
+        <v>100</v>
+      </c>
+      <c r="L49" s="11">
+        <v>100</v>
+      </c>
+      <c r="M49" s="11">
+        <v>100</v>
+      </c>
+      <c r="N49" s="35">
         <v>90</v>
       </c>
-      <c r="O49" s="15">
+      <c r="O49" s="11">
         <v>95</v>
       </c>
-      <c r="P49" s="37">
+      <c r="P49" s="11">
         <v>65</v>
       </c>
-      <c r="Q49" s="14">
+      <c r="Q49" s="10">
         <f>IF([1]punteo!L50="",0,[1]punteo!L50)</f>
         <v>100</v>
       </c>
@@ -5619,51 +5605,51 @@
       </c>
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A50" s="15"/>
-      <c r="B50" s="16"/>
-      <c r="C50" s="15">
+      <c r="A50" s="11"/>
+      <c r="B50" s="12"/>
+      <c r="C50" s="11">
         <v>46</v>
       </c>
-      <c r="D50" s="15">
+      <c r="D50" s="11">
         <v>202531013</v>
       </c>
-      <c r="E50" s="15" t="s">
+      <c r="E50" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="F50" s="15">
-        <v>100</v>
-      </c>
-      <c r="G50" s="15">
-        <v>0</v>
-      </c>
-      <c r="H50" s="15">
-        <v>100</v>
-      </c>
-      <c r="I50" s="15">
+      <c r="F50" s="11">
+        <v>100</v>
+      </c>
+      <c r="G50" s="11">
+        <v>0</v>
+      </c>
+      <c r="H50" s="11">
+        <v>100</v>
+      </c>
+      <c r="I50" s="11">
         <v>90</v>
       </c>
-      <c r="J50" s="37">
-        <v>100</v>
-      </c>
-      <c r="K50" s="37">
+      <c r="J50" s="11">
+        <v>100</v>
+      </c>
+      <c r="K50" s="11">
         <v>75</v>
       </c>
-      <c r="L50" s="15">
-        <v>100</v>
-      </c>
-      <c r="M50" s="15">
-        <v>100</v>
-      </c>
-      <c r="N50" s="37">
-        <v>100</v>
-      </c>
-      <c r="O50" s="15">
+      <c r="L50" s="11">
+        <v>100</v>
+      </c>
+      <c r="M50" s="11">
+        <v>100</v>
+      </c>
+      <c r="N50" s="35">
+        <v>100</v>
+      </c>
+      <c r="O50" s="11">
         <v>90</v>
       </c>
-      <c r="P50" s="37">
+      <c r="P50" s="11">
         <v>70</v>
       </c>
-      <c r="Q50" s="14">
+      <c r="Q50" s="10">
         <f>IF([1]punteo!L51="",0,[1]punteo!L51)</f>
         <v>100</v>
       </c>
@@ -5690,51 +5676,51 @@
       </c>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A51" s="15"/>
-      <c r="B51" s="16"/>
-      <c r="C51" s="15">
+      <c r="A51" s="11"/>
+      <c r="B51" s="12"/>
+      <c r="C51" s="11">
         <v>47</v>
       </c>
-      <c r="D51" s="15">
+      <c r="D51" s="11">
         <v>202531019</v>
       </c>
-      <c r="E51" s="15" t="s">
+      <c r="E51" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="F51" s="15">
-        <v>0</v>
-      </c>
-      <c r="G51" s="15">
-        <v>0</v>
-      </c>
-      <c r="H51" s="15">
-        <v>100</v>
-      </c>
-      <c r="I51" s="15">
+      <c r="F51" s="11">
+        <v>0</v>
+      </c>
+      <c r="G51" s="11">
+        <v>0</v>
+      </c>
+      <c r="H51" s="11">
+        <v>100</v>
+      </c>
+      <c r="I51" s="11">
         <v>90</v>
       </c>
-      <c r="J51" s="37">
-        <v>100</v>
-      </c>
-      <c r="K51" s="37">
+      <c r="J51" s="11">
+        <v>100</v>
+      </c>
+      <c r="K51" s="11">
         <v>55</v>
       </c>
-      <c r="L51" s="15">
-        <v>100</v>
-      </c>
-      <c r="M51" s="15">
-        <v>100</v>
-      </c>
-      <c r="N51" s="37">
+      <c r="L51" s="11">
+        <v>100</v>
+      </c>
+      <c r="M51" s="11">
+        <v>100</v>
+      </c>
+      <c r="N51" s="35">
         <v>95</v>
       </c>
-      <c r="O51" s="15">
-        <v>0</v>
-      </c>
-      <c r="P51" s="37">
+      <c r="O51" s="11">
+        <v>0</v>
+      </c>
+      <c r="P51" s="11">
         <v>55</v>
       </c>
-      <c r="Q51" s="14">
+      <c r="Q51" s="10">
         <f>IF([1]punteo!L52="",0,[1]punteo!L52)</f>
         <v>100</v>
       </c>
@@ -5761,51 +5747,51 @@
       </c>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A52" s="15"/>
-      <c r="B52" s="16"/>
-      <c r="C52" s="15">
+      <c r="A52" s="11"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="11">
         <v>48</v>
       </c>
-      <c r="D52" s="15">
+      <c r="D52" s="11">
         <v>202531089</v>
       </c>
-      <c r="E52" s="15" t="s">
+      <c r="E52" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="F52" s="15">
-        <v>100</v>
-      </c>
-      <c r="G52" s="15">
-        <v>0</v>
-      </c>
-      <c r="H52" s="15">
-        <v>100</v>
-      </c>
-      <c r="I52" s="15">
+      <c r="F52" s="11">
+        <v>100</v>
+      </c>
+      <c r="G52" s="11">
+        <v>0</v>
+      </c>
+      <c r="H52" s="11">
+        <v>100</v>
+      </c>
+      <c r="I52" s="11">
         <v>90</v>
       </c>
-      <c r="J52" s="37">
+      <c r="J52" s="11">
         <v>70</v>
       </c>
-      <c r="K52" s="37">
-        <v>100</v>
-      </c>
-      <c r="L52" s="15">
+      <c r="K52" s="11">
+        <v>100</v>
+      </c>
+      <c r="L52" s="11">
         <v>90</v>
       </c>
-      <c r="M52" s="15">
-        <v>100</v>
-      </c>
-      <c r="N52" s="37">
+      <c r="M52" s="11">
+        <v>100</v>
+      </c>
+      <c r="N52" s="35">
         <v>50</v>
       </c>
-      <c r="O52" s="15">
+      <c r="O52" s="11">
         <v>85</v>
       </c>
-      <c r="P52" s="37">
+      <c r="P52" s="11">
         <v>55</v>
       </c>
-      <c r="Q52" s="14">
+      <c r="Q52" s="10">
         <f>IF([1]punteo!L53="",0,[1]punteo!L53)</f>
         <v>100</v>
       </c>
@@ -5832,51 +5818,51 @@
       </c>
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A53" s="15"/>
-      <c r="B53" s="16"/>
-      <c r="C53" s="15">
+      <c r="A53" s="11"/>
+      <c r="B53" s="12"/>
+      <c r="C53" s="11">
         <v>49</v>
       </c>
-      <c r="D53" s="15">
+      <c r="D53" s="11">
         <v>202531127</v>
       </c>
-      <c r="E53" s="15" t="s">
+      <c r="E53" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F53" s="15">
-        <v>0</v>
-      </c>
-      <c r="G53" s="15">
-        <v>0</v>
-      </c>
-      <c r="H53" s="15">
-        <v>100</v>
-      </c>
-      <c r="I53" s="15">
-        <v>0</v>
-      </c>
-      <c r="J53" s="37">
-        <v>0</v>
-      </c>
-      <c r="K53" s="37">
-        <v>100</v>
-      </c>
-      <c r="L53" s="15">
-        <v>0</v>
-      </c>
-      <c r="M53" s="15">
-        <v>100</v>
-      </c>
-      <c r="N53" s="37">
+      <c r="F53" s="11">
+        <v>0</v>
+      </c>
+      <c r="G53" s="11">
+        <v>0</v>
+      </c>
+      <c r="H53" s="11">
+        <v>100</v>
+      </c>
+      <c r="I53" s="11">
+        <v>0</v>
+      </c>
+      <c r="J53" s="11">
+        <v>0</v>
+      </c>
+      <c r="K53" s="11">
+        <v>100</v>
+      </c>
+      <c r="L53" s="11">
+        <v>0</v>
+      </c>
+      <c r="M53" s="11">
+        <v>100</v>
+      </c>
+      <c r="N53" s="35">
         <v>70</v>
       </c>
-      <c r="O53" s="15">
+      <c r="O53" s="11">
         <v>85</v>
       </c>
-      <c r="P53" s="37">
+      <c r="P53" s="11">
         <v>85</v>
       </c>
-      <c r="Q53" s="14">
+      <c r="Q53" s="10">
         <f>IF([1]punteo!L54="",0,[1]punteo!L54)</f>
         <v>80</v>
       </c>
@@ -5903,51 +5889,51 @@
       </c>
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A54" s="15"/>
-      <c r="B54" s="16"/>
-      <c r="C54" s="15">
+      <c r="A54" s="11"/>
+      <c r="B54" s="12"/>
+      <c r="C54" s="11">
         <v>50</v>
       </c>
-      <c r="D54" s="15">
+      <c r="D54" s="11">
         <v>202531213</v>
       </c>
-      <c r="E54" s="15" t="s">
+      <c r="E54" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="F54" s="15">
-        <v>100</v>
-      </c>
-      <c r="G54" s="15">
-        <v>100</v>
-      </c>
-      <c r="H54" s="15">
-        <v>100</v>
-      </c>
-      <c r="I54" s="15">
+      <c r="F54" s="11">
+        <v>100</v>
+      </c>
+      <c r="G54" s="11">
+        <v>100</v>
+      </c>
+      <c r="H54" s="11">
+        <v>100</v>
+      </c>
+      <c r="I54" s="11">
         <v>90</v>
       </c>
-      <c r="J54" s="37">
-        <v>100</v>
-      </c>
-      <c r="K54" s="37">
+      <c r="J54" s="11">
+        <v>100</v>
+      </c>
+      <c r="K54" s="11">
         <v>90</v>
       </c>
-      <c r="L54" s="15">
-        <v>100</v>
-      </c>
-      <c r="M54" s="15">
-        <v>100</v>
-      </c>
-      <c r="N54" s="37">
+      <c r="L54" s="11">
+        <v>100</v>
+      </c>
+      <c r="M54" s="11">
+        <v>100</v>
+      </c>
+      <c r="N54" s="35">
         <v>80</v>
       </c>
-      <c r="O54" s="15">
-        <v>100</v>
-      </c>
-      <c r="P54" s="37">
-        <v>100</v>
-      </c>
-      <c r="Q54" s="14">
+      <c r="O54" s="11">
+        <v>100</v>
+      </c>
+      <c r="P54" s="11">
+        <v>100</v>
+      </c>
+      <c r="Q54" s="10">
         <f>IF([1]punteo!L55="",0,[1]punteo!L55)</f>
         <v>90</v>
       </c>
@@ -5974,51 +5960,51 @@
       </c>
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A55" s="15"/>
-      <c r="B55" s="16"/>
-      <c r="C55" s="15">
+      <c r="A55" s="11"/>
+      <c r="B55" s="12"/>
+      <c r="C55" s="11">
         <v>51</v>
       </c>
-      <c r="D55" s="15">
+      <c r="D55" s="11">
         <v>202531219</v>
       </c>
-      <c r="E55" s="15" t="s">
+      <c r="E55" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="F55" s="15">
-        <v>0</v>
-      </c>
-      <c r="G55" s="15">
-        <v>0</v>
-      </c>
-      <c r="H55" s="15">
-        <v>100</v>
-      </c>
-      <c r="I55" s="15">
-        <v>100</v>
-      </c>
-      <c r="J55" s="37">
+      <c r="F55" s="11">
+        <v>0</v>
+      </c>
+      <c r="G55" s="11">
+        <v>0</v>
+      </c>
+      <c r="H55" s="11">
+        <v>100</v>
+      </c>
+      <c r="I55" s="11">
+        <v>100</v>
+      </c>
+      <c r="J55" s="11">
         <v>75</v>
       </c>
-      <c r="K55" s="37">
+      <c r="K55" s="11">
         <v>90</v>
       </c>
-      <c r="L55" s="15">
-        <v>100</v>
-      </c>
-      <c r="M55" s="15">
+      <c r="L55" s="11">
+        <v>100</v>
+      </c>
+      <c r="M55" s="11">
         <v>80</v>
       </c>
-      <c r="N55" s="37">
+      <c r="N55" s="35">
         <v>70</v>
       </c>
-      <c r="O55" s="15">
+      <c r="O55" s="11">
         <v>45</v>
       </c>
-      <c r="P55" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="14">
+      <c r="P55" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="10">
         <f>IF([1]punteo!L56="",0,[1]punteo!L56)</f>
         <v>80</v>
       </c>
@@ -6045,51 +6031,51 @@
       </c>
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A56" s="15"/>
-      <c r="B56" s="16"/>
-      <c r="C56" s="15">
+      <c r="A56" s="11"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="11">
         <v>52</v>
       </c>
-      <c r="D56" s="15">
+      <c r="D56" s="11">
         <v>202531289</v>
       </c>
-      <c r="E56" s="15" t="s">
+      <c r="E56" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="F56" s="15">
-        <v>100</v>
-      </c>
-      <c r="G56" s="15">
-        <v>0</v>
-      </c>
-      <c r="H56" s="15">
-        <v>100</v>
-      </c>
-      <c r="I56" s="15">
-        <v>100</v>
-      </c>
-      <c r="J56" s="37">
+      <c r="F56" s="11">
+        <v>100</v>
+      </c>
+      <c r="G56" s="11">
+        <v>0</v>
+      </c>
+      <c r="H56" s="11">
+        <v>100</v>
+      </c>
+      <c r="I56" s="11">
+        <v>100</v>
+      </c>
+      <c r="J56" s="11">
         <v>85</v>
       </c>
-      <c r="K56" s="37">
-        <v>100</v>
-      </c>
-      <c r="L56" s="15">
-        <v>100</v>
-      </c>
-      <c r="M56" s="15">
-        <v>100</v>
-      </c>
-      <c r="N56" s="37">
-        <v>100</v>
-      </c>
-      <c r="O56" s="15">
+      <c r="K56" s="11">
+        <v>100</v>
+      </c>
+      <c r="L56" s="11">
+        <v>100</v>
+      </c>
+      <c r="M56" s="11">
+        <v>100</v>
+      </c>
+      <c r="N56" s="35">
+        <v>100</v>
+      </c>
+      <c r="O56" s="11">
         <v>95</v>
       </c>
-      <c r="P56" s="37">
+      <c r="P56" s="11">
         <v>85</v>
       </c>
-      <c r="Q56" s="14">
+      <c r="Q56" s="10">
         <f>IF([1]punteo!L57="",0,[1]punteo!L57)</f>
         <v>95</v>
       </c>
@@ -6116,55 +6102,55 @@
       </c>
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A57" s="38">
+      <c r="A57" s="27">
         <v>0.27777777777777779</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C57" s="15">
+      <c r="C57" s="11">
         <v>53</v>
       </c>
-      <c r="D57" s="15">
+      <c r="D57" s="11">
         <v>202531319</v>
       </c>
-      <c r="E57" s="15" t="s">
+      <c r="E57" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="F57" s="15">
-        <v>100</v>
-      </c>
-      <c r="G57" s="15">
-        <v>0</v>
-      </c>
-      <c r="H57" s="15">
+      <c r="F57" s="11">
+        <v>100</v>
+      </c>
+      <c r="G57" s="11">
+        <v>0</v>
+      </c>
+      <c r="H57" s="11">
         <v>50</v>
       </c>
-      <c r="I57" s="15">
-        <v>100</v>
-      </c>
-      <c r="J57" s="37">
+      <c r="I57" s="11">
+        <v>100</v>
+      </c>
+      <c r="J57" s="11">
         <v>75</v>
       </c>
-      <c r="K57" s="37">
-        <v>100</v>
-      </c>
-      <c r="L57" s="15">
-        <v>100</v>
-      </c>
-      <c r="M57" s="15">
-        <v>100</v>
-      </c>
-      <c r="N57" s="37">
+      <c r="K57" s="11">
+        <v>100</v>
+      </c>
+      <c r="L57" s="11">
+        <v>100</v>
+      </c>
+      <c r="M57" s="11">
+        <v>100</v>
+      </c>
+      <c r="N57" s="35">
         <v>50</v>
       </c>
-      <c r="O57" s="15">
-        <v>0</v>
-      </c>
-      <c r="P57" s="37">
+      <c r="O57" s="11">
+        <v>0</v>
+      </c>
+      <c r="P57" s="11">
         <v>50</v>
       </c>
-      <c r="Q57" s="14">
+      <c r="Q57" s="10">
         <f>IF([1]punteo!L58="",0,[1]punteo!L58)</f>
         <v>100</v>
       </c>
@@ -6191,55 +6177,55 @@
       </c>
     </row>
     <row r="58" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A58" s="38">
+      <c r="A58" s="27">
         <v>0.27777777777777779</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C58" s="15">
+      <c r="C58" s="11">
         <v>54</v>
       </c>
-      <c r="D58" s="15">
+      <c r="D58" s="11">
         <v>202531351</v>
       </c>
-      <c r="E58" s="15" t="s">
+      <c r="E58" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F58" s="15">
-        <v>100</v>
-      </c>
-      <c r="G58" s="15">
-        <v>100</v>
-      </c>
-      <c r="H58" s="15">
-        <v>100</v>
-      </c>
-      <c r="I58" s="15">
+      <c r="F58" s="11">
+        <v>100</v>
+      </c>
+      <c r="G58" s="11">
+        <v>100</v>
+      </c>
+      <c r="H58" s="11">
+        <v>100</v>
+      </c>
+      <c r="I58" s="11">
         <v>90</v>
       </c>
-      <c r="J58" s="37">
-        <v>100</v>
-      </c>
-      <c r="K58" s="37">
-        <v>100</v>
-      </c>
-      <c r="L58" s="15">
-        <v>100</v>
-      </c>
-      <c r="M58" s="15">
-        <v>100</v>
-      </c>
-      <c r="N58" s="37">
+      <c r="J58" s="11">
+        <v>100</v>
+      </c>
+      <c r="K58" s="11">
+        <v>100</v>
+      </c>
+      <c r="L58" s="11">
+        <v>100</v>
+      </c>
+      <c r="M58" s="11">
+        <v>100</v>
+      </c>
+      <c r="N58" s="35">
         <v>80</v>
       </c>
-      <c r="O58" s="15">
+      <c r="O58" s="11">
         <v>90</v>
       </c>
-      <c r="P58" s="37">
-        <v>100</v>
-      </c>
-      <c r="Q58" s="14">
+      <c r="P58" s="11">
+        <v>100</v>
+      </c>
+      <c r="Q58" s="10">
         <f>IF([1]punteo!L59="",0,[1]punteo!L59)</f>
         <v>90</v>
       </c>
@@ -6266,55 +6252,55 @@
       </c>
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A59" s="38">
+      <c r="A59" s="27">
         <v>0.27777777777777779</v>
       </c>
       <c r="B59" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C59" s="15">
+      <c r="C59" s="11">
         <v>55</v>
       </c>
-      <c r="D59" s="15">
+      <c r="D59" s="11">
         <v>202531352</v>
       </c>
-      <c r="E59" s="15" t="s">
+      <c r="E59" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="F59" s="15">
-        <v>100</v>
-      </c>
-      <c r="G59" s="15">
-        <v>0</v>
-      </c>
-      <c r="H59" s="15">
-        <v>100</v>
-      </c>
-      <c r="I59" s="15">
-        <v>100</v>
-      </c>
-      <c r="J59" s="37">
-        <v>100</v>
-      </c>
-      <c r="K59" s="37">
-        <v>100</v>
-      </c>
-      <c r="L59" s="15">
-        <v>100</v>
-      </c>
-      <c r="M59" s="15">
-        <v>100</v>
-      </c>
-      <c r="N59" s="37">
+      <c r="F59" s="11">
+        <v>100</v>
+      </c>
+      <c r="G59" s="11">
+        <v>0</v>
+      </c>
+      <c r="H59" s="11">
+        <v>100</v>
+      </c>
+      <c r="I59" s="11">
+        <v>100</v>
+      </c>
+      <c r="J59" s="11">
+        <v>100</v>
+      </c>
+      <c r="K59" s="11">
+        <v>100</v>
+      </c>
+      <c r="L59" s="11">
+        <v>100</v>
+      </c>
+      <c r="M59" s="11">
+        <v>100</v>
+      </c>
+      <c r="N59" s="35">
         <v>70</v>
       </c>
-      <c r="O59" s="15">
-        <v>0</v>
-      </c>
-      <c r="P59" s="37">
+      <c r="O59" s="11">
+        <v>0</v>
+      </c>
+      <c r="P59" s="11">
         <v>75</v>
       </c>
-      <c r="Q59" s="14">
+      <c r="Q59" s="10">
         <f>IF([1]punteo!L60="",0,[1]punteo!L60)</f>
         <v>80</v>
       </c>
@@ -6341,51 +6327,51 @@
       </c>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A60" s="15"/>
-      <c r="B60" s="16"/>
-      <c r="C60" s="15">
+      <c r="A60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="11">
         <v>56</v>
       </c>
-      <c r="D60" s="15">
+      <c r="D60" s="11">
         <v>202531384</v>
       </c>
-      <c r="E60" s="15" t="s">
+      <c r="E60" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="F60" s="15">
-        <v>100</v>
-      </c>
-      <c r="G60" s="15">
-        <v>100</v>
-      </c>
-      <c r="H60" s="15">
+      <c r="F60" s="11">
+        <v>100</v>
+      </c>
+      <c r="G60" s="11">
+        <v>100</v>
+      </c>
+      <c r="H60" s="11">
         <v>50</v>
       </c>
-      <c r="I60" s="15">
+      <c r="I60" s="11">
         <v>90</v>
       </c>
-      <c r="J60" s="37">
-        <v>100</v>
-      </c>
-      <c r="K60" s="37">
-        <v>100</v>
-      </c>
-      <c r="L60" s="15">
-        <v>100</v>
-      </c>
-      <c r="M60" s="15">
-        <v>100</v>
-      </c>
-      <c r="N60" s="37">
+      <c r="J60" s="11">
+        <v>100</v>
+      </c>
+      <c r="K60" s="11">
+        <v>100</v>
+      </c>
+      <c r="L60" s="11">
+        <v>100</v>
+      </c>
+      <c r="M60" s="11">
+        <v>100</v>
+      </c>
+      <c r="N60" s="35">
         <v>70</v>
       </c>
-      <c r="O60" s="15">
-        <v>100</v>
-      </c>
-      <c r="P60" s="37">
+      <c r="O60" s="11">
+        <v>100</v>
+      </c>
+      <c r="P60" s="11">
         <v>90</v>
       </c>
-      <c r="Q60" s="14">
+      <c r="Q60" s="10">
         <f>IF([1]punteo!L61="",0,[1]punteo!L61)</f>
         <v>80</v>
       </c>
@@ -6412,51 +6398,51 @@
       </c>
     </row>
     <row r="61" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A61" s="15"/>
-      <c r="B61" s="16"/>
-      <c r="C61" s="15">
+      <c r="A61" s="11"/>
+      <c r="B61" s="12"/>
+      <c r="C61" s="11">
         <v>57</v>
       </c>
-      <c r="D61" s="15">
+      <c r="D61" s="11">
         <v>202531399</v>
       </c>
-      <c r="E61" s="15" t="s">
+      <c r="E61" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="F61" s="15">
-        <v>0</v>
-      </c>
-      <c r="G61" s="15">
-        <v>0</v>
-      </c>
-      <c r="H61" s="15">
+      <c r="F61" s="11">
+        <v>0</v>
+      </c>
+      <c r="G61" s="11">
+        <v>0</v>
+      </c>
+      <c r="H61" s="11">
         <v>50</v>
       </c>
-      <c r="I61" s="15">
-        <v>0</v>
-      </c>
-      <c r="J61" s="37">
-        <v>0</v>
-      </c>
-      <c r="K61" s="37">
-        <v>0</v>
-      </c>
-      <c r="L61" s="15">
-        <v>0</v>
-      </c>
-      <c r="M61" s="15">
-        <v>0</v>
-      </c>
-      <c r="N61" s="37">
-        <v>0</v>
-      </c>
-      <c r="O61" s="15">
-        <v>0</v>
-      </c>
-      <c r="P61" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="14">
+      <c r="I61" s="11">
+        <v>0</v>
+      </c>
+      <c r="J61" s="11">
+        <v>0</v>
+      </c>
+      <c r="K61" s="11">
+        <v>0</v>
+      </c>
+      <c r="L61" s="11">
+        <v>0</v>
+      </c>
+      <c r="M61" s="11">
+        <v>0</v>
+      </c>
+      <c r="N61" s="35">
+        <v>0</v>
+      </c>
+      <c r="O61" s="11">
+        <v>0</v>
+      </c>
+      <c r="P61" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="10">
         <f>IF([1]punteo!L62="",0,[1]punteo!L62)</f>
         <v>0</v>
       </c>
@@ -6483,51 +6469,51 @@
       </c>
     </row>
     <row r="62" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A62" s="15"/>
-      <c r="B62" s="16"/>
-      <c r="C62" s="15">
+      <c r="A62" s="11"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="11">
         <v>58</v>
       </c>
-      <c r="D62" s="15">
+      <c r="D62" s="11">
         <v>202531441</v>
       </c>
-      <c r="E62" s="15" t="s">
+      <c r="E62" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="F62" s="15">
-        <v>0</v>
-      </c>
-      <c r="G62" s="15">
-        <v>0</v>
-      </c>
-      <c r="H62" s="15">
-        <v>0</v>
-      </c>
-      <c r="I62" s="15">
-        <v>0</v>
-      </c>
-      <c r="J62" s="37">
-        <v>0</v>
-      </c>
-      <c r="K62" s="37">
-        <v>0</v>
-      </c>
-      <c r="L62" s="15">
-        <v>0</v>
-      </c>
-      <c r="M62" s="15">
-        <v>0</v>
-      </c>
-      <c r="N62" s="37">
-        <v>0</v>
-      </c>
-      <c r="O62" s="15">
-        <v>0</v>
-      </c>
-      <c r="P62" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="14">
+      <c r="F62" s="11">
+        <v>0</v>
+      </c>
+      <c r="G62" s="11">
+        <v>0</v>
+      </c>
+      <c r="H62" s="11">
+        <v>0</v>
+      </c>
+      <c r="I62" s="11">
+        <v>0</v>
+      </c>
+      <c r="J62" s="11">
+        <v>0</v>
+      </c>
+      <c r="K62" s="11">
+        <v>0</v>
+      </c>
+      <c r="L62" s="11">
+        <v>0</v>
+      </c>
+      <c r="M62" s="11">
+        <v>0</v>
+      </c>
+      <c r="N62" s="35">
+        <v>0</v>
+      </c>
+      <c r="O62" s="11">
+        <v>0</v>
+      </c>
+      <c r="P62" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="10">
         <f>IF([1]punteo!L63="",0,[1]punteo!L63)</f>
         <v>0</v>
       </c>
@@ -6554,51 +6540,51 @@
       </c>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A63" s="15"/>
-      <c r="B63" s="16"/>
-      <c r="C63" s="15">
+      <c r="A63" s="11"/>
+      <c r="B63" s="12"/>
+      <c r="C63" s="11">
         <v>59</v>
       </c>
-      <c r="D63" s="15">
+      <c r="D63" s="11">
         <v>202531444</v>
       </c>
-      <c r="E63" s="15" t="s">
+      <c r="E63" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="F63" s="15">
-        <v>100</v>
-      </c>
-      <c r="G63" s="15">
-        <v>0</v>
-      </c>
-      <c r="H63" s="15">
-        <v>100</v>
-      </c>
-      <c r="I63" s="15">
+      <c r="F63" s="11">
+        <v>100</v>
+      </c>
+      <c r="G63" s="11">
+        <v>0</v>
+      </c>
+      <c r="H63" s="11">
+        <v>100</v>
+      </c>
+      <c r="I63" s="11">
         <v>90</v>
       </c>
-      <c r="J63" s="37">
-        <v>100</v>
-      </c>
-      <c r="K63" s="37">
+      <c r="J63" s="11">
+        <v>100</v>
+      </c>
+      <c r="K63" s="11">
         <v>95</v>
       </c>
-      <c r="L63" s="15">
-        <v>100</v>
-      </c>
-      <c r="M63" s="15">
-        <v>100</v>
-      </c>
-      <c r="N63" s="37">
+      <c r="L63" s="11">
+        <v>100</v>
+      </c>
+      <c r="M63" s="11">
+        <v>100</v>
+      </c>
+      <c r="N63" s="35">
         <v>50</v>
       </c>
-      <c r="O63" s="15">
-        <v>0</v>
-      </c>
-      <c r="P63" s="37">
+      <c r="O63" s="11">
+        <v>0</v>
+      </c>
+      <c r="P63" s="11">
         <v>65</v>
       </c>
-      <c r="Q63" s="14">
+      <c r="Q63" s="10">
         <f>IF([1]punteo!L64="",0,[1]punteo!L64)</f>
         <v>100</v>
       </c>
@@ -6625,51 +6611,51 @@
       </c>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A64" s="15"/>
-      <c r="B64" s="16"/>
-      <c r="C64" s="15">
+      <c r="A64" s="11"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="11">
         <v>60</v>
       </c>
-      <c r="D64" s="15">
+      <c r="D64" s="11">
         <v>202531566</v>
       </c>
-      <c r="E64" s="15" t="s">
+      <c r="E64" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="F64" s="15">
-        <v>100</v>
-      </c>
-      <c r="G64" s="15">
-        <v>0</v>
-      </c>
-      <c r="H64" s="15">
-        <v>100</v>
-      </c>
-      <c r="I64" s="15">
+      <c r="F64" s="11">
+        <v>100</v>
+      </c>
+      <c r="G64" s="11">
+        <v>0</v>
+      </c>
+      <c r="H64" s="11">
+        <v>100</v>
+      </c>
+      <c r="I64" s="11">
         <v>90</v>
       </c>
-      <c r="J64" s="37">
-        <v>100</v>
-      </c>
-      <c r="K64" s="37">
+      <c r="J64" s="11">
+        <v>100</v>
+      </c>
+      <c r="K64" s="11">
         <v>85</v>
       </c>
-      <c r="L64" s="15">
-        <v>100</v>
-      </c>
-      <c r="M64" s="15">
-        <v>100</v>
-      </c>
-      <c r="N64" s="37">
+      <c r="L64" s="11">
+        <v>100</v>
+      </c>
+      <c r="M64" s="11">
+        <v>100</v>
+      </c>
+      <c r="N64" s="35">
         <v>70</v>
       </c>
-      <c r="O64" s="15">
+      <c r="O64" s="11">
         <v>75</v>
       </c>
-      <c r="P64" s="37">
+      <c r="P64" s="11">
         <v>55</v>
       </c>
-      <c r="Q64" s="14">
+      <c r="Q64" s="10">
         <f>IF([1]punteo!L65="",0,[1]punteo!L65)</f>
         <v>95</v>
       </c>
@@ -6696,55 +6682,55 @@
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A65" s="38">
+      <c r="A65" s="27">
         <v>0.27777777777777779</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C65" s="15">
+      <c r="C65" s="11">
         <v>61</v>
       </c>
-      <c r="D65" s="15">
+      <c r="D65" s="11">
         <v>202531611</v>
       </c>
-      <c r="E65" s="15" t="s">
+      <c r="E65" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="F65" s="15">
-        <v>100</v>
-      </c>
-      <c r="G65" s="15">
-        <v>0</v>
-      </c>
-      <c r="H65" s="15">
-        <v>100</v>
-      </c>
-      <c r="I65" s="15">
-        <v>0</v>
-      </c>
-      <c r="J65" s="37">
+      <c r="F65" s="11">
+        <v>100</v>
+      </c>
+      <c r="G65" s="11">
+        <v>0</v>
+      </c>
+      <c r="H65" s="11">
+        <v>100</v>
+      </c>
+      <c r="I65" s="11">
+        <v>0</v>
+      </c>
+      <c r="J65" s="11">
         <v>75</v>
       </c>
-      <c r="K65" s="37">
-        <v>100</v>
-      </c>
-      <c r="L65" s="15">
-        <v>100</v>
-      </c>
-      <c r="M65" s="15">
-        <v>100</v>
-      </c>
-      <c r="N65" s="37">
+      <c r="K65" s="11">
+        <v>100</v>
+      </c>
+      <c r="L65" s="11">
+        <v>100</v>
+      </c>
+      <c r="M65" s="11">
+        <v>100</v>
+      </c>
+      <c r="N65" s="35">
         <v>70</v>
       </c>
-      <c r="O65" s="15">
+      <c r="O65" s="11">
         <v>45</v>
       </c>
-      <c r="P65" s="37">
+      <c r="P65" s="11">
         <v>75</v>
       </c>
-      <c r="Q65" s="14">
+      <c r="Q65" s="10">
         <f>IF([1]punteo!L66="",0,[1]punteo!L66)</f>
         <v>0</v>
       </c>
@@ -6770,123 +6756,123 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A66" s="15"/>
-      <c r="B66" s="16"/>
-      <c r="C66" s="15">
+    <row r="66" spans="1:25" s="31" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="35"/>
+      <c r="B66" s="37"/>
+      <c r="C66" s="35">
         <v>62</v>
       </c>
-      <c r="D66" s="15">
+      <c r="D66" s="35">
         <v>202531645</v>
       </c>
-      <c r="E66" s="15" t="s">
+      <c r="E66" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="F66" s="15">
-        <v>100</v>
-      </c>
-      <c r="G66" s="15">
-        <v>100</v>
-      </c>
-      <c r="H66" s="15">
-        <v>100</v>
-      </c>
-      <c r="I66" s="15">
+      <c r="F66" s="35">
+        <v>100</v>
+      </c>
+      <c r="G66" s="35">
+        <v>100</v>
+      </c>
+      <c r="H66" s="35">
+        <v>100</v>
+      </c>
+      <c r="I66" s="35">
         <v>90</v>
       </c>
-      <c r="J66" s="37">
-        <v>100</v>
-      </c>
-      <c r="K66" s="37">
-        <v>100</v>
-      </c>
-      <c r="L66" s="15">
-        <v>100</v>
-      </c>
-      <c r="M66" s="15">
-        <v>0</v>
-      </c>
-      <c r="N66" s="37">
-        <v>0</v>
-      </c>
-      <c r="O66" s="15">
+      <c r="J66" s="35">
+        <v>100</v>
+      </c>
+      <c r="K66" s="35">
+        <v>100</v>
+      </c>
+      <c r="L66" s="35">
+        <v>100</v>
+      </c>
+      <c r="M66" s="35">
+        <v>0</v>
+      </c>
+      <c r="N66" s="35">
+        <v>40</v>
+      </c>
+      <c r="O66" s="35">
         <v>90</v>
       </c>
-      <c r="P66" s="37">
-        <v>100</v>
-      </c>
-      <c r="Q66" s="14">
+      <c r="P66" s="35">
+        <v>100</v>
+      </c>
+      <c r="Q66" s="38">
         <f>IF([1]punteo!L67="",0,[1]punteo!L67)</f>
         <v>90</v>
       </c>
-      <c r="R66" s="10">
+      <c r="R66" s="38">
         <f>IF([2]punteo!L67="",0,[2]punteo!L67)</f>
         <v>100</v>
       </c>
-      <c r="S66" s="10">
+      <c r="S66" s="38">
         <f>IF([3]punteo!L67="",0,[3]punteo!L67)</f>
         <v>100</v>
       </c>
-      <c r="T66" s="10"/>
-      <c r="U66" s="10"/>
-      <c r="V66">
+      <c r="T66" s="38"/>
+      <c r="U66" s="38"/>
+      <c r="V66" s="31">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="W66">
+      <c r="W66" s="31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="X66">
+      <c r="X66" s="31">
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A67" s="15"/>
-      <c r="B67" s="16"/>
-      <c r="C67" s="15">
+      <c r="A67" s="11"/>
+      <c r="B67" s="12"/>
+      <c r="C67" s="11">
         <v>63</v>
       </c>
-      <c r="D67" s="15">
+      <c r="D67" s="11">
         <v>202531663</v>
       </c>
-      <c r="E67" s="15" t="s">
+      <c r="E67" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="F67" s="15">
-        <v>100</v>
-      </c>
-      <c r="G67" s="15">
-        <v>0</v>
-      </c>
-      <c r="H67" s="15">
-        <v>0</v>
-      </c>
-      <c r="I67" s="15">
-        <v>0</v>
-      </c>
-      <c r="J67" s="37">
-        <v>0</v>
-      </c>
-      <c r="K67" s="37">
-        <v>0</v>
-      </c>
-      <c r="L67" s="15">
-        <v>0</v>
-      </c>
-      <c r="M67" s="15">
-        <v>0</v>
-      </c>
-      <c r="N67" s="37">
-        <v>0</v>
-      </c>
-      <c r="O67" s="15">
-        <v>0</v>
-      </c>
-      <c r="P67" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q67" s="14">
+      <c r="F67" s="11">
+        <v>100</v>
+      </c>
+      <c r="G67" s="11">
+        <v>0</v>
+      </c>
+      <c r="H67" s="11">
+        <v>0</v>
+      </c>
+      <c r="I67" s="11">
+        <v>0</v>
+      </c>
+      <c r="J67" s="11">
+        <v>0</v>
+      </c>
+      <c r="K67" s="11">
+        <v>0</v>
+      </c>
+      <c r="L67" s="11">
+        <v>0</v>
+      </c>
+      <c r="M67" s="11">
+        <v>0</v>
+      </c>
+      <c r="N67" s="35">
+        <v>0</v>
+      </c>
+      <c r="O67" s="11">
+        <v>0</v>
+      </c>
+      <c r="P67" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="10">
         <f>IF([1]punteo!L68="",0,[1]punteo!L68)</f>
         <v>0</v>
       </c>
@@ -6913,51 +6899,51 @@
       </c>
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A68" s="15"/>
-      <c r="B68" s="16"/>
-      <c r="C68" s="15">
+      <c r="A68" s="11"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="11">
         <v>64</v>
       </c>
-      <c r="D68" s="15">
+      <c r="D68" s="11">
         <v>202531724</v>
       </c>
-      <c r="E68" s="15" t="s">
+      <c r="E68" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="F68" s="15">
-        <v>100</v>
-      </c>
-      <c r="G68" s="15">
-        <v>0</v>
-      </c>
-      <c r="H68" s="15">
+      <c r="F68" s="11">
+        <v>100</v>
+      </c>
+      <c r="G68" s="11">
+        <v>0</v>
+      </c>
+      <c r="H68" s="11">
         <v>50</v>
       </c>
-      <c r="I68" s="15">
+      <c r="I68" s="11">
         <v>90</v>
       </c>
-      <c r="J68" s="37">
+      <c r="J68" s="11">
         <v>40</v>
       </c>
-      <c r="K68" s="37">
+      <c r="K68" s="11">
         <v>85</v>
       </c>
-      <c r="L68" s="15">
-        <v>100</v>
-      </c>
-      <c r="M68" s="15">
-        <v>100</v>
-      </c>
-      <c r="N68" s="37">
+      <c r="L68" s="11">
+        <v>100</v>
+      </c>
+      <c r="M68" s="11">
+        <v>100</v>
+      </c>
+      <c r="N68" s="35">
         <v>70</v>
       </c>
-      <c r="O68" s="15">
+      <c r="O68" s="11">
         <v>75</v>
       </c>
-      <c r="P68" s="37">
+      <c r="P68" s="11">
         <v>70</v>
       </c>
-      <c r="Q68" s="14">
+      <c r="Q68" s="10">
         <f>IF([1]punteo!L69="",0,[1]punteo!L69)</f>
         <v>100</v>
       </c>
@@ -6984,51 +6970,51 @@
       </c>
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A69" s="15"/>
-      <c r="B69" s="16"/>
-      <c r="C69" s="15">
+      <c r="A69" s="11"/>
+      <c r="B69" s="12"/>
+      <c r="C69" s="11">
         <v>65</v>
       </c>
-      <c r="D69" s="15">
+      <c r="D69" s="11">
         <v>202531736</v>
       </c>
-      <c r="E69" s="15" t="s">
+      <c r="E69" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F69" s="15">
-        <v>100</v>
-      </c>
-      <c r="G69" s="15">
-        <v>0</v>
-      </c>
-      <c r="H69" s="15">
-        <v>100</v>
-      </c>
-      <c r="I69" s="15">
-        <v>0</v>
-      </c>
-      <c r="J69" s="37">
-        <v>0</v>
-      </c>
-      <c r="K69" s="37">
-        <v>100</v>
-      </c>
-      <c r="L69" s="15">
-        <v>100</v>
-      </c>
-      <c r="M69" s="15">
-        <v>100</v>
-      </c>
-      <c r="N69" s="37">
-        <v>0</v>
-      </c>
-      <c r="O69" s="15">
+      <c r="F69" s="11">
+        <v>100</v>
+      </c>
+      <c r="G69" s="11">
+        <v>0</v>
+      </c>
+      <c r="H69" s="11">
+        <v>100</v>
+      </c>
+      <c r="I69" s="11">
+        <v>0</v>
+      </c>
+      <c r="J69" s="11">
+        <v>0</v>
+      </c>
+      <c r="K69" s="11">
+        <v>100</v>
+      </c>
+      <c r="L69" s="11">
+        <v>100</v>
+      </c>
+      <c r="M69" s="11">
+        <v>100</v>
+      </c>
+      <c r="N69" s="35">
+        <v>0</v>
+      </c>
+      <c r="O69" s="11">
         <v>60</v>
       </c>
-      <c r="P69" s="37">
+      <c r="P69" s="11">
         <v>65</v>
       </c>
-      <c r="Q69" s="14">
+      <c r="Q69" s="10">
         <f>IF([1]punteo!L70="",0,[1]punteo!L70)</f>
         <v>80</v>
       </c>
@@ -7055,55 +7041,55 @@
       </c>
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A70" s="38">
+      <c r="A70" s="27">
         <v>0.27777777777777779</v>
       </c>
       <c r="B70" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C70" s="15">
+      <c r="C70" s="11">
         <v>66</v>
       </c>
-      <c r="D70" s="15">
+      <c r="D70" s="11">
         <v>202531778</v>
       </c>
-      <c r="E70" s="15" t="s">
+      <c r="E70" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F70" s="15">
-        <v>100</v>
-      </c>
-      <c r="G70" s="15">
-        <v>0</v>
-      </c>
-      <c r="H70" s="15">
-        <v>100</v>
-      </c>
-      <c r="I70" s="15">
+      <c r="F70" s="11">
+        <v>100</v>
+      </c>
+      <c r="G70" s="11">
+        <v>0</v>
+      </c>
+      <c r="H70" s="11">
+        <v>100</v>
+      </c>
+      <c r="I70" s="11">
         <v>90</v>
       </c>
-      <c r="J70" s="37">
+      <c r="J70" s="11">
         <v>75</v>
       </c>
-      <c r="K70" s="37">
+      <c r="K70" s="11">
         <v>85</v>
       </c>
-      <c r="L70" s="15">
-        <v>100</v>
-      </c>
-      <c r="M70" s="15">
-        <v>100</v>
-      </c>
-      <c r="N70" s="37">
+      <c r="L70" s="11">
+        <v>100</v>
+      </c>
+      <c r="M70" s="11">
+        <v>100</v>
+      </c>
+      <c r="N70" s="35">
         <v>70</v>
       </c>
-      <c r="O70" s="15">
+      <c r="O70" s="11">
         <v>90</v>
       </c>
-      <c r="P70" s="37">
-        <v>100</v>
-      </c>
-      <c r="Q70" s="14">
+      <c r="P70" s="11">
+        <v>100</v>
+      </c>
+      <c r="Q70" s="10">
         <f>IF([1]punteo!L71="",0,[1]punteo!L71)</f>
         <v>100</v>
       </c>
@@ -7130,51 +7116,51 @@
       </c>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A71" s="15"/>
-      <c r="B71" s="16"/>
-      <c r="C71" s="15">
+      <c r="A71" s="11"/>
+      <c r="B71" s="12"/>
+      <c r="C71" s="11">
         <v>67</v>
       </c>
-      <c r="D71" s="15">
+      <c r="D71" s="11">
         <v>202531844</v>
       </c>
-      <c r="E71" s="15" t="s">
+      <c r="E71" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="F71" s="15">
-        <v>100</v>
-      </c>
-      <c r="G71" s="15">
-        <v>0</v>
-      </c>
-      <c r="H71" s="15">
-        <v>100</v>
-      </c>
-      <c r="I71" s="15">
-        <v>100</v>
-      </c>
-      <c r="J71" s="37">
-        <v>100</v>
-      </c>
-      <c r="K71" s="37">
-        <v>100</v>
-      </c>
-      <c r="L71" s="15">
-        <v>100</v>
-      </c>
-      <c r="M71" s="15">
-        <v>100</v>
-      </c>
-      <c r="N71" s="37">
-        <v>100</v>
-      </c>
-      <c r="O71" s="15">
-        <v>0</v>
-      </c>
-      <c r="P71" s="37">
-        <v>100</v>
-      </c>
-      <c r="Q71" s="14">
+      <c r="F71" s="11">
+        <v>100</v>
+      </c>
+      <c r="G71" s="11">
+        <v>0</v>
+      </c>
+      <c r="H71" s="11">
+        <v>100</v>
+      </c>
+      <c r="I71" s="11">
+        <v>100</v>
+      </c>
+      <c r="J71" s="11">
+        <v>100</v>
+      </c>
+      <c r="K71" s="11">
+        <v>100</v>
+      </c>
+      <c r="L71" s="11">
+        <v>100</v>
+      </c>
+      <c r="M71" s="11">
+        <v>100</v>
+      </c>
+      <c r="N71" s="35">
+        <v>100</v>
+      </c>
+      <c r="O71" s="11">
+        <v>0</v>
+      </c>
+      <c r="P71" s="11">
+        <v>100</v>
+      </c>
+      <c r="Q71" s="10">
         <f>IF([1]punteo!L72="",0,[1]punteo!L72)</f>
         <v>0</v>
       </c>
@@ -7201,51 +7187,51 @@
       </c>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A72" s="15"/>
-      <c r="B72" s="16"/>
-      <c r="C72" s="15">
+      <c r="A72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="11">
         <v>68</v>
       </c>
-      <c r="D72" s="15">
+      <c r="D72" s="11">
         <v>202531883</v>
       </c>
-      <c r="E72" s="15" t="s">
+      <c r="E72" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="F72" s="15">
-        <v>100</v>
-      </c>
-      <c r="G72" s="15">
-        <v>0</v>
-      </c>
-      <c r="H72" s="15">
-        <v>100</v>
-      </c>
-      <c r="I72" s="15">
-        <v>100</v>
-      </c>
-      <c r="J72" s="37">
+      <c r="F72" s="11">
+        <v>100</v>
+      </c>
+      <c r="G72" s="11">
+        <v>0</v>
+      </c>
+      <c r="H72" s="11">
+        <v>100</v>
+      </c>
+      <c r="I72" s="11">
+        <v>100</v>
+      </c>
+      <c r="J72" s="11">
         <v>85</v>
       </c>
-      <c r="K72" s="37">
-        <v>100</v>
-      </c>
-      <c r="L72" s="15">
-        <v>100</v>
-      </c>
-      <c r="M72" s="15">
-        <v>100</v>
-      </c>
-      <c r="N72" s="37">
+      <c r="K72" s="11">
+        <v>100</v>
+      </c>
+      <c r="L72" s="11">
+        <v>100</v>
+      </c>
+      <c r="M72" s="11">
+        <v>100</v>
+      </c>
+      <c r="N72" s="35">
         <v>90</v>
       </c>
-      <c r="O72" s="15">
+      <c r="O72" s="11">
         <v>95</v>
       </c>
-      <c r="P72" s="37">
+      <c r="P72" s="11">
         <v>85</v>
       </c>
-      <c r="Q72" s="14">
+      <c r="Q72" s="10">
         <f>IF([1]punteo!L73="",0,[1]punteo!L73)</f>
         <v>95</v>
       </c>
@@ -7272,51 +7258,51 @@
       </c>
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A73" s="15"/>
-      <c r="B73" s="16"/>
-      <c r="C73" s="15">
+      <c r="A73" s="11"/>
+      <c r="B73" s="12"/>
+      <c r="C73" s="11">
         <v>69</v>
       </c>
-      <c r="D73" s="15">
+      <c r="D73" s="11">
         <v>202531947</v>
       </c>
-      <c r="E73" s="15" t="s">
+      <c r="E73" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="F73" s="15">
-        <v>100</v>
-      </c>
-      <c r="G73" s="15">
-        <v>0</v>
-      </c>
-      <c r="H73" s="15">
-        <v>100</v>
-      </c>
-      <c r="I73" s="15">
-        <v>0</v>
-      </c>
-      <c r="J73" s="37">
+      <c r="F73" s="11">
+        <v>100</v>
+      </c>
+      <c r="G73" s="11">
+        <v>0</v>
+      </c>
+      <c r="H73" s="11">
+        <v>100</v>
+      </c>
+      <c r="I73" s="11">
+        <v>0</v>
+      </c>
+      <c r="J73" s="11">
         <v>85</v>
       </c>
-      <c r="K73" s="37">
+      <c r="K73" s="11">
         <v>75</v>
       </c>
-      <c r="L73" s="15">
-        <v>100</v>
-      </c>
-      <c r="M73" s="15">
-        <v>100</v>
-      </c>
-      <c r="N73" s="37">
+      <c r="L73" s="11">
+        <v>100</v>
+      </c>
+      <c r="M73" s="11">
+        <v>100</v>
+      </c>
+      <c r="N73" s="35">
         <v>50</v>
       </c>
-      <c r="O73" s="15">
+      <c r="O73" s="11">
         <v>90</v>
       </c>
-      <c r="P73" s="37">
+      <c r="P73" s="11">
         <v>70</v>
       </c>
-      <c r="Q73" s="14">
+      <c r="Q73" s="10">
         <f>IF([1]punteo!L74="",0,[1]punteo!L74)</f>
         <v>0</v>
       </c>
@@ -7343,55 +7329,55 @@
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A74" s="38">
+      <c r="A74" s="27">
         <v>0.27777777777777779</v>
       </c>
       <c r="B74" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C74" s="15">
+      <c r="C74" s="11">
         <v>70</v>
       </c>
-      <c r="D74" s="15">
+      <c r="D74" s="11">
         <v>202532062</v>
       </c>
-      <c r="E74" s="15" t="s">
+      <c r="E74" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="F74" s="15">
-        <v>0</v>
-      </c>
-      <c r="G74" s="15">
-        <v>0</v>
-      </c>
-      <c r="H74" s="15">
-        <v>100</v>
-      </c>
-      <c r="I74" s="15">
-        <v>0</v>
-      </c>
-      <c r="J74" s="37">
+      <c r="F74" s="11">
+        <v>0</v>
+      </c>
+      <c r="G74" s="11">
+        <v>0</v>
+      </c>
+      <c r="H74" s="11">
+        <v>100</v>
+      </c>
+      <c r="I74" s="11">
+        <v>0</v>
+      </c>
+      <c r="J74" s="11">
         <v>85</v>
       </c>
-      <c r="K74" s="37">
-        <v>100</v>
-      </c>
-      <c r="L74" s="15">
-        <v>100</v>
-      </c>
-      <c r="M74" s="15">
-        <v>100</v>
-      </c>
-      <c r="N74" s="37">
+      <c r="K74" s="11">
+        <v>100</v>
+      </c>
+      <c r="L74" s="11">
+        <v>100</v>
+      </c>
+      <c r="M74" s="11">
+        <v>100</v>
+      </c>
+      <c r="N74" s="35">
         <v>50</v>
       </c>
-      <c r="O74" s="15">
-        <v>0</v>
-      </c>
-      <c r="P74" s="37">
+      <c r="O74" s="11">
+        <v>0</v>
+      </c>
+      <c r="P74" s="11">
         <v>20</v>
       </c>
-      <c r="Q74" s="14">
+      <c r="Q74" s="10">
         <f>IF([1]punteo!L75="",0,[1]punteo!L75)</f>
         <v>100</v>
       </c>
@@ -7418,51 +7404,51 @@
       </c>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A75" s="15"/>
-      <c r="B75" s="16"/>
-      <c r="C75" s="15">
+      <c r="A75" s="11"/>
+      <c r="B75" s="12"/>
+      <c r="C75" s="11">
         <v>71</v>
       </c>
-      <c r="D75" s="15">
+      <c r="D75" s="11">
         <v>202532079</v>
       </c>
-      <c r="E75" s="15" t="s">
+      <c r="E75" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="F75" s="15">
-        <v>0</v>
-      </c>
-      <c r="G75" s="15">
-        <v>0</v>
-      </c>
-      <c r="H75" s="15">
-        <v>100</v>
-      </c>
-      <c r="I75" s="15">
-        <v>0</v>
-      </c>
-      <c r="J75" s="37">
-        <v>0</v>
-      </c>
-      <c r="K75" s="37">
+      <c r="F75" s="11">
+        <v>0</v>
+      </c>
+      <c r="G75" s="11">
+        <v>0</v>
+      </c>
+      <c r="H75" s="11">
+        <v>100</v>
+      </c>
+      <c r="I75" s="11">
+        <v>0</v>
+      </c>
+      <c r="J75" s="11">
+        <v>0</v>
+      </c>
+      <c r="K75" s="11">
         <v>50</v>
       </c>
-      <c r="L75" s="15">
-        <v>0</v>
-      </c>
-      <c r="M75" s="15">
-        <v>0</v>
-      </c>
-      <c r="N75" s="37">
-        <v>0</v>
-      </c>
-      <c r="O75" s="15">
-        <v>0</v>
-      </c>
-      <c r="P75" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q75" s="14">
+      <c r="L75" s="11">
+        <v>0</v>
+      </c>
+      <c r="M75" s="11">
+        <v>0</v>
+      </c>
+      <c r="N75" s="35">
+        <v>0</v>
+      </c>
+      <c r="O75" s="11">
+        <v>0</v>
+      </c>
+      <c r="P75" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="10">
         <f>IF([1]punteo!L76="",0,[1]punteo!L76)</f>
         <v>0</v>
       </c>
@@ -7489,53 +7475,53 @@
       </c>
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A76" s="15"/>
-      <c r="B76" s="16" t="s">
+      <c r="A76" s="11"/>
+      <c r="B76" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C76" s="15">
+      <c r="C76" s="11">
         <v>72</v>
       </c>
-      <c r="D76" s="15">
+      <c r="D76" s="11">
         <v>202530466</v>
       </c>
-      <c r="E76" s="15" t="s">
+      <c r="E76" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="F76" s="15">
-        <v>100</v>
-      </c>
-      <c r="G76" s="15">
-        <v>0</v>
-      </c>
-      <c r="H76" s="15">
-        <v>100</v>
-      </c>
-      <c r="I76" s="15">
-        <v>100</v>
-      </c>
-      <c r="J76" s="37">
-        <v>100</v>
-      </c>
-      <c r="K76" s="37">
-        <v>100</v>
-      </c>
-      <c r="L76" s="15">
-        <v>100</v>
-      </c>
-      <c r="M76" s="15">
-        <v>100</v>
-      </c>
-      <c r="N76" s="37">
-        <v>100</v>
-      </c>
-      <c r="O76" s="15">
-        <v>100</v>
-      </c>
-      <c r="P76" s="37">
-        <v>100</v>
-      </c>
-      <c r="Q76" s="14">
+      <c r="F76" s="11">
+        <v>100</v>
+      </c>
+      <c r="G76" s="11">
+        <v>0</v>
+      </c>
+      <c r="H76" s="11">
+        <v>100</v>
+      </c>
+      <c r="I76" s="11">
+        <v>100</v>
+      </c>
+      <c r="J76" s="11">
+        <v>100</v>
+      </c>
+      <c r="K76" s="11">
+        <v>100</v>
+      </c>
+      <c r="L76" s="11">
+        <v>100</v>
+      </c>
+      <c r="M76" s="11">
+        <v>100</v>
+      </c>
+      <c r="N76" s="35">
+        <v>100</v>
+      </c>
+      <c r="O76" s="11">
+        <v>100</v>
+      </c>
+      <c r="P76" s="11">
+        <v>100</v>
+      </c>
+      <c r="Q76" s="10">
         <f>IF([1]punteo!L77="",0,[1]punteo!L77)</f>
         <v>100</v>
       </c>
@@ -7562,53 +7548,53 @@
       </c>
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A77" s="15"/>
-      <c r="B77" s="16" t="s">
+      <c r="A77" s="11"/>
+      <c r="B77" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C77" s="15">
+      <c r="C77" s="11">
         <v>73</v>
       </c>
-      <c r="D77" s="15">
+      <c r="D77" s="11">
         <v>202030192</v>
       </c>
-      <c r="E77" s="15" t="s">
+      <c r="E77" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="F77" s="15">
-        <v>0</v>
-      </c>
-      <c r="G77" s="15">
-        <v>0</v>
-      </c>
-      <c r="H77" s="15">
+      <c r="F77" s="11">
+        <v>0</v>
+      </c>
+      <c r="G77" s="11">
+        <v>0</v>
+      </c>
+      <c r="H77" s="11">
         <v>50</v>
       </c>
-      <c r="I77" s="15">
+      <c r="I77" s="11">
         <v>75</v>
       </c>
-      <c r="J77" s="37">
-        <v>0</v>
-      </c>
-      <c r="K77" s="37">
-        <v>100</v>
-      </c>
-      <c r="L77" s="15">
-        <v>100</v>
-      </c>
-      <c r="M77" s="15">
-        <v>100</v>
-      </c>
-      <c r="N77" s="37">
-        <v>100</v>
-      </c>
-      <c r="O77" s="15">
+      <c r="J77" s="11">
+        <v>0</v>
+      </c>
+      <c r="K77" s="11">
+        <v>100</v>
+      </c>
+      <c r="L77" s="11">
+        <v>100</v>
+      </c>
+      <c r="M77" s="11">
+        <v>100</v>
+      </c>
+      <c r="N77" s="35">
+        <v>100</v>
+      </c>
+      <c r="O77" s="11">
         <v>85</v>
       </c>
-      <c r="P77" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="14">
+      <c r="P77" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="10">
         <f>IF([1]punteo!L78="",0,[1]punteo!L78)</f>
         <v>0</v>
       </c>
@@ -7635,70 +7621,70 @@
       </c>
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A78" s="15"/>
-      <c r="B78" s="16"/>
-      <c r="C78" s="19" t="s">
+      <c r="A78" s="11"/>
+      <c r="B78" s="12"/>
+      <c r="C78" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="D78" s="40"/>
-      <c r="E78" s="40"/>
-      <c r="F78" s="41">
+      <c r="D78" s="28"/>
+      <c r="E78" s="28"/>
+      <c r="F78" s="29">
         <f t="shared" ref="F78:N78" si="4">COUNTIF(F5:F77,"&gt;0")</f>
         <v>49</v>
       </c>
-      <c r="G78" s="41">
+      <c r="G78" s="29">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="H78" s="41">
+      <c r="H78" s="29">
         <f t="shared" si="4"/>
         <v>59</v>
       </c>
-      <c r="I78" s="41">
+      <c r="I78" s="29">
         <f t="shared" si="4"/>
         <v>47</v>
       </c>
-      <c r="J78" s="42">
+      <c r="J78" s="29">
         <f t="shared" si="4"/>
         <v>57</v>
       </c>
-      <c r="K78" s="42">
+      <c r="K78" s="29">
         <f t="shared" si="4"/>
         <v>62</v>
       </c>
-      <c r="L78" s="41">
+      <c r="L78" s="29">
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="M78" s="41">
+      <c r="M78" s="29">
         <f t="shared" si="4"/>
         <v>61</v>
       </c>
-      <c r="N78" s="42">
+      <c r="N78" s="36">
         <f t="shared" si="4"/>
-        <v>58</v>
-      </c>
-      <c r="O78" s="41">
+        <v>59</v>
+      </c>
+      <c r="O78" s="29">
         <f>COUNTIF(O5:O77,"&gt;0")</f>
         <v>52</v>
       </c>
-      <c r="P78" s="43">
+      <c r="P78" s="13">
         <f>COUNTIF(P5:P77,"&gt;0")</f>
         <v>60</v>
       </c>
-      <c r="Q78" s="43">
+      <c r="Q78" s="13">
         <f>COUNTIF(Q5:Q77,"&gt;0")</f>
         <v>50</v>
       </c>
-      <c r="R78" s="17">
+      <c r="R78" s="13">
         <f t="shared" ref="R78:S78" si="5">COUNTIF(R5:R77,"&gt;0")</f>
         <v>41</v>
       </c>
-      <c r="S78" s="17">
+      <c r="S78" s="13">
         <f t="shared" si="5"/>
         <v>52</v>
       </c>
-      <c r="T78" s="41"/>
+      <c r="T78" s="29"/>
       <c r="U78" s="7"/>
       <c r="V78" s="7"/>
       <c r="W78" s="7"/>
